--- a/templates/ERC000022/metadata_template_ERC000022.xlsx
+++ b/templates/ERC000022/metadata_template_ERC000022.xlsx
@@ -19,14 +19,14 @@
   <definedNames>
     <definedName name="drainageclassification">'cv_sample'!$BJ$1:$BJ$6</definedName>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AZ$1:$AZ$289</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AZ$1:$AZ$294</definedName>
     <definedName name="historytillage">'cv_sample'!$CE$1:$CE$9</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
     <definedName name="observedbioticrelationship">'cv_sample'!$H$1:$H$5</definedName>
-    <definedName name="platform">'cv_experiment'!$M$1:$M$17</definedName>
+    <definedName name="platform">'cv_experiment'!$M$1:$M$18</definedName>
     <definedName name="profileposition">'cv_sample'!$BQ$1:$BQ$5</definedName>
     <definedName name="relationshiptooxygen">'cv_sample'!$J$1:$J$7</definedName>
     <definedName name="sequencequalitycheck">'cv_sample'!$AE$1:$AE$3</definedName>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="884">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="899" uniqueCount="891">
   <si>
     <t>alias</t>
   </si>
@@ -456,6 +456,9 @@
     <t>ELEMENT</t>
   </si>
   <si>
+    <t>AVITI</t>
+  </si>
+  <si>
     <t>ULTIMA</t>
   </si>
   <si>
@@ -546,6 +549,9 @@
     <t>AB SOLiD System 3.0</t>
   </si>
   <si>
+    <t>AVITI 24</t>
+  </si>
+  <si>
     <t>BGISEQ-50</t>
   </si>
   <si>
@@ -1320,7 +1326,7 @@
     <t>amount or size of sample collected</t>
   </si>
   <si>
-    <t>(Optional) The total amount or size (volume (ml), mass (g) or area (m2) ) of sample collected. (Units: m3)</t>
+    <t>(Optional) The total amount or size (volume (ml), mass (g) or area (m2) ) of sample collected. (Units: kg)</t>
   </si>
   <si>
     <t>sieving</t>
@@ -1578,9 +1584,6 @@
     <t>Dominican Republic</t>
   </si>
   <si>
-    <t>East Timor</t>
-  </si>
-  <si>
     <t>Ecuador</t>
   </si>
   <si>
@@ -1599,6 +1602,9 @@
     <t>Estonia</t>
   </si>
   <si>
+    <t>Eswatini</t>
+  </si>
+  <si>
     <t>Ethiopia</t>
   </si>
   <si>
@@ -1800,6 +1806,9 @@
     <t>Liechtenstein</t>
   </si>
   <si>
+    <t>Line Islands</t>
+  </si>
+  <si>
     <t>Lithuania</t>
   </si>
   <si>
@@ -1809,9 +1818,6 @@
     <t>Macau</t>
   </si>
   <si>
-    <t>Macedonia</t>
-  </si>
-  <si>
     <t>Madagascar</t>
   </si>
   <si>
@@ -1851,7 +1857,7 @@
     <t>Mexico</t>
   </si>
   <si>
-    <t>Micronesia</t>
+    <t>Micronesia, Federated States of</t>
   </si>
   <si>
     <t>Midway Islands</t>
@@ -1920,6 +1926,9 @@
     <t>North Korea</t>
   </si>
   <si>
+    <t>North Macedonia</t>
+  </si>
+  <si>
     <t>North Sea</t>
   </si>
   <si>
@@ -1995,6 +2004,9 @@
     <t>Rwanda</t>
   </si>
   <si>
+    <t>Saint Barthelemy</t>
+  </si>
+  <si>
     <t>Saint Helena</t>
   </si>
   <si>
@@ -2016,6 +2028,9 @@
     <t>San Marino</t>
   </si>
   <si>
+    <t>Saint Martin</t>
+  </si>
+  <si>
     <t>Sao Tome and Principe</t>
   </si>
   <si>
@@ -2061,6 +2076,9 @@
     <t>South Korea</t>
   </si>
   <si>
+    <t>South Sudan</t>
+  </si>
+  <si>
     <t>Southern Ocean</t>
   </si>
   <si>
@@ -2073,6 +2091,9 @@
     <t>Sri Lanka</t>
   </si>
   <si>
+    <t>State of Palestine</t>
+  </si>
+  <si>
     <t>Sudan</t>
   </si>
   <si>
@@ -2082,9 +2103,6 @@
     <t>Svalbard</t>
   </si>
   <si>
-    <t>Swaziland</t>
-  </si>
-  <si>
     <t>Sweden</t>
   </si>
   <si>
@@ -2109,6 +2127,9 @@
     <t>Thailand</t>
   </si>
   <si>
+    <t>Timor-Leste</t>
+  </si>
+  <si>
     <t>Togo</t>
   </si>
   <si>
@@ -2169,12 +2190,12 @@
     <t>Viet Nam</t>
   </si>
   <si>
+    <t>Wake Island</t>
+  </si>
+  <si>
     <t>Virgin Islands</t>
   </si>
   <si>
-    <t>Wake Island</t>
-  </si>
-  <si>
     <t>Wallis and Futuna</t>
   </si>
   <si>
@@ -2430,7 +2451,7 @@
     <t>total nitrogen content</t>
   </si>
   <si>
-    <t>(Optional) Total nitrogen content of the sample (Units: µmol/L)</t>
+    <t>(Optional) Total nitrogen content of the sample (Units: µg/L)</t>
   </si>
   <si>
     <t>salinity method</t>
@@ -2625,7 +2646,7 @@
     <t>sample volume or weight for DNA extraction</t>
   </si>
   <si>
-    <t>(Optional) Volume (ml) or mass (g) of total collected sample processed for dna extraction. note: total sample collected should be entered under the term 'sample size'. (Units: ng)</t>
+    <t>(Optional) Volume (ml) or mass (g) of total collected sample processed for dna extraction. note: total sample collected should be entered under the term 'sample size'. (Units: mL)</t>
   </si>
   <si>
     <t>nucleic acid extraction</t>
@@ -2691,7 +2712,7 @@
     <t>depth</t>
   </si>
   <si>
-    <t>(Mandatory) The vertical distance below local surface, e.g. for sediment or soil samples depth is measured from sediment or soil surface, respectively. depth can be reported as an interval for subsurface samples. (Units: mm)</t>
+    <t>(Mandatory) The vertical distance below local surface, e.g. for sediment or soil samples depth is measured from sediment or soil surface, respectively. depth can be reported as an interval for subsurface samples. (Units: m)</t>
   </si>
 </sst>
 </file>
@@ -3218,10 +3239,10 @@
         <v>124</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -3262,10 +3283,10 @@
         <v>125</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -3292,7 +3313,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N87"/>
+  <dimension ref="G1:N88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -3309,7 +3330,7 @@
         <v>126</v>
       </c>
       <c r="N1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="7:14">
@@ -3326,7 +3347,7 @@
         <v>127</v>
       </c>
       <c r="N2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="7:14">
@@ -3343,7 +3364,7 @@
         <v>128</v>
       </c>
       <c r="N3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="7:14">
@@ -3360,7 +3381,7 @@
         <v>129</v>
       </c>
       <c r="N4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="7:14">
@@ -3377,7 +3398,7 @@
         <v>130</v>
       </c>
       <c r="N5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="7:14">
@@ -3394,7 +3415,7 @@
         <v>131</v>
       </c>
       <c r="N6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="7:14">
@@ -3411,7 +3432,7 @@
         <v>132</v>
       </c>
       <c r="N7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="7:14">
@@ -3428,7 +3449,7 @@
         <v>133</v>
       </c>
       <c r="N8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="7:14">
@@ -3445,7 +3466,7 @@
         <v>134</v>
       </c>
       <c r="N9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="7:14">
@@ -3459,7 +3480,7 @@
         <v>135</v>
       </c>
       <c r="N10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="7:14">
@@ -3473,7 +3494,7 @@
         <v>136</v>
       </c>
       <c r="N11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="7:14">
@@ -3487,7 +3508,7 @@
         <v>137</v>
       </c>
       <c r="N12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="7:14">
@@ -3501,7 +3522,7 @@
         <v>138</v>
       </c>
       <c r="N13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="7:14">
@@ -3515,7 +3536,7 @@
         <v>139</v>
       </c>
       <c r="N14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="7:14">
@@ -3529,7 +3550,7 @@
         <v>140</v>
       </c>
       <c r="N15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="7:14">
@@ -3543,7 +3564,7 @@
         <v>141</v>
       </c>
       <c r="N16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="7:14">
@@ -3557,7 +3578,7 @@
         <v>142</v>
       </c>
       <c r="N17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="7:14">
@@ -3567,8 +3588,11 @@
       <c r="I18" t="s">
         <v>54</v>
       </c>
+      <c r="M18" t="s">
+        <v>143</v>
+      </c>
       <c r="N18" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="7:14">
@@ -3579,7 +3603,7 @@
         <v>105</v>
       </c>
       <c r="N19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="7:14">
@@ -3590,7 +3614,7 @@
         <v>106</v>
       </c>
       <c r="N20" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="7:14">
@@ -3601,7 +3625,7 @@
         <v>107</v>
       </c>
       <c r="N21" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="7:14">
@@ -3612,7 +3636,7 @@
         <v>108</v>
       </c>
       <c r="N22" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="7:14">
@@ -3623,7 +3647,7 @@
         <v>109</v>
       </c>
       <c r="N23" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24" spans="7:14">
@@ -3634,7 +3658,7 @@
         <v>110</v>
       </c>
       <c r="N24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="7:14">
@@ -3645,7 +3669,7 @@
         <v>111</v>
       </c>
       <c r="N25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" spans="7:14">
@@ -3656,7 +3680,7 @@
         <v>112</v>
       </c>
       <c r="N26" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="7:14">
@@ -3667,7 +3691,7 @@
         <v>113</v>
       </c>
       <c r="N27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="7:14">
@@ -3678,7 +3702,7 @@
         <v>114</v>
       </c>
       <c r="N28" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="7:14">
@@ -3689,7 +3713,7 @@
         <v>115</v>
       </c>
       <c r="N29" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="7:14">
@@ -3700,7 +3724,7 @@
         <v>116</v>
       </c>
       <c r="N30" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="7:14">
@@ -3711,7 +3735,7 @@
         <v>117</v>
       </c>
       <c r="N31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="7:14">
@@ -3719,7 +3743,7 @@
         <v>66</v>
       </c>
       <c r="N32" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="7:14">
@@ -3727,7 +3751,7 @@
         <v>67</v>
       </c>
       <c r="N33" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="7:14">
@@ -3735,7 +3759,7 @@
         <v>68</v>
       </c>
       <c r="N34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="7:14">
@@ -3743,7 +3767,7 @@
         <v>69</v>
       </c>
       <c r="N35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="7:14">
@@ -3751,7 +3775,7 @@
         <v>70</v>
       </c>
       <c r="N36" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" spans="7:14">
@@ -3759,7 +3783,7 @@
         <v>71</v>
       </c>
       <c r="N37" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="38" spans="7:14">
@@ -3767,7 +3791,7 @@
         <v>72</v>
       </c>
       <c r="N38" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39" spans="7:14">
@@ -3775,7 +3799,7 @@
         <v>73</v>
       </c>
       <c r="N39" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40" spans="7:14">
@@ -3783,7 +3807,7 @@
         <v>74</v>
       </c>
       <c r="N40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="41" spans="7:14">
@@ -3791,236 +3815,241 @@
         <v>75</v>
       </c>
       <c r="N41" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="7:14">
       <c r="N42" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="43" spans="7:14">
       <c r="N43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="7:14">
       <c r="N44" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="7:14">
       <c r="N45" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="46" spans="7:14">
       <c r="N46" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="47" spans="7:14">
       <c r="N47" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="48" spans="7:14">
       <c r="N48" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="49" spans="14:14">
       <c r="N49" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="50" spans="14:14">
       <c r="N50" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="14:14">
       <c r="N51" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="52" spans="14:14">
       <c r="N52" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="53" spans="14:14">
       <c r="N53" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="54" spans="14:14">
       <c r="N54" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="55" spans="14:14">
       <c r="N55" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="56" spans="14:14">
       <c r="N56" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57" spans="14:14">
       <c r="N57" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="58" spans="14:14">
       <c r="N58" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="59" spans="14:14">
       <c r="N59" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="60" spans="14:14">
       <c r="N60" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" spans="14:14">
       <c r="N61" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="62" spans="14:14">
       <c r="N62" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="63" spans="14:14">
       <c r="N63" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="64" spans="14:14">
       <c r="N64" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="65" spans="14:14">
       <c r="N65" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="66" spans="14:14">
       <c r="N66" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="67" spans="14:14">
       <c r="N67" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="68" spans="14:14">
       <c r="N68" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="69" spans="14:14">
       <c r="N69" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="70" spans="14:14">
       <c r="N70" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="71" spans="14:14">
       <c r="N71" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="72" spans="14:14">
       <c r="N72" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="73" spans="14:14">
       <c r="N73" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="74" spans="14:14">
       <c r="N74" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="75" spans="14:14">
       <c r="N75" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="76" spans="14:14">
       <c r="N76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="77" spans="14:14">
       <c r="N77" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="78" spans="14:14">
       <c r="N78" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="79" spans="14:14">
       <c r="N79" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="80" spans="14:14">
       <c r="N80" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="81" spans="14:14">
       <c r="N81" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="82" spans="14:14">
       <c r="N82" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="83" spans="14:14">
       <c r="N83" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="84" spans="14:14">
       <c r="N84" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="85" spans="14:14">
       <c r="N85" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="86" spans="14:14">
       <c r="N86" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="87" spans="14:14">
       <c r="N87" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="88" spans="14:14">
+      <c r="N88" t="s">
         <v>117</v>
       </c>
     </row>
@@ -4042,27 +4071,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -4082,122 +4111,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -4221,690 +4250,690 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>730</v>
+        <v>737</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>732</v>
+        <v>739</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>734</v>
+        <v>741</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>736</v>
+        <v>743</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>738</v>
+        <v>745</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>740</v>
+        <v>747</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>742</v>
+        <v>749</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>744</v>
+        <v>751</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>746</v>
+        <v>753</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>754</v>
+        <v>761</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>762</v>
+        <v>769</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>764</v>
+        <v>771</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>766</v>
+        <v>773</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>768</v>
+        <v>775</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>770</v>
+        <v>777</v>
       </c>
       <c r="BO1" s="1" t="s">
-        <v>772</v>
+        <v>779</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>774</v>
+        <v>781</v>
       </c>
       <c r="BQ1" s="1" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="BS1" s="1" t="s">
-        <v>785</v>
+        <v>792</v>
       </c>
       <c r="BT1" s="1" t="s">
-        <v>787</v>
+        <v>794</v>
       </c>
       <c r="BU1" s="1" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="BV1" s="1" t="s">
-        <v>791</v>
+        <v>798</v>
       </c>
       <c r="BW1" s="1" t="s">
-        <v>793</v>
+        <v>800</v>
       </c>
       <c r="BX1" s="1" t="s">
-        <v>795</v>
+        <v>802</v>
       </c>
       <c r="BY1" s="1" t="s">
-        <v>797</v>
+        <v>804</v>
       </c>
       <c r="BZ1" s="1" t="s">
-        <v>799</v>
+        <v>806</v>
       </c>
       <c r="CA1" s="1" t="s">
-        <v>801</v>
+        <v>808</v>
       </c>
       <c r="CB1" s="1" t="s">
-        <v>803</v>
+        <v>810</v>
       </c>
       <c r="CC1" s="1" t="s">
-        <v>805</v>
+        <v>812</v>
       </c>
       <c r="CD1" s="1" t="s">
-        <v>807</v>
+        <v>814</v>
       </c>
       <c r="CE1" s="1" t="s">
-        <v>818</v>
+        <v>825</v>
       </c>
       <c r="CF1" s="1" t="s">
-        <v>820</v>
+        <v>827</v>
       </c>
       <c r="CG1" s="1" t="s">
-        <v>822</v>
+        <v>829</v>
       </c>
       <c r="CH1" s="1" t="s">
-        <v>824</v>
+        <v>831</v>
       </c>
       <c r="CI1" s="1" t="s">
-        <v>826</v>
+        <v>833</v>
       </c>
       <c r="CJ1" s="1" t="s">
-        <v>828</v>
+        <v>835</v>
       </c>
       <c r="CK1" s="1" t="s">
-        <v>830</v>
+        <v>837</v>
       </c>
       <c r="CL1" s="1" t="s">
-        <v>832</v>
+        <v>839</v>
       </c>
       <c r="CM1" s="1" t="s">
-        <v>834</v>
+        <v>841</v>
       </c>
       <c r="CN1" s="1" t="s">
-        <v>836</v>
+        <v>843</v>
       </c>
       <c r="CO1" s="1" t="s">
-        <v>838</v>
+        <v>845</v>
       </c>
       <c r="CP1" s="1" t="s">
-        <v>840</v>
+        <v>847</v>
       </c>
       <c r="CQ1" s="1" t="s">
-        <v>842</v>
+        <v>849</v>
       </c>
       <c r="CR1" s="1" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
       <c r="CS1" s="1" t="s">
-        <v>846</v>
+        <v>853</v>
       </c>
       <c r="CT1" s="1" t="s">
-        <v>848</v>
+        <v>855</v>
       </c>
       <c r="CU1" s="1" t="s">
-        <v>850</v>
+        <v>857</v>
       </c>
       <c r="CV1" s="1" t="s">
-        <v>852</v>
+        <v>859</v>
       </c>
       <c r="CW1" s="1" t="s">
-        <v>854</v>
+        <v>861</v>
       </c>
       <c r="CX1" s="1" t="s">
-        <v>856</v>
+        <v>863</v>
       </c>
       <c r="CY1" s="1" t="s">
-        <v>858</v>
+        <v>865</v>
       </c>
       <c r="CZ1" s="1" t="s">
-        <v>860</v>
+        <v>867</v>
       </c>
       <c r="DA1" s="1" t="s">
-        <v>862</v>
+        <v>869</v>
       </c>
       <c r="DB1" s="1" t="s">
-        <v>864</v>
+        <v>871</v>
       </c>
       <c r="DC1" s="1" t="s">
-        <v>866</v>
+        <v>873</v>
       </c>
       <c r="DD1" s="1" t="s">
-        <v>868</v>
+        <v>875</v>
       </c>
       <c r="DE1" s="1" t="s">
-        <v>870</v>
+        <v>877</v>
       </c>
       <c r="DF1" s="1" t="s">
-        <v>872</v>
+        <v>879</v>
       </c>
       <c r="DG1" s="1" t="s">
-        <v>874</v>
+        <v>881</v>
       </c>
       <c r="DH1" s="1" t="s">
-        <v>876</v>
+        <v>883</v>
       </c>
       <c r="DI1" s="1" t="s">
-        <v>878</v>
+        <v>885</v>
       </c>
       <c r="DJ1" s="1" t="s">
-        <v>880</v>
+        <v>887</v>
       </c>
       <c r="DK1" s="1" t="s">
-        <v>882</v>
+        <v>889</v>
       </c>
     </row>
     <row r="2" spans="1:115" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AS2" s="2" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AU2" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="AW2" s="2" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AX2" s="2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AY2" s="2" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AZ2" s="2" t="s">
-        <v>731</v>
+        <v>738</v>
       </c>
       <c r="BA2" s="2" t="s">
-        <v>733</v>
+        <v>740</v>
       </c>
       <c r="BB2" s="2" t="s">
-        <v>735</v>
+        <v>742</v>
       </c>
       <c r="BC2" s="2" t="s">
-        <v>737</v>
+        <v>744</v>
       </c>
       <c r="BD2" s="2" t="s">
-        <v>739</v>
+        <v>746</v>
       </c>
       <c r="BE2" s="2" t="s">
-        <v>741</v>
+        <v>748</v>
       </c>
       <c r="BF2" s="2" t="s">
-        <v>743</v>
+        <v>750</v>
       </c>
       <c r="BG2" s="2" t="s">
-        <v>745</v>
+        <v>752</v>
       </c>
       <c r="BH2" s="2" t="s">
-        <v>747</v>
+        <v>754</v>
       </c>
       <c r="BI2" s="2" t="s">
-        <v>755</v>
+        <v>762</v>
       </c>
       <c r="BJ2" s="2" t="s">
-        <v>763</v>
+        <v>770</v>
       </c>
       <c r="BK2" s="2" t="s">
-        <v>765</v>
+        <v>772</v>
       </c>
       <c r="BL2" s="2" t="s">
-        <v>767</v>
+        <v>774</v>
       </c>
       <c r="BM2" s="2" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="BN2" s="2" t="s">
-        <v>771</v>
+        <v>778</v>
       </c>
       <c r="BO2" s="2" t="s">
-        <v>773</v>
+        <v>780</v>
       </c>
       <c r="BP2" s="2" t="s">
-        <v>775</v>
+        <v>782</v>
       </c>
       <c r="BQ2" s="2" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="BR2" s="2" t="s">
-        <v>784</v>
+        <v>791</v>
       </c>
       <c r="BS2" s="2" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="BT2" s="2" t="s">
-        <v>788</v>
+        <v>795</v>
       </c>
       <c r="BU2" s="2" t="s">
-        <v>790</v>
+        <v>797</v>
       </c>
       <c r="BV2" s="2" t="s">
-        <v>792</v>
+        <v>799</v>
       </c>
       <c r="BW2" s="2" t="s">
-        <v>794</v>
+        <v>801</v>
       </c>
       <c r="BX2" s="2" t="s">
-        <v>796</v>
+        <v>803</v>
       </c>
       <c r="BY2" s="2" t="s">
-        <v>798</v>
+        <v>805</v>
       </c>
       <c r="BZ2" s="2" t="s">
-        <v>800</v>
+        <v>807</v>
       </c>
       <c r="CA2" s="2" t="s">
-        <v>802</v>
+        <v>809</v>
       </c>
       <c r="CB2" s="2" t="s">
-        <v>804</v>
+        <v>811</v>
       </c>
       <c r="CC2" s="2" t="s">
-        <v>806</v>
+        <v>813</v>
       </c>
       <c r="CD2" s="2" t="s">
-        <v>808</v>
+        <v>815</v>
       </c>
       <c r="CE2" s="2" t="s">
-        <v>819</v>
+        <v>826</v>
       </c>
       <c r="CF2" s="2" t="s">
-        <v>821</v>
+        <v>828</v>
       </c>
       <c r="CG2" s="2" t="s">
-        <v>823</v>
+        <v>830</v>
       </c>
       <c r="CH2" s="2" t="s">
-        <v>825</v>
+        <v>832</v>
       </c>
       <c r="CI2" s="2" t="s">
-        <v>827</v>
+        <v>834</v>
       </c>
       <c r="CJ2" s="2" t="s">
-        <v>829</v>
+        <v>836</v>
       </c>
       <c r="CK2" s="2" t="s">
-        <v>831</v>
+        <v>838</v>
       </c>
       <c r="CL2" s="2" t="s">
-        <v>833</v>
+        <v>840</v>
       </c>
       <c r="CM2" s="2" t="s">
-        <v>835</v>
+        <v>842</v>
       </c>
       <c r="CN2" s="2" t="s">
-        <v>837</v>
+        <v>844</v>
       </c>
       <c r="CO2" s="2" t="s">
-        <v>839</v>
+        <v>846</v>
       </c>
       <c r="CP2" s="2" t="s">
-        <v>841</v>
+        <v>848</v>
       </c>
       <c r="CQ2" s="2" t="s">
-        <v>843</v>
+        <v>850</v>
       </c>
       <c r="CR2" s="2" t="s">
-        <v>845</v>
+        <v>852</v>
       </c>
       <c r="CS2" s="2" t="s">
-        <v>847</v>
+        <v>854</v>
       </c>
       <c r="CT2" s="2" t="s">
-        <v>849</v>
+        <v>856</v>
       </c>
       <c r="CU2" s="2" t="s">
-        <v>851</v>
+        <v>858</v>
       </c>
       <c r="CV2" s="2" t="s">
-        <v>853</v>
+        <v>860</v>
       </c>
       <c r="CW2" s="2" t="s">
-        <v>855</v>
+        <v>862</v>
       </c>
       <c r="CX2" s="2" t="s">
-        <v>857</v>
+        <v>864</v>
       </c>
       <c r="CY2" s="2" t="s">
-        <v>859</v>
+        <v>866</v>
       </c>
       <c r="CZ2" s="2" t="s">
-        <v>861</v>
+        <v>868</v>
       </c>
       <c r="DA2" s="2" t="s">
-        <v>863</v>
+        <v>870</v>
       </c>
       <c r="DB2" s="2" t="s">
-        <v>865</v>
+        <v>872</v>
       </c>
       <c r="DC2" s="2" t="s">
-        <v>867</v>
+        <v>874</v>
       </c>
       <c r="DD2" s="2" t="s">
-        <v>869</v>
+        <v>876</v>
       </c>
       <c r="DE2" s="2" t="s">
-        <v>871</v>
+        <v>878</v>
       </c>
       <c r="DF2" s="2" t="s">
-        <v>873</v>
+        <v>880</v>
       </c>
       <c r="DG2" s="2" t="s">
-        <v>875</v>
+        <v>882</v>
       </c>
       <c r="DH2" s="2" t="s">
-        <v>877</v>
+        <v>884</v>
       </c>
       <c r="DI2" s="2" t="s">
-        <v>879</v>
+        <v>886</v>
       </c>
       <c r="DJ2" s="2" t="s">
-        <v>881</v>
+        <v>888</v>
       </c>
       <c r="DK2" s="2" t="s">
-        <v>883</v>
+        <v>890</v>
       </c>
     </row>
   </sheetData>
@@ -4946,1761 +4975,1786 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:CE289"/>
+  <dimension ref="G1:CE294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:83">
       <c r="G1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="J1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="R1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AE1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AZ1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="BI1" t="s">
-        <v>748</v>
+        <v>755</v>
       </c>
       <c r="BJ1" t="s">
-        <v>756</v>
+        <v>763</v>
       </c>
       <c r="BQ1" t="s">
-        <v>776</v>
+        <v>783</v>
       </c>
       <c r="CE1" t="s">
-        <v>809</v>
+        <v>816</v>
       </c>
     </row>
     <row r="2" spans="7:83">
       <c r="G2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="H2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="J2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="R2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AE2" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AZ2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="BI2" t="s">
-        <v>749</v>
+        <v>756</v>
       </c>
       <c r="BJ2" t="s">
-        <v>757</v>
+        <v>764</v>
       </c>
       <c r="BQ2" t="s">
-        <v>777</v>
+        <v>784</v>
       </c>
       <c r="CE2" t="s">
-        <v>810</v>
+        <v>817</v>
       </c>
     </row>
     <row r="3" spans="7:83">
       <c r="G3" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="H3" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="J3" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="R3" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AE3" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AZ3" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="BI3" t="s">
-        <v>750</v>
+        <v>757</v>
       </c>
       <c r="BJ3" t="s">
-        <v>758</v>
+        <v>765</v>
       </c>
       <c r="BQ3" t="s">
-        <v>778</v>
+        <v>785</v>
       </c>
       <c r="CE3" t="s">
-        <v>811</v>
+        <v>818</v>
       </c>
     </row>
     <row r="4" spans="7:83">
       <c r="G4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="H4" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="J4" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="R4" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AZ4" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="BI4" t="s">
-        <v>751</v>
+        <v>758</v>
       </c>
       <c r="BJ4" t="s">
-        <v>759</v>
+        <v>766</v>
       </c>
       <c r="BQ4" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="CE4" t="s">
-        <v>812</v>
+        <v>819</v>
       </c>
     </row>
     <row r="5" spans="7:83">
       <c r="G5" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H5" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="J5" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="R5" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AZ5" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="BI5" t="s">
-        <v>752</v>
+        <v>759</v>
       </c>
       <c r="BJ5" t="s">
-        <v>760</v>
+        <v>767</v>
       </c>
       <c r="BQ5" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="CE5" t="s">
-        <v>813</v>
+        <v>820</v>
       </c>
     </row>
     <row r="6" spans="7:83">
       <c r="G6" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="J6" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="R6" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AZ6" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="BI6" t="s">
-        <v>753</v>
+        <v>760</v>
       </c>
       <c r="BJ6" t="s">
-        <v>761</v>
+        <v>768</v>
       </c>
       <c r="CE6" t="s">
-        <v>814</v>
+        <v>821</v>
       </c>
     </row>
     <row r="7" spans="7:83">
       <c r="G7" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J7" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="R7" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AZ7" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="CE7" t="s">
-        <v>815</v>
+        <v>822</v>
       </c>
     </row>
     <row r="8" spans="7:83">
       <c r="G8" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="R8" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AZ8" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="CE8" t="s">
-        <v>816</v>
+        <v>823</v>
       </c>
     </row>
     <row r="9" spans="7:83">
       <c r="G9" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="R9" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AZ9" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="CE9" t="s">
-        <v>817</v>
+        <v>824</v>
       </c>
     </row>
     <row r="10" spans="7:83">
       <c r="G10" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="R10" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AZ10" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="11" spans="7:83">
       <c r="G11" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="R11" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AZ11" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="12" spans="7:83">
       <c r="G12" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="R12" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AZ12" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="13" spans="7:83">
       <c r="G13" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="R13" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AZ13" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="14" spans="7:83">
       <c r="G14" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="R14" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AZ14" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="15" spans="7:83">
       <c r="G15" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="R15" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AZ15" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="16" spans="7:83">
       <c r="G16" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="R16" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AZ16" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="17" spans="7:52">
       <c r="G17" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="R17" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AZ17" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="18" spans="7:52">
       <c r="G18" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="R18" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AZ18" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="19" spans="7:52">
       <c r="G19" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="R19" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AZ19" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="20" spans="7:52">
       <c r="G20" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="R20" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AZ20" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="21" spans="7:52">
       <c r="G21" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="R21" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AZ21" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="22" spans="7:52">
       <c r="G22" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="R22" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AZ22" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="23" spans="7:52">
       <c r="G23" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="R23" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AZ23" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="24" spans="7:52">
       <c r="G24" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="R24" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AZ24" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="25" spans="7:52">
       <c r="G25" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="R25" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AZ25" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="26" spans="7:52">
       <c r="G26" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="R26" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AZ26" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="27" spans="7:52">
       <c r="G27" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="R27" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AZ27" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="28" spans="7:52">
       <c r="G28" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="R28" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AZ28" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="29" spans="7:52">
       <c r="G29" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="R29" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AZ29" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="30" spans="7:52">
       <c r="G30" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="R30" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AZ30" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="31" spans="7:52">
       <c r="R31" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AZ31" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="32" spans="7:52">
       <c r="R32" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AZ32" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="33" spans="52:52">
       <c r="AZ33" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="34" spans="52:52">
       <c r="AZ34" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="35" spans="52:52">
       <c r="AZ35" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="36" spans="52:52">
       <c r="AZ36" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="37" spans="52:52">
       <c r="AZ37" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="38" spans="52:52">
       <c r="AZ38" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="39" spans="52:52">
       <c r="AZ39" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="40" spans="52:52">
       <c r="AZ40" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="41" spans="52:52">
       <c r="AZ41" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="42" spans="52:52">
       <c r="AZ42" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="43" spans="52:52">
       <c r="AZ43" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="44" spans="52:52">
       <c r="AZ44" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="45" spans="52:52">
       <c r="AZ45" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="46" spans="52:52">
       <c r="AZ46" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="47" spans="52:52">
       <c r="AZ47" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="48" spans="52:52">
       <c r="AZ48" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="49" spans="52:52">
       <c r="AZ49" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="50" spans="52:52">
       <c r="AZ50" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="51" spans="52:52">
       <c r="AZ51" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="52" spans="52:52">
       <c r="AZ52" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="53" spans="52:52">
       <c r="AZ53" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="54" spans="52:52">
       <c r="AZ54" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="55" spans="52:52">
       <c r="AZ55" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="56" spans="52:52">
       <c r="AZ56" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="57" spans="52:52">
       <c r="AZ57" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="58" spans="52:52">
       <c r="AZ58" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="59" spans="52:52">
       <c r="AZ59" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="60" spans="52:52">
       <c r="AZ60" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="61" spans="52:52">
       <c r="AZ61" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="62" spans="52:52">
       <c r="AZ62" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="63" spans="52:52">
       <c r="AZ63" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="64" spans="52:52">
       <c r="AZ64" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="65" spans="52:52">
       <c r="AZ65" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="66" spans="52:52">
       <c r="AZ66" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="67" spans="52:52">
       <c r="AZ67" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="68" spans="52:52">
       <c r="AZ68" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="69" spans="52:52">
       <c r="AZ69" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="70" spans="52:52">
       <c r="AZ70" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="71" spans="52:52">
       <c r="AZ71" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="72" spans="52:52">
       <c r="AZ72" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="73" spans="52:52">
       <c r="AZ73" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="74" spans="52:52">
       <c r="AZ74" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="75" spans="52:52">
       <c r="AZ75" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="76" spans="52:52">
       <c r="AZ76" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="77" spans="52:52">
       <c r="AZ77" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="78" spans="52:52">
       <c r="AZ78" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="79" spans="52:52">
       <c r="AZ79" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="80" spans="52:52">
       <c r="AZ80" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="81" spans="52:52">
       <c r="AZ81" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="82" spans="52:52">
       <c r="AZ82" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="83" spans="52:52">
       <c r="AZ83" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="84" spans="52:52">
       <c r="AZ84" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="85" spans="52:52">
       <c r="AZ85" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="86" spans="52:52">
       <c r="AZ86" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="87" spans="52:52">
       <c r="AZ87" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="88" spans="52:52">
       <c r="AZ88" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="89" spans="52:52">
       <c r="AZ89" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="90" spans="52:52">
       <c r="AZ90" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="91" spans="52:52">
       <c r="AZ91" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="92" spans="52:52">
       <c r="AZ92" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="93" spans="52:52">
       <c r="AZ93" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="94" spans="52:52">
       <c r="AZ94" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="95" spans="52:52">
       <c r="AZ95" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="96" spans="52:52">
       <c r="AZ96" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="97" spans="52:52">
       <c r="AZ97" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="98" spans="52:52">
       <c r="AZ98" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="99" spans="52:52">
       <c r="AZ99" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="100" spans="52:52">
       <c r="AZ100" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="101" spans="52:52">
       <c r="AZ101" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="102" spans="52:52">
       <c r="AZ102" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="103" spans="52:52">
       <c r="AZ103" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="104" spans="52:52">
       <c r="AZ104" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="105" spans="52:52">
       <c r="AZ105" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="106" spans="52:52">
       <c r="AZ106" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="107" spans="52:52">
       <c r="AZ107" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="108" spans="52:52">
       <c r="AZ108" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="109" spans="52:52">
       <c r="AZ109" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="110" spans="52:52">
       <c r="AZ110" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="111" spans="52:52">
       <c r="AZ111" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="112" spans="52:52">
       <c r="AZ112" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="113" spans="52:52">
       <c r="AZ113" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="114" spans="52:52">
       <c r="AZ114" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="115" spans="52:52">
       <c r="AZ115" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="116" spans="52:52">
       <c r="AZ116" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="117" spans="52:52">
       <c r="AZ117" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="118" spans="52:52">
       <c r="AZ118" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="119" spans="52:52">
       <c r="AZ119" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="120" spans="52:52">
       <c r="AZ120" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="121" spans="52:52">
       <c r="AZ121" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="122" spans="52:52">
       <c r="AZ122" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="123" spans="52:52">
       <c r="AZ123" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="124" spans="52:52">
       <c r="AZ124" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="125" spans="52:52">
       <c r="AZ125" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="126" spans="52:52">
       <c r="AZ126" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="127" spans="52:52">
       <c r="AZ127" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="128" spans="52:52">
       <c r="AZ128" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="129" spans="52:52">
       <c r="AZ129" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="130" spans="52:52">
       <c r="AZ130" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="131" spans="52:52">
       <c r="AZ131" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="132" spans="52:52">
       <c r="AZ132" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="133" spans="52:52">
       <c r="AZ133" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="134" spans="52:52">
       <c r="AZ134" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="135" spans="52:52">
       <c r="AZ135" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="136" spans="52:52">
       <c r="AZ136" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="137" spans="52:52">
       <c r="AZ137" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="138" spans="52:52">
       <c r="AZ138" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="139" spans="52:52">
       <c r="AZ139" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="140" spans="52:52">
       <c r="AZ140" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="141" spans="52:52">
       <c r="AZ141" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="142" spans="52:52">
       <c r="AZ142" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="143" spans="52:52">
       <c r="AZ143" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="144" spans="52:52">
       <c r="AZ144" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="145" spans="52:52">
       <c r="AZ145" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="146" spans="52:52">
       <c r="AZ146" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="147" spans="52:52">
       <c r="AZ147" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="148" spans="52:52">
       <c r="AZ148" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="149" spans="52:52">
       <c r="AZ149" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="150" spans="52:52">
       <c r="AZ150" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="151" spans="52:52">
       <c r="AZ151" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="152" spans="52:52">
       <c r="AZ152" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="153" spans="52:52">
       <c r="AZ153" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="154" spans="52:52">
       <c r="AZ154" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="155" spans="52:52">
       <c r="AZ155" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="156" spans="52:52">
       <c r="AZ156" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="157" spans="52:52">
       <c r="AZ157" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="158" spans="52:52">
       <c r="AZ158" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="159" spans="52:52">
       <c r="AZ159" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="160" spans="52:52">
       <c r="AZ160" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="161" spans="52:52">
       <c r="AZ161" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="162" spans="52:52">
       <c r="AZ162" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="163" spans="52:52">
       <c r="AZ163" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="164" spans="52:52">
       <c r="AZ164" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="165" spans="52:52">
       <c r="AZ165" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="166" spans="52:52">
       <c r="AZ166" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="167" spans="52:52">
       <c r="AZ167" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="168" spans="52:52">
       <c r="AZ168" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="169" spans="52:52">
       <c r="AZ169" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="170" spans="52:52">
       <c r="AZ170" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="171" spans="52:52">
       <c r="AZ171" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="172" spans="52:52">
       <c r="AZ172" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="173" spans="52:52">
       <c r="AZ173" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="174" spans="52:52">
       <c r="AZ174" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="175" spans="52:52">
       <c r="AZ175" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="176" spans="52:52">
       <c r="AZ176" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="177" spans="52:52">
       <c r="AZ177" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="178" spans="52:52">
       <c r="AZ178" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="179" spans="52:52">
       <c r="AZ179" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="180" spans="52:52">
       <c r="AZ180" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="181" spans="52:52">
       <c r="AZ181" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
     </row>
     <row r="182" spans="52:52">
       <c r="AZ182" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="183" spans="52:52">
       <c r="AZ183" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="184" spans="52:52">
       <c r="AZ184" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="185" spans="52:52">
       <c r="AZ185" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="186" spans="52:52">
       <c r="AZ186" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="187" spans="52:52">
       <c r="AZ187" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="188" spans="52:52">
       <c r="AZ188" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="189" spans="52:52">
       <c r="AZ189" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="190" spans="52:52">
       <c r="AZ190" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="191" spans="52:52">
       <c r="AZ191" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
     </row>
     <row r="192" spans="52:52">
       <c r="AZ192" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="193" spans="52:52">
       <c r="AZ193" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
     </row>
     <row r="194" spans="52:52">
       <c r="AZ194" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
     </row>
     <row r="195" spans="52:52">
       <c r="AZ195" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="196" spans="52:52">
       <c r="AZ196" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
     </row>
     <row r="197" spans="52:52">
       <c r="AZ197" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
     </row>
     <row r="198" spans="52:52">
       <c r="AZ198" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="199" spans="52:52">
       <c r="AZ199" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="200" spans="52:52">
       <c r="AZ200" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="201" spans="52:52">
       <c r="AZ201" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
     <row r="202" spans="52:52">
       <c r="AZ202" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="203" spans="52:52">
       <c r="AZ203" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
     </row>
     <row r="204" spans="52:52">
       <c r="AZ204" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="205" spans="52:52">
       <c r="AZ205" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
     </row>
     <row r="206" spans="52:52">
       <c r="AZ206" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="207" spans="52:52">
       <c r="AZ207" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
     </row>
     <row r="208" spans="52:52">
       <c r="AZ208" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="209" spans="52:52">
       <c r="AZ209" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="210" spans="52:52">
       <c r="AZ210" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="211" spans="52:52">
       <c r="AZ211" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="212" spans="52:52">
       <c r="AZ212" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="213" spans="52:52">
       <c r="AZ213" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="214" spans="52:52">
       <c r="AZ214" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="215" spans="52:52">
       <c r="AZ215" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
     </row>
     <row r="216" spans="52:52">
       <c r="AZ216" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="217" spans="52:52">
       <c r="AZ217" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
     </row>
     <row r="218" spans="52:52">
       <c r="AZ218" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="219" spans="52:52">
       <c r="AZ219" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="220" spans="52:52">
       <c r="AZ220" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="221" spans="52:52">
       <c r="AZ221" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="222" spans="52:52">
       <c r="AZ222" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="223" spans="52:52">
       <c r="AZ223" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="224" spans="52:52">
       <c r="AZ224" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="225" spans="52:52">
       <c r="AZ225" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="226" spans="52:52">
       <c r="AZ226" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="227" spans="52:52">
       <c r="AZ227" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="228" spans="52:52">
       <c r="AZ228" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="229" spans="52:52">
       <c r="AZ229" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="230" spans="52:52">
       <c r="AZ230" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
     </row>
     <row r="231" spans="52:52">
       <c r="AZ231" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="232" spans="52:52">
       <c r="AZ232" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="233" spans="52:52">
       <c r="AZ233" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="234" spans="52:52">
       <c r="AZ234" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="235" spans="52:52">
       <c r="AZ235" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
     </row>
     <row r="236" spans="52:52">
       <c r="AZ236" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="237" spans="52:52">
       <c r="AZ237" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
     <row r="238" spans="52:52">
       <c r="AZ238" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="239" spans="52:52">
       <c r="AZ239" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
     </row>
     <row r="240" spans="52:52">
       <c r="AZ240" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
     </row>
     <row r="241" spans="52:52">
       <c r="AZ241" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
     </row>
     <row r="242" spans="52:52">
       <c r="AZ242" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
     </row>
     <row r="243" spans="52:52">
       <c r="AZ243" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="244" spans="52:52">
       <c r="AZ244" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
     </row>
     <row r="245" spans="52:52">
       <c r="AZ245" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
     </row>
     <row r="246" spans="52:52">
       <c r="AZ246" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
     </row>
     <row r="247" spans="52:52">
       <c r="AZ247" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
     </row>
     <row r="248" spans="52:52">
       <c r="AZ248" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
     </row>
     <row r="249" spans="52:52">
       <c r="AZ249" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
     </row>
     <row r="250" spans="52:52">
       <c r="AZ250" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
     </row>
     <row r="251" spans="52:52">
       <c r="AZ251" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
     </row>
     <row r="252" spans="52:52">
       <c r="AZ252" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
     </row>
     <row r="253" spans="52:52">
       <c r="AZ253" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
     </row>
     <row r="254" spans="52:52">
       <c r="AZ254" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
     </row>
     <row r="255" spans="52:52">
       <c r="AZ255" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
     </row>
     <row r="256" spans="52:52">
       <c r="AZ256" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
     </row>
     <row r="257" spans="52:52">
       <c r="AZ257" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
     </row>
     <row r="258" spans="52:52">
       <c r="AZ258" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
     </row>
     <row r="259" spans="52:52">
       <c r="AZ259" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
     </row>
     <row r="260" spans="52:52">
       <c r="AZ260" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
     </row>
     <row r="261" spans="52:52">
       <c r="AZ261" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
     </row>
     <row r="262" spans="52:52">
       <c r="AZ262" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
     </row>
     <row r="263" spans="52:52">
       <c r="AZ263" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
     </row>
     <row r="264" spans="52:52">
       <c r="AZ264" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
     </row>
     <row r="265" spans="52:52">
       <c r="AZ265" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
     </row>
     <row r="266" spans="52:52">
       <c r="AZ266" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
     </row>
     <row r="267" spans="52:52">
       <c r="AZ267" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
     </row>
     <row r="268" spans="52:52">
       <c r="AZ268" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
     </row>
     <row r="269" spans="52:52">
       <c r="AZ269" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
     </row>
     <row r="270" spans="52:52">
       <c r="AZ270" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
     </row>
     <row r="271" spans="52:52">
       <c r="AZ271" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
     </row>
     <row r="272" spans="52:52">
       <c r="AZ272" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
     </row>
     <row r="273" spans="52:52">
       <c r="AZ273" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
     </row>
     <row r="274" spans="52:52">
       <c r="AZ274" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
     </row>
     <row r="275" spans="52:52">
       <c r="AZ275" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
     </row>
     <row r="276" spans="52:52">
       <c r="AZ276" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
     </row>
     <row r="277" spans="52:52">
       <c r="AZ277" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
     </row>
     <row r="278" spans="52:52">
       <c r="AZ278" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
     </row>
     <row r="279" spans="52:52">
       <c r="AZ279" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
     </row>
     <row r="280" spans="52:52">
       <c r="AZ280" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
     </row>
     <row r="281" spans="52:52">
       <c r="AZ281" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
     </row>
     <row r="282" spans="52:52">
       <c r="AZ282" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
     </row>
     <row r="283" spans="52:52">
       <c r="AZ283" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
     </row>
     <row r="284" spans="52:52">
       <c r="AZ284" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
     </row>
     <row r="285" spans="52:52">
       <c r="AZ285" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
     </row>
     <row r="286" spans="52:52">
       <c r="AZ286" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
     </row>
     <row r="287" spans="52:52">
       <c r="AZ287" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
     </row>
     <row r="288" spans="52:52">
       <c r="AZ288" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
     </row>
     <row r="289" spans="52:52">
       <c r="AZ289" t="s">
-        <v>729</v>
+        <v>731</v>
+      </c>
+    </row>
+    <row r="290" spans="52:52">
+      <c r="AZ290" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="291" spans="52:52">
+      <c r="AZ291" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="292" spans="52:52">
+      <c r="AZ292" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="293" spans="52:52">
+      <c r="AZ293" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="294" spans="52:52">
+      <c r="AZ294" t="s">
+        <v>736</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000022/metadata_template_ERC000022.xlsx
+++ b/templates/ERC000022/metadata_template_ERC000022.xlsx
@@ -17,30 +17,30 @@
     <sheet name="cv_sample" sheetId="8" state="hidden" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="drainageclassification">'cv_sample'!$BH$1:$BH$6</definedName>
+    <definedName name="drainageclassification">'cv_sample'!$BI$1:$BI$6</definedName>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AX$1:$AX$289</definedName>
-    <definedName name="historytillage">'cv_sample'!$CC$1:$CC$9</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AY$1:$AY$294</definedName>
+    <definedName name="historytillage">'cv_sample'!$CD$1:$CD$9</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
-    <definedName name="observedbioticrelationship">'cv_sample'!$F$1:$F$5</definedName>
-    <definedName name="platform">'cv_experiment'!$M$1:$M$17</definedName>
-    <definedName name="profileposition">'cv_sample'!$BO$1:$BO$5</definedName>
-    <definedName name="relationshiptooxygen">'cv_sample'!$H$1:$H$7</definedName>
-    <definedName name="sequencequalitycheck">'cv_sample'!$AC$1:$AC$3</definedName>
-    <definedName name="soilhorizon">'cv_sample'!$BG$1:$BG$6</definedName>
-    <definedName name="soiltype">'cv_sample'!$P$1:$P$32</definedName>
+    <definedName name="observedbioticrelationship">'cv_sample'!$G$1:$G$5</definedName>
+    <definedName name="platform">'cv_experiment'!$M$1:$M$18</definedName>
+    <definedName name="profileposition">'cv_sample'!$BP$1:$BP$5</definedName>
+    <definedName name="relationshiptooxygen">'cv_sample'!$I$1:$I$7</definedName>
+    <definedName name="sequencequalitycheck">'cv_sample'!$AD$1:$AD$3</definedName>
+    <definedName name="soilhorizon">'cv_sample'!$BH$1:$BH$6</definedName>
+    <definedName name="soiltype">'cv_sample'!$Q$1:$Q$32</definedName>
     <definedName name="studytype">'cv_study'!$C$1:$C$15</definedName>
-    <definedName name="trophiclevel">'cv_sample'!$E$1:$E$30</definedName>
+    <definedName name="trophiclevel">'cv_sample'!$F$1:$F$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="888" uniqueCount="880">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="897" uniqueCount="889">
   <si>
     <t>alias</t>
   </si>
@@ -456,6 +456,9 @@
     <t>ELEMENT</t>
   </si>
   <si>
+    <t>AVITI</t>
+  </si>
+  <si>
     <t>ULTIMA</t>
   </si>
   <si>
@@ -546,6 +549,9 @@
     <t>AB SOLiD System 3.0</t>
   </si>
   <si>
+    <t>AVITI 24</t>
+  </si>
+  <si>
     <t>BGISEQ-50</t>
   </si>
   <si>
@@ -846,6 +852,12 @@
     <t>(Mandatory) Ncbi taxonomy identifier.  this is appropriate for individual organisms and some environmental samples.</t>
   </si>
   <si>
+    <t>scientific_name</t>
+  </si>
+  <si>
+    <t>(Optional) Scientific name of sample that distinguishes its taxonomy.  please use a name or synonym that is tracked in the insdc taxonomy database. also, this field can be used to confirm the taxon_id setting.</t>
+  </si>
+  <si>
     <t>sample_description</t>
   </si>
   <si>
@@ -1566,9 +1578,6 @@
     <t>Dominican Republic</t>
   </si>
   <si>
-    <t>East Timor</t>
-  </si>
-  <si>
     <t>Ecuador</t>
   </si>
   <si>
@@ -1587,6 +1596,9 @@
     <t>Estonia</t>
   </si>
   <si>
+    <t>Eswatini</t>
+  </si>
+  <si>
     <t>Ethiopia</t>
   </si>
   <si>
@@ -1788,6 +1800,9 @@
     <t>Liechtenstein</t>
   </si>
   <si>
+    <t>Line Islands</t>
+  </si>
+  <si>
     <t>Lithuania</t>
   </si>
   <si>
@@ -1797,9 +1812,6 @@
     <t>Macau</t>
   </si>
   <si>
-    <t>Macedonia</t>
-  </si>
-  <si>
     <t>Madagascar</t>
   </si>
   <si>
@@ -1839,7 +1851,7 @@
     <t>Mexico</t>
   </si>
   <si>
-    <t>Micronesia</t>
+    <t>Micronesia, Federated States of</t>
   </si>
   <si>
     <t>Midway Islands</t>
@@ -1908,6 +1920,9 @@
     <t>North Korea</t>
   </si>
   <si>
+    <t>North Macedonia</t>
+  </si>
+  <si>
     <t>North Sea</t>
   </si>
   <si>
@@ -1983,6 +1998,9 @@
     <t>Rwanda</t>
   </si>
   <si>
+    <t>Saint Barthelemy</t>
+  </si>
+  <si>
     <t>Saint Helena</t>
   </si>
   <si>
@@ -2004,6 +2022,9 @@
     <t>San Marino</t>
   </si>
   <si>
+    <t>Saint Martin</t>
+  </si>
+  <si>
     <t>Sao Tome and Principe</t>
   </si>
   <si>
@@ -2049,6 +2070,9 @@
     <t>South Korea</t>
   </si>
   <si>
+    <t>South Sudan</t>
+  </si>
+  <si>
     <t>Southern Ocean</t>
   </si>
   <si>
@@ -2061,6 +2085,9 @@
     <t>Sri Lanka</t>
   </si>
   <si>
+    <t>State of Palestine</t>
+  </si>
+  <si>
     <t>Sudan</t>
   </si>
   <si>
@@ -2070,9 +2097,6 @@
     <t>Svalbard</t>
   </si>
   <si>
-    <t>Swaziland</t>
-  </si>
-  <si>
     <t>Sweden</t>
   </si>
   <si>
@@ -2097,6 +2121,9 @@
     <t>Thailand</t>
   </si>
   <si>
+    <t>Timor-Leste</t>
+  </si>
+  <si>
     <t>Togo</t>
   </si>
   <si>
@@ -2157,10 +2184,10 @@
     <t>Viet Nam</t>
   </si>
   <si>
+    <t>Wake Island</t>
+  </si>
+  <si>
     <t>Virgin Islands</t>
-  </si>
-  <si>
-    <t>Wake Island</t>
   </si>
   <si>
     <t>Wallis and Futuna</t>
@@ -3206,10 +3233,10 @@
         <v>124</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -3250,10 +3277,10 @@
         <v>125</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -3280,7 +3307,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N87"/>
+  <dimension ref="G1:N88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -3297,7 +3324,7 @@
         <v>126</v>
       </c>
       <c r="N1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="7:14">
@@ -3314,7 +3341,7 @@
         <v>127</v>
       </c>
       <c r="N2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="7:14">
@@ -3331,7 +3358,7 @@
         <v>128</v>
       </c>
       <c r="N3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="7:14">
@@ -3348,7 +3375,7 @@
         <v>129</v>
       </c>
       <c r="N4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="7:14">
@@ -3365,7 +3392,7 @@
         <v>130</v>
       </c>
       <c r="N5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="7:14">
@@ -3382,7 +3409,7 @@
         <v>131</v>
       </c>
       <c r="N6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="7:14">
@@ -3399,7 +3426,7 @@
         <v>132</v>
       </c>
       <c r="N7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="7:14">
@@ -3416,7 +3443,7 @@
         <v>133</v>
       </c>
       <c r="N8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="7:14">
@@ -3433,7 +3460,7 @@
         <v>134</v>
       </c>
       <c r="N9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="7:14">
@@ -3447,7 +3474,7 @@
         <v>135</v>
       </c>
       <c r="N10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="7:14">
@@ -3461,7 +3488,7 @@
         <v>136</v>
       </c>
       <c r="N11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="7:14">
@@ -3475,7 +3502,7 @@
         <v>137</v>
       </c>
       <c r="N12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="7:14">
@@ -3489,7 +3516,7 @@
         <v>138</v>
       </c>
       <c r="N13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="7:14">
@@ -3503,7 +3530,7 @@
         <v>139</v>
       </c>
       <c r="N14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="7:14">
@@ -3517,7 +3544,7 @@
         <v>140</v>
       </c>
       <c r="N15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="7:14">
@@ -3531,7 +3558,7 @@
         <v>141</v>
       </c>
       <c r="N16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="7:14">
@@ -3545,7 +3572,7 @@
         <v>142</v>
       </c>
       <c r="N17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="7:14">
@@ -3555,8 +3582,11 @@
       <c r="I18" t="s">
         <v>54</v>
       </c>
+      <c r="M18" t="s">
+        <v>143</v>
+      </c>
       <c r="N18" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="7:14">
@@ -3567,7 +3597,7 @@
         <v>105</v>
       </c>
       <c r="N19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="7:14">
@@ -3578,7 +3608,7 @@
         <v>106</v>
       </c>
       <c r="N20" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="7:14">
@@ -3589,7 +3619,7 @@
         <v>107</v>
       </c>
       <c r="N21" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="7:14">
@@ -3600,7 +3630,7 @@
         <v>108</v>
       </c>
       <c r="N22" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="7:14">
@@ -3611,7 +3641,7 @@
         <v>109</v>
       </c>
       <c r="N23" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24" spans="7:14">
@@ -3622,7 +3652,7 @@
         <v>110</v>
       </c>
       <c r="N24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="7:14">
@@ -3633,7 +3663,7 @@
         <v>111</v>
       </c>
       <c r="N25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" spans="7:14">
@@ -3644,7 +3674,7 @@
         <v>112</v>
       </c>
       <c r="N26" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="7:14">
@@ -3655,7 +3685,7 @@
         <v>113</v>
       </c>
       <c r="N27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="7:14">
@@ -3666,7 +3696,7 @@
         <v>114</v>
       </c>
       <c r="N28" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="7:14">
@@ -3677,7 +3707,7 @@
         <v>115</v>
       </c>
       <c r="N29" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="7:14">
@@ -3688,7 +3718,7 @@
         <v>116</v>
       </c>
       <c r="N30" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="7:14">
@@ -3699,7 +3729,7 @@
         <v>117</v>
       </c>
       <c r="N31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="7:14">
@@ -3707,7 +3737,7 @@
         <v>66</v>
       </c>
       <c r="N32" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="7:14">
@@ -3715,7 +3745,7 @@
         <v>67</v>
       </c>
       <c r="N33" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="7:14">
@@ -3723,7 +3753,7 @@
         <v>68</v>
       </c>
       <c r="N34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="7:14">
@@ -3731,7 +3761,7 @@
         <v>69</v>
       </c>
       <c r="N35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="7:14">
@@ -3739,7 +3769,7 @@
         <v>70</v>
       </c>
       <c r="N36" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" spans="7:14">
@@ -3747,7 +3777,7 @@
         <v>71</v>
       </c>
       <c r="N37" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="38" spans="7:14">
@@ -3755,7 +3785,7 @@
         <v>72</v>
       </c>
       <c r="N38" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39" spans="7:14">
@@ -3763,7 +3793,7 @@
         <v>73</v>
       </c>
       <c r="N39" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40" spans="7:14">
@@ -3771,7 +3801,7 @@
         <v>74</v>
       </c>
       <c r="N40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="41" spans="7:14">
@@ -3779,236 +3809,241 @@
         <v>75</v>
       </c>
       <c r="N41" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="7:14">
       <c r="N42" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="43" spans="7:14">
       <c r="N43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="7:14">
       <c r="N44" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="7:14">
       <c r="N45" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="46" spans="7:14">
       <c r="N46" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="47" spans="7:14">
       <c r="N47" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="48" spans="7:14">
       <c r="N48" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="49" spans="14:14">
       <c r="N49" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="50" spans="14:14">
       <c r="N50" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="14:14">
       <c r="N51" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="52" spans="14:14">
       <c r="N52" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="53" spans="14:14">
       <c r="N53" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="54" spans="14:14">
       <c r="N54" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="55" spans="14:14">
       <c r="N55" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="56" spans="14:14">
       <c r="N56" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57" spans="14:14">
       <c r="N57" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="58" spans="14:14">
       <c r="N58" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="59" spans="14:14">
       <c r="N59" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="60" spans="14:14">
       <c r="N60" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" spans="14:14">
       <c r="N61" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="62" spans="14:14">
       <c r="N62" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="63" spans="14:14">
       <c r="N63" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="64" spans="14:14">
       <c r="N64" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="65" spans="14:14">
       <c r="N65" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="66" spans="14:14">
       <c r="N66" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="67" spans="14:14">
       <c r="N67" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="68" spans="14:14">
       <c r="N68" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="69" spans="14:14">
       <c r="N69" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="70" spans="14:14">
       <c r="N70" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="71" spans="14:14">
       <c r="N71" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="72" spans="14:14">
       <c r="N72" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="73" spans="14:14">
       <c r="N73" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="74" spans="14:14">
       <c r="N74" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="75" spans="14:14">
       <c r="N75" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="76" spans="14:14">
       <c r="N76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="77" spans="14:14">
       <c r="N77" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="78" spans="14:14">
       <c r="N78" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="79" spans="14:14">
       <c r="N79" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="80" spans="14:14">
       <c r="N80" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="81" spans="14:14">
       <c r="N81" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="82" spans="14:14">
       <c r="N82" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="83" spans="14:14">
       <c r="N83" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="84" spans="14:14">
       <c r="N84" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="85" spans="14:14">
       <c r="N85" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="86" spans="14:14">
       <c r="N86" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="87" spans="14:14">
       <c r="N87" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="88" spans="14:14">
+      <c r="N88" t="s">
         <v>117</v>
       </c>
     </row>
@@ -4030,27 +4065,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -4070,122 +4105,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -4195,13 +4230,13 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:DI2"/>
+  <dimension ref="A1:DJ2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="301" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:113">
+    <row r="1" spans="1:114">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4209,710 +4244,716 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="AU1" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="AV1" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="AW1" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="AX1" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="AY1" s="1" t="s">
+        <v>735</v>
+      </c>
+      <c r="AZ1" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="BA1" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="BB1" s="1" t="s">
+        <v>741</v>
+      </c>
+      <c r="BC1" s="1" t="s">
+        <v>743</v>
+      </c>
+      <c r="BD1" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="BE1" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="BF1" s="1" t="s">
+        <v>749</v>
+      </c>
+      <c r="BG1" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="BH1" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="BI1" s="1" t="s">
+        <v>767</v>
+      </c>
+      <c r="BJ1" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="BK1" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="BL1" s="1" t="s">
+        <v>773</v>
+      </c>
+      <c r="BM1" s="1" t="s">
+        <v>775</v>
+      </c>
+      <c r="BN1" s="1" t="s">
+        <v>777</v>
+      </c>
+      <c r="BO1" s="1" t="s">
+        <v>779</v>
+      </c>
+      <c r="BP1" s="1" t="s">
+        <v>786</v>
+      </c>
+      <c r="BQ1" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="BR1" s="1" t="s">
+        <v>790</v>
+      </c>
+      <c r="BS1" s="1" t="s">
+        <v>792</v>
+      </c>
+      <c r="BT1" s="1" t="s">
+        <v>794</v>
+      </c>
+      <c r="BU1" s="1" t="s">
+        <v>796</v>
+      </c>
+      <c r="BV1" s="1" t="s">
+        <v>798</v>
+      </c>
+      <c r="BW1" s="1" t="s">
+        <v>800</v>
+      </c>
+      <c r="BX1" s="1" t="s">
+        <v>802</v>
+      </c>
+      <c r="BY1" s="1" t="s">
+        <v>804</v>
+      </c>
+      <c r="BZ1" s="1" t="s">
+        <v>806</v>
+      </c>
+      <c r="CA1" s="1" t="s">
+        <v>808</v>
+      </c>
+      <c r="CB1" s="1" t="s">
+        <v>810</v>
+      </c>
+      <c r="CC1" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="CD1" s="1" t="s">
+        <v>823</v>
+      </c>
+      <c r="CE1" s="1" t="s">
+        <v>825</v>
+      </c>
+      <c r="CF1" s="1" t="s">
+        <v>827</v>
+      </c>
+      <c r="CG1" s="1" t="s">
+        <v>829</v>
+      </c>
+      <c r="CH1" s="1" t="s">
+        <v>831</v>
+      </c>
+      <c r="CI1" s="1" t="s">
+        <v>833</v>
+      </c>
+      <c r="CJ1" s="1" t="s">
+        <v>835</v>
+      </c>
+      <c r="CK1" s="1" t="s">
+        <v>837</v>
+      </c>
+      <c r="CL1" s="1" t="s">
+        <v>839</v>
+      </c>
+      <c r="CM1" s="1" t="s">
+        <v>841</v>
+      </c>
+      <c r="CN1" s="1" t="s">
+        <v>843</v>
+      </c>
+      <c r="CO1" s="1" t="s">
+        <v>845</v>
+      </c>
+      <c r="CP1" s="1" t="s">
+        <v>847</v>
+      </c>
+      <c r="CQ1" s="1" t="s">
+        <v>849</v>
+      </c>
+      <c r="CR1" s="1" t="s">
+        <v>851</v>
+      </c>
+      <c r="CS1" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="CT1" s="1" t="s">
+        <v>855</v>
+      </c>
+      <c r="CU1" s="1" t="s">
+        <v>857</v>
+      </c>
+      <c r="CV1" s="1" t="s">
+        <v>859</v>
+      </c>
+      <c r="CW1" s="1" t="s">
+        <v>861</v>
+      </c>
+      <c r="CX1" s="1" t="s">
+        <v>863</v>
+      </c>
+      <c r="CY1" s="1" t="s">
+        <v>865</v>
+      </c>
+      <c r="CZ1" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="DA1" s="1" t="s">
+        <v>869</v>
+      </c>
+      <c r="DB1" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="DC1" s="1" t="s">
+        <v>873</v>
+      </c>
+      <c r="DD1" s="1" t="s">
+        <v>875</v>
+      </c>
+      <c r="DE1" s="1" t="s">
+        <v>877</v>
+      </c>
+      <c r="DF1" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="DG1" s="1" t="s">
+        <v>881</v>
+      </c>
+      <c r="DH1" s="1" t="s">
+        <v>883</v>
+      </c>
+      <c r="DI1" s="1" t="s">
+        <v>885</v>
+      </c>
+      <c r="DJ1" s="1" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="2" spans="1:114" ht="150" customHeight="1">
+      <c r="A2" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>378</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="AC1" s="1" t="s">
+      <c r="B2" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="Z2" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="AA2" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="AB2" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="AC2" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="AD1" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="AK1" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="AL1" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="AM1" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>435</v>
-      </c>
-      <c r="AX1" s="1" t="s">
-        <v>726</v>
-      </c>
-      <c r="AY1" s="1" t="s">
-        <v>728</v>
-      </c>
-      <c r="AZ1" s="1" t="s">
-        <v>730</v>
-      </c>
-      <c r="BA1" s="1" t="s">
-        <v>732</v>
-      </c>
-      <c r="BB1" s="1" t="s">
-        <v>734</v>
-      </c>
-      <c r="BC1" s="1" t="s">
+      <c r="AD2" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="AE2" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="AF2" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="AG2" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="AH2" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="AI2" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="AJ2" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="AK2" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="AL2" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="AM2" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="AN2" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="AO2" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="AP2" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="AQ2" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="AR2" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="AS2" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="AT2" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="AU2" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="AV2" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="AW2" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="AX2" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="AY2" s="2" t="s">
         <v>736</v>
       </c>
-      <c r="BD1" s="1" t="s">
+      <c r="AZ2" s="2" t="s">
         <v>738</v>
       </c>
-      <c r="BE1" s="1" t="s">
+      <c r="BA2" s="2" t="s">
         <v>740</v>
       </c>
-      <c r="BF1" s="1" t="s">
+      <c r="BB2" s="2" t="s">
         <v>742</v>
       </c>
-      <c r="BG1" s="1" t="s">
+      <c r="BC2" s="2" t="s">
+        <v>744</v>
+      </c>
+      <c r="BD2" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="BE2" s="2" t="s">
+        <v>748</v>
+      </c>
+      <c r="BF2" s="2" t="s">
         <v>750</v>
       </c>
-      <c r="BH1" s="1" t="s">
-        <v>758</v>
-      </c>
-      <c r="BI1" s="1" t="s">
+      <c r="BG2" s="2" t="s">
+        <v>752</v>
+      </c>
+      <c r="BH2" s="2" t="s">
         <v>760</v>
       </c>
-      <c r="BJ1" s="1" t="s">
-        <v>762</v>
-      </c>
-      <c r="BK1" s="1" t="s">
-        <v>764</v>
-      </c>
-      <c r="BL1" s="1" t="s">
-        <v>766</v>
-      </c>
-      <c r="BM1" s="1" t="s">
+      <c r="BI2" s="2" t="s">
         <v>768</v>
       </c>
-      <c r="BN1" s="1" t="s">
+      <c r="BJ2" s="2" t="s">
         <v>770</v>
       </c>
-      <c r="BO1" s="1" t="s">
-        <v>777</v>
-      </c>
-      <c r="BP1" s="1" t="s">
-        <v>779</v>
-      </c>
-      <c r="BQ1" s="1" t="s">
-        <v>781</v>
-      </c>
-      <c r="BR1" s="1" t="s">
-        <v>783</v>
-      </c>
-      <c r="BS1" s="1" t="s">
-        <v>785</v>
-      </c>
-      <c r="BT1" s="1" t="s">
+      <c r="BK2" s="2" t="s">
+        <v>772</v>
+      </c>
+      <c r="BL2" s="2" t="s">
+        <v>774</v>
+      </c>
+      <c r="BM2" s="2" t="s">
+        <v>776</v>
+      </c>
+      <c r="BN2" s="2" t="s">
+        <v>778</v>
+      </c>
+      <c r="BO2" s="2" t="s">
+        <v>780</v>
+      </c>
+      <c r="BP2" s="2" t="s">
         <v>787</v>
       </c>
-      <c r="BU1" s="1" t="s">
+      <c r="BQ2" s="2" t="s">
         <v>789</v>
       </c>
-      <c r="BV1" s="1" t="s">
+      <c r="BR2" s="2" t="s">
         <v>791</v>
       </c>
-      <c r="BW1" s="1" t="s">
+      <c r="BS2" s="2" t="s">
         <v>793</v>
       </c>
-      <c r="BX1" s="1" t="s">
+      <c r="BT2" s="2" t="s">
         <v>795</v>
       </c>
-      <c r="BY1" s="1" t="s">
+      <c r="BU2" s="2" t="s">
         <v>797</v>
       </c>
-      <c r="BZ1" s="1" t="s">
+      <c r="BV2" s="2" t="s">
         <v>799</v>
       </c>
-      <c r="CA1" s="1" t="s">
+      <c r="BW2" s="2" t="s">
         <v>801</v>
       </c>
-      <c r="CB1" s="1" t="s">
+      <c r="BX2" s="2" t="s">
         <v>803</v>
       </c>
-      <c r="CC1" s="1" t="s">
-        <v>814</v>
-      </c>
-      <c r="CD1" s="1" t="s">
-        <v>816</v>
-      </c>
-      <c r="CE1" s="1" t="s">
-        <v>818</v>
-      </c>
-      <c r="CF1" s="1" t="s">
-        <v>820</v>
-      </c>
-      <c r="CG1" s="1" t="s">
-        <v>822</v>
-      </c>
-      <c r="CH1" s="1" t="s">
+      <c r="BY2" s="2" t="s">
+        <v>805</v>
+      </c>
+      <c r="BZ2" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="CA2" s="2" t="s">
+        <v>809</v>
+      </c>
+      <c r="CB2" s="2" t="s">
+        <v>811</v>
+      </c>
+      <c r="CC2" s="2" t="s">
+        <v>813</v>
+      </c>
+      <c r="CD2" s="2" t="s">
         <v>824</v>
       </c>
-      <c r="CI1" s="1" t="s">
+      <c r="CE2" s="2" t="s">
         <v>826</v>
       </c>
-      <c r="CJ1" s="1" t="s">
+      <c r="CF2" s="2" t="s">
         <v>828</v>
       </c>
-      <c r="CK1" s="1" t="s">
+      <c r="CG2" s="2" t="s">
         <v>830</v>
       </c>
-      <c r="CL1" s="1" t="s">
+      <c r="CH2" s="2" t="s">
         <v>832</v>
       </c>
-      <c r="CM1" s="1" t="s">
+      <c r="CI2" s="2" t="s">
         <v>834</v>
       </c>
-      <c r="CN1" s="1" t="s">
+      <c r="CJ2" s="2" t="s">
         <v>836</v>
       </c>
-      <c r="CO1" s="1" t="s">
+      <c r="CK2" s="2" t="s">
         <v>838</v>
       </c>
-      <c r="CP1" s="1" t="s">
+      <c r="CL2" s="2" t="s">
         <v>840</v>
       </c>
-      <c r="CQ1" s="1" t="s">
+      <c r="CM2" s="2" t="s">
         <v>842</v>
       </c>
-      <c r="CR1" s="1" t="s">
+      <c r="CN2" s="2" t="s">
         <v>844</v>
       </c>
-      <c r="CS1" s="1" t="s">
+      <c r="CO2" s="2" t="s">
         <v>846</v>
       </c>
-      <c r="CT1" s="1" t="s">
+      <c r="CP2" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="CU1" s="1" t="s">
+      <c r="CQ2" s="2" t="s">
         <v>850</v>
       </c>
-      <c r="CV1" s="1" t="s">
+      <c r="CR2" s="2" t="s">
         <v>852</v>
       </c>
-      <c r="CW1" s="1" t="s">
+      <c r="CS2" s="2" t="s">
         <v>854</v>
       </c>
-      <c r="CX1" s="1" t="s">
+      <c r="CT2" s="2" t="s">
         <v>856</v>
       </c>
-      <c r="CY1" s="1" t="s">
+      <c r="CU2" s="2" t="s">
         <v>858</v>
       </c>
-      <c r="CZ1" s="1" t="s">
+      <c r="CV2" s="2" t="s">
         <v>860</v>
       </c>
-      <c r="DA1" s="1" t="s">
+      <c r="CW2" s="2" t="s">
         <v>862</v>
       </c>
-      <c r="DB1" s="1" t="s">
+      <c r="CX2" s="2" t="s">
         <v>864</v>
       </c>
-      <c r="DC1" s="1" t="s">
+      <c r="CY2" s="2" t="s">
         <v>866</v>
       </c>
-      <c r="DD1" s="1" t="s">
+      <c r="CZ2" s="2" t="s">
         <v>868</v>
       </c>
-      <c r="DE1" s="1" t="s">
+      <c r="DA2" s="2" t="s">
         <v>870</v>
       </c>
-      <c r="DF1" s="1" t="s">
+      <c r="DB2" s="2" t="s">
         <v>872</v>
       </c>
-      <c r="DG1" s="1" t="s">
+      <c r="DC2" s="2" t="s">
         <v>874</v>
       </c>
-      <c r="DH1" s="1" t="s">
+      <c r="DD2" s="2" t="s">
         <v>876</v>
       </c>
-      <c r="DI1" s="1" t="s">
+      <c r="DE2" s="2" t="s">
         <v>878</v>
       </c>
-    </row>
-    <row r="2" spans="1:113" ht="150" customHeight="1">
-      <c r="A2" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="S2" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="T2" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="U2" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="V2" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="W2" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="X2" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="Y2" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="Z2" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="AA2" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="AB2" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="AC2" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="AD2" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="AE2" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="AF2" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="AG2" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="AH2" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="AI2" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="AJ2" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="AK2" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="AL2" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="AM2" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="AN2" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="AO2" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="AP2" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="AQ2" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="AR2" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="AS2" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="AT2" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="AU2" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="AV2" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="AW2" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="AX2" s="2" t="s">
-        <v>727</v>
-      </c>
-      <c r="AY2" s="2" t="s">
-        <v>729</v>
-      </c>
-      <c r="AZ2" s="2" t="s">
-        <v>731</v>
-      </c>
-      <c r="BA2" s="2" t="s">
-        <v>733</v>
-      </c>
-      <c r="BB2" s="2" t="s">
-        <v>735</v>
-      </c>
-      <c r="BC2" s="2" t="s">
-        <v>737</v>
-      </c>
-      <c r="BD2" s="2" t="s">
-        <v>739</v>
-      </c>
-      <c r="BE2" s="2" t="s">
-        <v>741</v>
-      </c>
-      <c r="BF2" s="2" t="s">
-        <v>743</v>
-      </c>
-      <c r="BG2" s="2" t="s">
-        <v>751</v>
-      </c>
-      <c r="BH2" s="2" t="s">
-        <v>759</v>
-      </c>
-      <c r="BI2" s="2" t="s">
-        <v>761</v>
-      </c>
-      <c r="BJ2" s="2" t="s">
-        <v>763</v>
-      </c>
-      <c r="BK2" s="2" t="s">
-        <v>765</v>
-      </c>
-      <c r="BL2" s="2" t="s">
-        <v>767</v>
-      </c>
-      <c r="BM2" s="2" t="s">
-        <v>769</v>
-      </c>
-      <c r="BN2" s="2" t="s">
-        <v>771</v>
-      </c>
-      <c r="BO2" s="2" t="s">
-        <v>778</v>
-      </c>
-      <c r="BP2" s="2" t="s">
-        <v>780</v>
-      </c>
-      <c r="BQ2" s="2" t="s">
-        <v>782</v>
-      </c>
-      <c r="BR2" s="2" t="s">
-        <v>784</v>
-      </c>
-      <c r="BS2" s="2" t="s">
-        <v>786</v>
-      </c>
-      <c r="BT2" s="2" t="s">
-        <v>788</v>
-      </c>
-      <c r="BU2" s="2" t="s">
-        <v>790</v>
-      </c>
-      <c r="BV2" s="2" t="s">
-        <v>792</v>
-      </c>
-      <c r="BW2" s="2" t="s">
-        <v>794</v>
-      </c>
-      <c r="BX2" s="2" t="s">
-        <v>796</v>
-      </c>
-      <c r="BY2" s="2" t="s">
-        <v>798</v>
-      </c>
-      <c r="BZ2" s="2" t="s">
-        <v>800</v>
-      </c>
-      <c r="CA2" s="2" t="s">
-        <v>802</v>
-      </c>
-      <c r="CB2" s="2" t="s">
-        <v>804</v>
-      </c>
-      <c r="CC2" s="2" t="s">
-        <v>815</v>
-      </c>
-      <c r="CD2" s="2" t="s">
-        <v>817</v>
-      </c>
-      <c r="CE2" s="2" t="s">
-        <v>819</v>
-      </c>
-      <c r="CF2" s="2" t="s">
-        <v>821</v>
-      </c>
-      <c r="CG2" s="2" t="s">
-        <v>823</v>
-      </c>
-      <c r="CH2" s="2" t="s">
-        <v>825</v>
-      </c>
-      <c r="CI2" s="2" t="s">
-        <v>827</v>
-      </c>
-      <c r="CJ2" s="2" t="s">
-        <v>829</v>
-      </c>
-      <c r="CK2" s="2" t="s">
-        <v>831</v>
-      </c>
-      <c r="CL2" s="2" t="s">
-        <v>833</v>
-      </c>
-      <c r="CM2" s="2" t="s">
-        <v>835</v>
-      </c>
-      <c r="CN2" s="2" t="s">
-        <v>837</v>
-      </c>
-      <c r="CO2" s="2" t="s">
-        <v>839</v>
-      </c>
-      <c r="CP2" s="2" t="s">
-        <v>841</v>
-      </c>
-      <c r="CQ2" s="2" t="s">
-        <v>843</v>
-      </c>
-      <c r="CR2" s="2" t="s">
-        <v>845</v>
-      </c>
-      <c r="CS2" s="2" t="s">
-        <v>847</v>
-      </c>
-      <c r="CT2" s="2" t="s">
-        <v>849</v>
-      </c>
-      <c r="CU2" s="2" t="s">
-        <v>851</v>
-      </c>
-      <c r="CV2" s="2" t="s">
-        <v>853</v>
-      </c>
-      <c r="CW2" s="2" t="s">
-        <v>855</v>
-      </c>
-      <c r="CX2" s="2" t="s">
-        <v>857</v>
-      </c>
-      <c r="CY2" s="2" t="s">
-        <v>859</v>
-      </c>
-      <c r="CZ2" s="2" t="s">
-        <v>861</v>
-      </c>
-      <c r="DA2" s="2" t="s">
-        <v>863</v>
-      </c>
-      <c r="DB2" s="2" t="s">
-        <v>865</v>
-      </c>
-      <c r="DC2" s="2" t="s">
-        <v>867</v>
-      </c>
-      <c r="DD2" s="2" t="s">
-        <v>869</v>
-      </c>
-      <c r="DE2" s="2" t="s">
-        <v>871</v>
-      </c>
       <c r="DF2" s="2" t="s">
-        <v>873</v>
+        <v>880</v>
       </c>
       <c r="DG2" s="2" t="s">
-        <v>875</v>
+        <v>882</v>
       </c>
       <c r="DH2" s="2" t="s">
-        <v>877</v>
+        <v>884</v>
       </c>
       <c r="DI2" s="2" t="s">
-        <v>879</v>
+        <v>886</v>
+      </c>
+      <c r="DJ2" s="2" t="s">
+        <v>888</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="10">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F101">
       <formula1>trophiclevel</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G101">
       <formula1>observedbioticrelationship</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I3:I101">
       <formula1>relationshiptooxygen</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P3:P101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q3:Q101">
       <formula1>soiltype</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AC3:AC101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD3:AD101">
       <formula1>sequencequalitycheck</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX3:AX101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AY3:AY101">
       <formula1>geographiclocationcountryandorsea</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BG3:BG101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BH3:BH101">
       <formula1>soilhorizon</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BH3:BH101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BI3:BI101">
       <formula1>drainageclassification</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BO3:BO101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BP3:BP101">
       <formula1>profileposition</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CC3:CC101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CD3:CD101">
       <formula1>historytillage</formula1>
     </dataValidation>
   </dataValidations>
@@ -4922,1761 +4963,1786 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="E1:CC289"/>
+  <dimension ref="F1:CD294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="5:81">
-      <c r="E1" t="s">
-        <v>270</v>
-      </c>
+    <row r="1" spans="6:82">
       <c r="F1" t="s">
+        <v>274</v>
+      </c>
+      <c r="G1" t="s">
+        <v>306</v>
+      </c>
+      <c r="I1" t="s">
+        <v>315</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>338</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>396</v>
+      </c>
+      <c r="AY1" t="s">
+        <v>441</v>
+      </c>
+      <c r="BH1" t="s">
+        <v>753</v>
+      </c>
+      <c r="BI1" t="s">
+        <v>761</v>
+      </c>
+      <c r="BP1" t="s">
+        <v>781</v>
+      </c>
+      <c r="CD1" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="2" spans="6:82">
+      <c r="F2" t="s">
+        <v>275</v>
+      </c>
+      <c r="G2" t="s">
+        <v>307</v>
+      </c>
+      <c r="I2" t="s">
+        <v>316</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>339</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>397</v>
+      </c>
+      <c r="AY2" t="s">
+        <v>442</v>
+      </c>
+      <c r="BH2" t="s">
+        <v>754</v>
+      </c>
+      <c r="BI2" t="s">
+        <v>762</v>
+      </c>
+      <c r="BP2" t="s">
+        <v>782</v>
+      </c>
+      <c r="CD2" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="3" spans="6:82">
+      <c r="F3" t="s">
+        <v>276</v>
+      </c>
+      <c r="G3" t="s">
+        <v>308</v>
+      </c>
+      <c r="I3" t="s">
+        <v>317</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>340</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>398</v>
+      </c>
+      <c r="AY3" t="s">
+        <v>443</v>
+      </c>
+      <c r="BH3" t="s">
+        <v>755</v>
+      </c>
+      <c r="BI3" t="s">
+        <v>763</v>
+      </c>
+      <c r="BP3" t="s">
+        <v>783</v>
+      </c>
+      <c r="CD3" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="4" spans="6:82">
+      <c r="F4" t="s">
+        <v>277</v>
+      </c>
+      <c r="G4" t="s">
+        <v>309</v>
+      </c>
+      <c r="I4" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>341</v>
+      </c>
+      <c r="AY4" t="s">
+        <v>444</v>
+      </c>
+      <c r="BH4" t="s">
+        <v>756</v>
+      </c>
+      <c r="BI4" t="s">
+        <v>764</v>
+      </c>
+      <c r="BP4" t="s">
+        <v>784</v>
+      </c>
+      <c r="CD4" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="5" spans="6:82">
+      <c r="F5" t="s">
+        <v>278</v>
+      </c>
+      <c r="G5" t="s">
+        <v>310</v>
+      </c>
+      <c r="I5" t="s">
+        <v>319</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>342</v>
+      </c>
+      <c r="AY5" t="s">
+        <v>445</v>
+      </c>
+      <c r="BH5" t="s">
+        <v>757</v>
+      </c>
+      <c r="BI5" t="s">
+        <v>765</v>
+      </c>
+      <c r="BP5" t="s">
+        <v>785</v>
+      </c>
+      <c r="CD5" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="6" spans="6:82">
+      <c r="F6" t="s">
+        <v>279</v>
+      </c>
+      <c r="I6" t="s">
+        <v>320</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>343</v>
+      </c>
+      <c r="AY6" t="s">
+        <v>446</v>
+      </c>
+      <c r="BH6" t="s">
+        <v>758</v>
+      </c>
+      <c r="BI6" t="s">
+        <v>766</v>
+      </c>
+      <c r="CD6" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="7" spans="6:82">
+      <c r="F7" t="s">
+        <v>280</v>
+      </c>
+      <c r="I7" t="s">
+        <v>321</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>344</v>
+      </c>
+      <c r="AY7" t="s">
+        <v>447</v>
+      </c>
+      <c r="CD7" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="8" spans="6:82">
+      <c r="F8" t="s">
+        <v>281</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>345</v>
+      </c>
+      <c r="AY8" t="s">
+        <v>448</v>
+      </c>
+      <c r="CD8" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="9" spans="6:82">
+      <c r="F9" t="s">
+        <v>282</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>346</v>
+      </c>
+      <c r="AY9" t="s">
+        <v>449</v>
+      </c>
+      <c r="CD9" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="10" spans="6:82">
+      <c r="F10" t="s">
+        <v>283</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>347</v>
+      </c>
+      <c r="AY10" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="11" spans="6:82">
+      <c r="F11" t="s">
+        <v>284</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>348</v>
+      </c>
+      <c r="AY11" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="12" spans="6:82">
+      <c r="F12" t="s">
+        <v>285</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>349</v>
+      </c>
+      <c r="AY12" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="13" spans="6:82">
+      <c r="F13" t="s">
+        <v>286</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>350</v>
+      </c>
+      <c r="AY13" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="14" spans="6:82">
+      <c r="F14" t="s">
+        <v>287</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>351</v>
+      </c>
+      <c r="AY14" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="15" spans="6:82">
+      <c r="F15" t="s">
+        <v>288</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>352</v>
+      </c>
+      <c r="AY15" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="16" spans="6:82">
+      <c r="F16" t="s">
+        <v>289</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>353</v>
+      </c>
+      <c r="AY16" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="17" spans="6:51">
+      <c r="F17" t="s">
+        <v>290</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>354</v>
+      </c>
+      <c r="AY17" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="18" spans="6:51">
+      <c r="F18" t="s">
+        <v>291</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>355</v>
+      </c>
+      <c r="AY18" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="19" spans="6:51">
+      <c r="F19" t="s">
+        <v>292</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>356</v>
+      </c>
+      <c r="AY19" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="20" spans="6:51">
+      <c r="F20" t="s">
+        <v>293</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>357</v>
+      </c>
+      <c r="AY20" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="21" spans="6:51">
+      <c r="F21" t="s">
+        <v>294</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>358</v>
+      </c>
+      <c r="AY21" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="22" spans="6:51">
+      <c r="F22" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>359</v>
+      </c>
+      <c r="AY22" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="23" spans="6:51">
+      <c r="F23" t="s">
+        <v>296</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>360</v>
+      </c>
+      <c r="AY23" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="24" spans="6:51">
+      <c r="F24" t="s">
+        <v>297</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>361</v>
+      </c>
+      <c r="AY24" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="25" spans="6:51">
+      <c r="F25" t="s">
+        <v>298</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>362</v>
+      </c>
+      <c r="AY25" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="26" spans="6:51">
+      <c r="F26" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>363</v>
+      </c>
+      <c r="AY26" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="27" spans="6:51">
+      <c r="F27" t="s">
+        <v>300</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>364</v>
+      </c>
+      <c r="AY27" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="28" spans="6:51">
+      <c r="F28" t="s">
+        <v>301</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>365</v>
+      </c>
+      <c r="AY28" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="29" spans="6:51">
+      <c r="F29" t="s">
         <v>302</v>
       </c>
-      <c r="H1" t="s">
-        <v>311</v>
-      </c>
-      <c r="P1" t="s">
-        <v>334</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>392</v>
-      </c>
-      <c r="AX1" t="s">
-        <v>437</v>
-      </c>
-      <c r="BG1" t="s">
-        <v>744</v>
-      </c>
-      <c r="BH1" t="s">
-        <v>752</v>
-      </c>
-      <c r="BO1" t="s">
-        <v>772</v>
-      </c>
-      <c r="CC1" t="s">
-        <v>805</v>
-      </c>
-    </row>
-    <row r="2" spans="5:81">
-      <c r="E2" t="s">
-        <v>271</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="Q29" t="s">
+        <v>366</v>
+      </c>
+      <c r="AY29" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="30" spans="6:51">
+      <c r="F30" t="s">
         <v>303</v>
       </c>
-      <c r="H2" t="s">
-        <v>312</v>
-      </c>
-      <c r="P2" t="s">
-        <v>335</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>393</v>
-      </c>
-      <c r="AX2" t="s">
-        <v>438</v>
-      </c>
-      <c r="BG2" t="s">
-        <v>745</v>
-      </c>
-      <c r="BH2" t="s">
-        <v>753</v>
-      </c>
-      <c r="BO2" t="s">
-        <v>773</v>
-      </c>
-      <c r="CC2" t="s">
-        <v>806</v>
-      </c>
-    </row>
-    <row r="3" spans="5:81">
-      <c r="E3" t="s">
-        <v>272</v>
-      </c>
-      <c r="F3" t="s">
-        <v>304</v>
-      </c>
-      <c r="H3" t="s">
-        <v>313</v>
-      </c>
-      <c r="P3" t="s">
-        <v>336</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>394</v>
-      </c>
-      <c r="AX3" t="s">
-        <v>439</v>
-      </c>
-      <c r="BG3" t="s">
-        <v>746</v>
-      </c>
-      <c r="BH3" t="s">
-        <v>754</v>
-      </c>
-      <c r="BO3" t="s">
-        <v>774</v>
-      </c>
-      <c r="CC3" t="s">
-        <v>807</v>
-      </c>
-    </row>
-    <row r="4" spans="5:81">
-      <c r="E4" t="s">
-        <v>273</v>
-      </c>
-      <c r="F4" t="s">
-        <v>305</v>
-      </c>
-      <c r="H4" t="s">
-        <v>314</v>
-      </c>
-      <c r="P4" t="s">
-        <v>337</v>
-      </c>
-      <c r="AX4" t="s">
-        <v>440</v>
-      </c>
-      <c r="BG4" t="s">
-        <v>747</v>
-      </c>
-      <c r="BH4" t="s">
-        <v>755</v>
-      </c>
-      <c r="BO4" t="s">
-        <v>775</v>
-      </c>
-      <c r="CC4" t="s">
-        <v>808</v>
-      </c>
-    </row>
-    <row r="5" spans="5:81">
-      <c r="E5" t="s">
-        <v>274</v>
-      </c>
-      <c r="F5" t="s">
-        <v>306</v>
-      </c>
-      <c r="H5" t="s">
-        <v>315</v>
-      </c>
-      <c r="P5" t="s">
-        <v>338</v>
-      </c>
-      <c r="AX5" t="s">
-        <v>441</v>
-      </c>
-      <c r="BG5" t="s">
-        <v>748</v>
-      </c>
-      <c r="BH5" t="s">
-        <v>756</v>
-      </c>
-      <c r="BO5" t="s">
-        <v>776</v>
-      </c>
-      <c r="CC5" t="s">
-        <v>809</v>
-      </c>
-    </row>
-    <row r="6" spans="5:81">
-      <c r="E6" t="s">
-        <v>275</v>
-      </c>
-      <c r="H6" t="s">
-        <v>316</v>
-      </c>
-      <c r="P6" t="s">
-        <v>339</v>
-      </c>
-      <c r="AX6" t="s">
-        <v>442</v>
-      </c>
-      <c r="BG6" t="s">
-        <v>749</v>
-      </c>
-      <c r="BH6" t="s">
-        <v>757</v>
-      </c>
-      <c r="CC6" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="7" spans="5:81">
-      <c r="E7" t="s">
-        <v>276</v>
-      </c>
-      <c r="H7" t="s">
-        <v>317</v>
-      </c>
-      <c r="P7" t="s">
-        <v>340</v>
-      </c>
-      <c r="AX7" t="s">
-        <v>443</v>
-      </c>
-      <c r="CC7" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="8" spans="5:81">
-      <c r="E8" t="s">
-        <v>277</v>
-      </c>
-      <c r="P8" t="s">
-        <v>341</v>
-      </c>
-      <c r="AX8" t="s">
-        <v>444</v>
-      </c>
-      <c r="CC8" t="s">
-        <v>812</v>
-      </c>
-    </row>
-    <row r="9" spans="5:81">
-      <c r="E9" t="s">
-        <v>278</v>
-      </c>
-      <c r="P9" t="s">
-        <v>342</v>
-      </c>
-      <c r="AX9" t="s">
-        <v>445</v>
-      </c>
-      <c r="CC9" t="s">
-        <v>813</v>
-      </c>
-    </row>
-    <row r="10" spans="5:81">
-      <c r="E10" t="s">
-        <v>279</v>
-      </c>
-      <c r="P10" t="s">
-        <v>343</v>
-      </c>
-      <c r="AX10" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="11" spans="5:81">
-      <c r="E11" t="s">
-        <v>280</v>
-      </c>
-      <c r="P11" t="s">
-        <v>344</v>
-      </c>
-      <c r="AX11" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="12" spans="5:81">
-      <c r="E12" t="s">
-        <v>281</v>
-      </c>
-      <c r="P12" t="s">
-        <v>345</v>
-      </c>
-      <c r="AX12" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="13" spans="5:81">
-      <c r="E13" t="s">
-        <v>282</v>
-      </c>
-      <c r="P13" t="s">
-        <v>346</v>
-      </c>
-      <c r="AX13" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="14" spans="5:81">
-      <c r="E14" t="s">
-        <v>283</v>
-      </c>
-      <c r="P14" t="s">
-        <v>347</v>
-      </c>
-      <c r="AX14" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="15" spans="5:81">
-      <c r="E15" t="s">
-        <v>284</v>
-      </c>
-      <c r="P15" t="s">
-        <v>348</v>
-      </c>
-      <c r="AX15" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="16" spans="5:81">
-      <c r="E16" t="s">
-        <v>285</v>
-      </c>
-      <c r="P16" t="s">
-        <v>349</v>
-      </c>
-      <c r="AX16" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="17" spans="5:50">
-      <c r="E17" t="s">
-        <v>286</v>
-      </c>
-      <c r="P17" t="s">
-        <v>350</v>
-      </c>
-      <c r="AX17" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="18" spans="5:50">
-      <c r="E18" t="s">
-        <v>287</v>
-      </c>
-      <c r="P18" t="s">
-        <v>351</v>
-      </c>
-      <c r="AX18" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="19" spans="5:50">
-      <c r="E19" t="s">
-        <v>288</v>
-      </c>
-      <c r="P19" t="s">
-        <v>352</v>
-      </c>
-      <c r="AX19" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="20" spans="5:50">
-      <c r="E20" t="s">
-        <v>289</v>
-      </c>
-      <c r="P20" t="s">
-        <v>353</v>
-      </c>
-      <c r="AX20" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="21" spans="5:50">
-      <c r="E21" t="s">
-        <v>290</v>
-      </c>
-      <c r="P21" t="s">
-        <v>354</v>
-      </c>
-      <c r="AX21" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="22" spans="5:50">
-      <c r="E22" t="s">
-        <v>291</v>
-      </c>
-      <c r="P22" t="s">
-        <v>355</v>
-      </c>
-      <c r="AX22" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="23" spans="5:50">
-      <c r="E23" t="s">
-        <v>292</v>
-      </c>
-      <c r="P23" t="s">
-        <v>356</v>
-      </c>
-      <c r="AX23" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="24" spans="5:50">
-      <c r="E24" t="s">
-        <v>293</v>
-      </c>
-      <c r="P24" t="s">
-        <v>357</v>
-      </c>
-      <c r="AX24" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="25" spans="5:50">
-      <c r="E25" t="s">
-        <v>294</v>
-      </c>
-      <c r="P25" t="s">
-        <v>358</v>
-      </c>
-      <c r="AX25" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="26" spans="5:50">
-      <c r="E26" t="s">
-        <v>295</v>
-      </c>
-      <c r="P26" t="s">
-        <v>359</v>
-      </c>
-      <c r="AX26" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="27" spans="5:50">
-      <c r="E27" t="s">
-        <v>296</v>
-      </c>
-      <c r="P27" t="s">
-        <v>360</v>
-      </c>
-      <c r="AX27" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="28" spans="5:50">
-      <c r="E28" t="s">
-        <v>297</v>
-      </c>
-      <c r="P28" t="s">
-        <v>361</v>
-      </c>
-      <c r="AX28" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="29" spans="5:50">
-      <c r="E29" t="s">
-        <v>298</v>
-      </c>
-      <c r="P29" t="s">
-        <v>362</v>
-      </c>
-      <c r="AX29" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="30" spans="5:50">
-      <c r="E30" t="s">
-        <v>299</v>
-      </c>
-      <c r="P30" t="s">
-        <v>363</v>
-      </c>
-      <c r="AX30" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="31" spans="5:50">
-      <c r="P31" t="s">
-        <v>364</v>
-      </c>
-      <c r="AX31" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="32" spans="5:50">
-      <c r="P32" t="s">
-        <v>365</v>
-      </c>
-      <c r="AX32" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="33" spans="50:50">
-      <c r="AX33" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="34" spans="50:50">
-      <c r="AX34" t="s">
+      <c r="Q30" t="s">
+        <v>367</v>
+      </c>
+      <c r="AY30" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="35" spans="50:50">
-      <c r="AX35" t="s">
+    <row r="31" spans="6:51">
+      <c r="Q31" t="s">
+        <v>368</v>
+      </c>
+      <c r="AY31" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="36" spans="50:50">
-      <c r="AX36" t="s">
+    <row r="32" spans="6:51">
+      <c r="Q32" t="s">
+        <v>369</v>
+      </c>
+      <c r="AY32" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="37" spans="50:50">
-      <c r="AX37" t="s">
+    <row r="33" spans="51:51">
+      <c r="AY33" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="38" spans="50:50">
-      <c r="AX38" t="s">
+    <row r="34" spans="51:51">
+      <c r="AY34" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="39" spans="50:50">
-      <c r="AX39" t="s">
+    <row r="35" spans="51:51">
+      <c r="AY35" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="40" spans="50:50">
-      <c r="AX40" t="s">
+    <row r="36" spans="51:51">
+      <c r="AY36" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="41" spans="50:50">
-      <c r="AX41" t="s">
+    <row r="37" spans="51:51">
+      <c r="AY37" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="42" spans="50:50">
-      <c r="AX42" t="s">
+    <row r="38" spans="51:51">
+      <c r="AY38" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="43" spans="50:50">
-      <c r="AX43" t="s">
+    <row r="39" spans="51:51">
+      <c r="AY39" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="44" spans="50:50">
-      <c r="AX44" t="s">
+    <row r="40" spans="51:51">
+      <c r="AY40" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="45" spans="50:50">
-      <c r="AX45" t="s">
+    <row r="41" spans="51:51">
+      <c r="AY41" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="46" spans="50:50">
-      <c r="AX46" t="s">
+    <row r="42" spans="51:51">
+      <c r="AY42" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="47" spans="50:50">
-      <c r="AX47" t="s">
+    <row r="43" spans="51:51">
+      <c r="AY43" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="48" spans="50:50">
-      <c r="AX48" t="s">
+    <row r="44" spans="51:51">
+      <c r="AY44" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="49" spans="50:50">
-      <c r="AX49" t="s">
+    <row r="45" spans="51:51">
+      <c r="AY45" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="50" spans="50:50">
-      <c r="AX50" t="s">
+    <row r="46" spans="51:51">
+      <c r="AY46" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="51" spans="50:50">
-      <c r="AX51" t="s">
+    <row r="47" spans="51:51">
+      <c r="AY47" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="52" spans="50:50">
-      <c r="AX52" t="s">
+    <row r="48" spans="51:51">
+      <c r="AY48" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="53" spans="50:50">
-      <c r="AX53" t="s">
+    <row r="49" spans="51:51">
+      <c r="AY49" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="54" spans="50:50">
-      <c r="AX54" t="s">
+    <row r="50" spans="51:51">
+      <c r="AY50" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="55" spans="50:50">
-      <c r="AX55" t="s">
+    <row r="51" spans="51:51">
+      <c r="AY51" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="56" spans="50:50">
-      <c r="AX56" t="s">
+    <row r="52" spans="51:51">
+      <c r="AY52" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="57" spans="50:50">
-      <c r="AX57" t="s">
+    <row r="53" spans="51:51">
+      <c r="AY53" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="58" spans="50:50">
-      <c r="AX58" t="s">
+    <row r="54" spans="51:51">
+      <c r="AY54" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="59" spans="50:50">
-      <c r="AX59" t="s">
+    <row r="55" spans="51:51">
+      <c r="AY55" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="60" spans="50:50">
-      <c r="AX60" t="s">
+    <row r="56" spans="51:51">
+      <c r="AY56" t="s">
         <v>496</v>
       </c>
     </row>
-    <row r="61" spans="50:50">
-      <c r="AX61" t="s">
+    <row r="57" spans="51:51">
+      <c r="AY57" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="62" spans="50:50">
-      <c r="AX62" t="s">
+    <row r="58" spans="51:51">
+      <c r="AY58" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="63" spans="50:50">
-      <c r="AX63" t="s">
+    <row r="59" spans="51:51">
+      <c r="AY59" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="64" spans="50:50">
-      <c r="AX64" t="s">
+    <row r="60" spans="51:51">
+      <c r="AY60" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="65" spans="50:50">
-      <c r="AX65" t="s">
+    <row r="61" spans="51:51">
+      <c r="AY61" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="66" spans="50:50">
-      <c r="AX66" t="s">
+    <row r="62" spans="51:51">
+      <c r="AY62" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="67" spans="50:50">
-      <c r="AX67" t="s">
+    <row r="63" spans="51:51">
+      <c r="AY63" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="68" spans="50:50">
-      <c r="AX68" t="s">
+    <row r="64" spans="51:51">
+      <c r="AY64" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="69" spans="50:50">
-      <c r="AX69" t="s">
+    <row r="65" spans="51:51">
+      <c r="AY65" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="70" spans="50:50">
-      <c r="AX70" t="s">
+    <row r="66" spans="51:51">
+      <c r="AY66" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="71" spans="50:50">
-      <c r="AX71" t="s">
+    <row r="67" spans="51:51">
+      <c r="AY67" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="72" spans="50:50">
-      <c r="AX72" t="s">
+    <row r="68" spans="51:51">
+      <c r="AY68" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="73" spans="50:50">
-      <c r="AX73" t="s">
+    <row r="69" spans="51:51">
+      <c r="AY69" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="74" spans="50:50">
-      <c r="AX74" t="s">
+    <row r="70" spans="51:51">
+      <c r="AY70" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="75" spans="50:50">
-      <c r="AX75" t="s">
+    <row r="71" spans="51:51">
+      <c r="AY71" t="s">
         <v>511</v>
       </c>
     </row>
-    <row r="76" spans="50:50">
-      <c r="AX76" t="s">
+    <row r="72" spans="51:51">
+      <c r="AY72" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="77" spans="50:50">
-      <c r="AX77" t="s">
+    <row r="73" spans="51:51">
+      <c r="AY73" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="78" spans="50:50">
-      <c r="AX78" t="s">
+    <row r="74" spans="51:51">
+      <c r="AY74" t="s">
         <v>514</v>
       </c>
     </row>
-    <row r="79" spans="50:50">
-      <c r="AX79" t="s">
+    <row r="75" spans="51:51">
+      <c r="AY75" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="80" spans="50:50">
-      <c r="AX80" t="s">
+    <row r="76" spans="51:51">
+      <c r="AY76" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="81" spans="50:50">
-      <c r="AX81" t="s">
+    <row r="77" spans="51:51">
+      <c r="AY77" t="s">
         <v>517</v>
       </c>
     </row>
-    <row r="82" spans="50:50">
-      <c r="AX82" t="s">
+    <row r="78" spans="51:51">
+      <c r="AY78" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="83" spans="50:50">
-      <c r="AX83" t="s">
+    <row r="79" spans="51:51">
+      <c r="AY79" t="s">
         <v>519</v>
       </c>
     </row>
-    <row r="84" spans="50:50">
-      <c r="AX84" t="s">
+    <row r="80" spans="51:51">
+      <c r="AY80" t="s">
         <v>520</v>
       </c>
     </row>
-    <row r="85" spans="50:50">
-      <c r="AX85" t="s">
+    <row r="81" spans="51:51">
+      <c r="AY81" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="86" spans="50:50">
-      <c r="AX86" t="s">
+    <row r="82" spans="51:51">
+      <c r="AY82" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="87" spans="50:50">
-      <c r="AX87" t="s">
+    <row r="83" spans="51:51">
+      <c r="AY83" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="88" spans="50:50">
-      <c r="AX88" t="s">
+    <row r="84" spans="51:51">
+      <c r="AY84" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="89" spans="50:50">
-      <c r="AX89" t="s">
+    <row r="85" spans="51:51">
+      <c r="AY85" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="90" spans="50:50">
-      <c r="AX90" t="s">
+    <row r="86" spans="51:51">
+      <c r="AY86" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="91" spans="50:50">
-      <c r="AX91" t="s">
+    <row r="87" spans="51:51">
+      <c r="AY87" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="92" spans="50:50">
-      <c r="AX92" t="s">
+    <row r="88" spans="51:51">
+      <c r="AY88" t="s">
         <v>528</v>
       </c>
     </row>
-    <row r="93" spans="50:50">
-      <c r="AX93" t="s">
+    <row r="89" spans="51:51">
+      <c r="AY89" t="s">
         <v>529</v>
       </c>
     </row>
-    <row r="94" spans="50:50">
-      <c r="AX94" t="s">
+    <row r="90" spans="51:51">
+      <c r="AY90" t="s">
         <v>530</v>
       </c>
     </row>
-    <row r="95" spans="50:50">
-      <c r="AX95" t="s">
+    <row r="91" spans="51:51">
+      <c r="AY91" t="s">
         <v>531</v>
       </c>
     </row>
-    <row r="96" spans="50:50">
-      <c r="AX96" t="s">
+    <row r="92" spans="51:51">
+      <c r="AY92" t="s">
         <v>532</v>
       </c>
     </row>
-    <row r="97" spans="50:50">
-      <c r="AX97" t="s">
+    <row r="93" spans="51:51">
+      <c r="AY93" t="s">
         <v>533</v>
       </c>
     </row>
-    <row r="98" spans="50:50">
-      <c r="AX98" t="s">
+    <row r="94" spans="51:51">
+      <c r="AY94" t="s">
         <v>534</v>
       </c>
     </row>
-    <row r="99" spans="50:50">
-      <c r="AX99" t="s">
+    <row r="95" spans="51:51">
+      <c r="AY95" t="s">
         <v>535</v>
       </c>
     </row>
-    <row r="100" spans="50:50">
-      <c r="AX100" t="s">
+    <row r="96" spans="51:51">
+      <c r="AY96" t="s">
         <v>536</v>
       </c>
     </row>
-    <row r="101" spans="50:50">
-      <c r="AX101" t="s">
+    <row r="97" spans="51:51">
+      <c r="AY97" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="102" spans="50:50">
-      <c r="AX102" t="s">
+    <row r="98" spans="51:51">
+      <c r="AY98" t="s">
         <v>538</v>
       </c>
     </row>
-    <row r="103" spans="50:50">
-      <c r="AX103" t="s">
+    <row r="99" spans="51:51">
+      <c r="AY99" t="s">
         <v>539</v>
       </c>
     </row>
-    <row r="104" spans="50:50">
-      <c r="AX104" t="s">
+    <row r="100" spans="51:51">
+      <c r="AY100" t="s">
         <v>540</v>
       </c>
     </row>
-    <row r="105" spans="50:50">
-      <c r="AX105" t="s">
+    <row r="101" spans="51:51">
+      <c r="AY101" t="s">
         <v>541</v>
       </c>
     </row>
-    <row r="106" spans="50:50">
-      <c r="AX106" t="s">
+    <row r="102" spans="51:51">
+      <c r="AY102" t="s">
         <v>542</v>
       </c>
     </row>
-    <row r="107" spans="50:50">
-      <c r="AX107" t="s">
+    <row r="103" spans="51:51">
+      <c r="AY103" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="108" spans="50:50">
-      <c r="AX108" t="s">
+    <row r="104" spans="51:51">
+      <c r="AY104" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="109" spans="50:50">
-      <c r="AX109" t="s">
+    <row r="105" spans="51:51">
+      <c r="AY105" t="s">
         <v>545</v>
       </c>
     </row>
-    <row r="110" spans="50:50">
-      <c r="AX110" t="s">
+    <row r="106" spans="51:51">
+      <c r="AY106" t="s">
         <v>546</v>
       </c>
     </row>
-    <row r="111" spans="50:50">
-      <c r="AX111" t="s">
+    <row r="107" spans="51:51">
+      <c r="AY107" t="s">
         <v>547</v>
       </c>
     </row>
-    <row r="112" spans="50:50">
-      <c r="AX112" t="s">
+    <row r="108" spans="51:51">
+      <c r="AY108" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="113" spans="50:50">
-      <c r="AX113" t="s">
+    <row r="109" spans="51:51">
+      <c r="AY109" t="s">
         <v>549</v>
       </c>
     </row>
-    <row r="114" spans="50:50">
-      <c r="AX114" t="s">
+    <row r="110" spans="51:51">
+      <c r="AY110" t="s">
         <v>550</v>
       </c>
     </row>
-    <row r="115" spans="50:50">
-      <c r="AX115" t="s">
+    <row r="111" spans="51:51">
+      <c r="AY111" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="116" spans="50:50">
-      <c r="AX116" t="s">
+    <row r="112" spans="51:51">
+      <c r="AY112" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="117" spans="50:50">
-      <c r="AX117" t="s">
+    <row r="113" spans="51:51">
+      <c r="AY113" t="s">
         <v>553</v>
       </c>
     </row>
-    <row r="118" spans="50:50">
-      <c r="AX118" t="s">
+    <row r="114" spans="51:51">
+      <c r="AY114" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="119" spans="50:50">
-      <c r="AX119" t="s">
+    <row r="115" spans="51:51">
+      <c r="AY115" t="s">
         <v>555</v>
       </c>
     </row>
-    <row r="120" spans="50:50">
-      <c r="AX120" t="s">
+    <row r="116" spans="51:51">
+      <c r="AY116" t="s">
         <v>556</v>
       </c>
     </row>
-    <row r="121" spans="50:50">
-      <c r="AX121" t="s">
+    <row r="117" spans="51:51">
+      <c r="AY117" t="s">
         <v>557</v>
       </c>
     </row>
-    <row r="122" spans="50:50">
-      <c r="AX122" t="s">
+    <row r="118" spans="51:51">
+      <c r="AY118" t="s">
         <v>558</v>
       </c>
     </row>
-    <row r="123" spans="50:50">
-      <c r="AX123" t="s">
+    <row r="119" spans="51:51">
+      <c r="AY119" t="s">
         <v>559</v>
       </c>
     </row>
-    <row r="124" spans="50:50">
-      <c r="AX124" t="s">
+    <row r="120" spans="51:51">
+      <c r="AY120" t="s">
         <v>560</v>
       </c>
     </row>
-    <row r="125" spans="50:50">
-      <c r="AX125" t="s">
+    <row r="121" spans="51:51">
+      <c r="AY121" t="s">
         <v>561</v>
       </c>
     </row>
-    <row r="126" spans="50:50">
-      <c r="AX126" t="s">
+    <row r="122" spans="51:51">
+      <c r="AY122" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="127" spans="50:50">
-      <c r="AX127" t="s">
+    <row r="123" spans="51:51">
+      <c r="AY123" t="s">
         <v>563</v>
       </c>
     </row>
-    <row r="128" spans="50:50">
-      <c r="AX128" t="s">
+    <row r="124" spans="51:51">
+      <c r="AY124" t="s">
         <v>564</v>
       </c>
     </row>
-    <row r="129" spans="50:50">
-      <c r="AX129" t="s">
+    <row r="125" spans="51:51">
+      <c r="AY125" t="s">
         <v>565</v>
       </c>
     </row>
-    <row r="130" spans="50:50">
-      <c r="AX130" t="s">
+    <row r="126" spans="51:51">
+      <c r="AY126" t="s">
         <v>566</v>
       </c>
     </row>
-    <row r="131" spans="50:50">
-      <c r="AX131" t="s">
+    <row r="127" spans="51:51">
+      <c r="AY127" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="132" spans="50:50">
-      <c r="AX132" t="s">
+    <row r="128" spans="51:51">
+      <c r="AY128" t="s">
         <v>568</v>
       </c>
     </row>
-    <row r="133" spans="50:50">
-      <c r="AX133" t="s">
+    <row r="129" spans="51:51">
+      <c r="AY129" t="s">
         <v>569</v>
       </c>
     </row>
-    <row r="134" spans="50:50">
-      <c r="AX134" t="s">
+    <row r="130" spans="51:51">
+      <c r="AY130" t="s">
         <v>570</v>
       </c>
     </row>
-    <row r="135" spans="50:50">
-      <c r="AX135" t="s">
+    <row r="131" spans="51:51">
+      <c r="AY131" t="s">
         <v>571</v>
       </c>
     </row>
-    <row r="136" spans="50:50">
-      <c r="AX136" t="s">
+    <row r="132" spans="51:51">
+      <c r="AY132" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="137" spans="50:50">
-      <c r="AX137" t="s">
+    <row r="133" spans="51:51">
+      <c r="AY133" t="s">
         <v>573</v>
       </c>
     </row>
-    <row r="138" spans="50:50">
-      <c r="AX138" t="s">
+    <row r="134" spans="51:51">
+      <c r="AY134" t="s">
         <v>574</v>
       </c>
     </row>
-    <row r="139" spans="50:50">
-      <c r="AX139" t="s">
+    <row r="135" spans="51:51">
+      <c r="AY135" t="s">
         <v>575</v>
       </c>
     </row>
-    <row r="140" spans="50:50">
-      <c r="AX140" t="s">
+    <row r="136" spans="51:51">
+      <c r="AY136" t="s">
         <v>576</v>
       </c>
     </row>
-    <row r="141" spans="50:50">
-      <c r="AX141" t="s">
+    <row r="137" spans="51:51">
+      <c r="AY137" t="s">
         <v>577</v>
       </c>
     </row>
-    <row r="142" spans="50:50">
-      <c r="AX142" t="s">
+    <row r="138" spans="51:51">
+      <c r="AY138" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="143" spans="50:50">
-      <c r="AX143" t="s">
+    <row r="139" spans="51:51">
+      <c r="AY139" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="144" spans="50:50">
-      <c r="AX144" t="s">
+    <row r="140" spans="51:51">
+      <c r="AY140" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="145" spans="50:50">
-      <c r="AX145" t="s">
+    <row r="141" spans="51:51">
+      <c r="AY141" t="s">
         <v>581</v>
       </c>
     </row>
-    <row r="146" spans="50:50">
-      <c r="AX146" t="s">
+    <row r="142" spans="51:51">
+      <c r="AY142" t="s">
         <v>582</v>
       </c>
     </row>
-    <row r="147" spans="50:50">
-      <c r="AX147" t="s">
+    <row r="143" spans="51:51">
+      <c r="AY143" t="s">
         <v>583</v>
       </c>
     </row>
-    <row r="148" spans="50:50">
-      <c r="AX148" t="s">
+    <row r="144" spans="51:51">
+      <c r="AY144" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="149" spans="50:50">
-      <c r="AX149" t="s">
+    <row r="145" spans="51:51">
+      <c r="AY145" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="150" spans="50:50">
-      <c r="AX150" t="s">
+    <row r="146" spans="51:51">
+      <c r="AY146" t="s">
         <v>586</v>
       </c>
     </row>
-    <row r="151" spans="50:50">
-      <c r="AX151" t="s">
+    <row r="147" spans="51:51">
+      <c r="AY147" t="s">
         <v>587</v>
       </c>
     </row>
-    <row r="152" spans="50:50">
-      <c r="AX152" t="s">
+    <row r="148" spans="51:51">
+      <c r="AY148" t="s">
         <v>588</v>
       </c>
     </row>
-    <row r="153" spans="50:50">
-      <c r="AX153" t="s">
+    <row r="149" spans="51:51">
+      <c r="AY149" t="s">
         <v>589</v>
       </c>
     </row>
-    <row r="154" spans="50:50">
-      <c r="AX154" t="s">
+    <row r="150" spans="51:51">
+      <c r="AY150" t="s">
         <v>590</v>
       </c>
     </row>
-    <row r="155" spans="50:50">
-      <c r="AX155" t="s">
+    <row r="151" spans="51:51">
+      <c r="AY151" t="s">
         <v>591</v>
       </c>
     </row>
-    <row r="156" spans="50:50">
-      <c r="AX156" t="s">
+    <row r="152" spans="51:51">
+      <c r="AY152" t="s">
         <v>592</v>
       </c>
     </row>
-    <row r="157" spans="50:50">
-      <c r="AX157" t="s">
+    <row r="153" spans="51:51">
+      <c r="AY153" t="s">
         <v>593</v>
       </c>
     </row>
-    <row r="158" spans="50:50">
-      <c r="AX158" t="s">
+    <row r="154" spans="51:51">
+      <c r="AY154" t="s">
         <v>594</v>
       </c>
     </row>
-    <row r="159" spans="50:50">
-      <c r="AX159" t="s">
+    <row r="155" spans="51:51">
+      <c r="AY155" t="s">
         <v>595</v>
       </c>
     </row>
-    <row r="160" spans="50:50">
-      <c r="AX160" t="s">
+    <row r="156" spans="51:51">
+      <c r="AY156" t="s">
         <v>596</v>
       </c>
     </row>
-    <row r="161" spans="50:50">
-      <c r="AX161" t="s">
+    <row r="157" spans="51:51">
+      <c r="AY157" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="162" spans="50:50">
-      <c r="AX162" t="s">
+    <row r="158" spans="51:51">
+      <c r="AY158" t="s">
         <v>598</v>
       </c>
     </row>
-    <row r="163" spans="50:50">
-      <c r="AX163" t="s">
+    <row r="159" spans="51:51">
+      <c r="AY159" t="s">
         <v>599</v>
       </c>
     </row>
-    <row r="164" spans="50:50">
-      <c r="AX164" t="s">
+    <row r="160" spans="51:51">
+      <c r="AY160" t="s">
         <v>600</v>
       </c>
     </row>
-    <row r="165" spans="50:50">
-      <c r="AX165" t="s">
+    <row r="161" spans="51:51">
+      <c r="AY161" t="s">
         <v>601</v>
       </c>
     </row>
-    <row r="166" spans="50:50">
-      <c r="AX166" t="s">
+    <row r="162" spans="51:51">
+      <c r="AY162" t="s">
         <v>602</v>
       </c>
     </row>
-    <row r="167" spans="50:50">
-      <c r="AX167" t="s">
+    <row r="163" spans="51:51">
+      <c r="AY163" t="s">
         <v>603</v>
       </c>
     </row>
-    <row r="168" spans="50:50">
-      <c r="AX168" t="s">
+    <row r="164" spans="51:51">
+      <c r="AY164" t="s">
         <v>604</v>
       </c>
     </row>
-    <row r="169" spans="50:50">
-      <c r="AX169" t="s">
+    <row r="165" spans="51:51">
+      <c r="AY165" t="s">
         <v>605</v>
       </c>
     </row>
-    <row r="170" spans="50:50">
-      <c r="AX170" t="s">
+    <row r="166" spans="51:51">
+      <c r="AY166" t="s">
         <v>606</v>
       </c>
     </row>
-    <row r="171" spans="50:50">
-      <c r="AX171" t="s">
+    <row r="167" spans="51:51">
+      <c r="AY167" t="s">
         <v>607</v>
       </c>
     </row>
-    <row r="172" spans="50:50">
-      <c r="AX172" t="s">
+    <row r="168" spans="51:51">
+      <c r="AY168" t="s">
         <v>608</v>
       </c>
     </row>
-    <row r="173" spans="50:50">
-      <c r="AX173" t="s">
+    <row r="169" spans="51:51">
+      <c r="AY169" t="s">
         <v>609</v>
       </c>
     </row>
-    <row r="174" spans="50:50">
-      <c r="AX174" t="s">
+    <row r="170" spans="51:51">
+      <c r="AY170" t="s">
         <v>610</v>
       </c>
     </row>
-    <row r="175" spans="50:50">
-      <c r="AX175" t="s">
+    <row r="171" spans="51:51">
+      <c r="AY171" t="s">
         <v>611</v>
       </c>
     </row>
-    <row r="176" spans="50:50">
-      <c r="AX176" t="s">
+    <row r="172" spans="51:51">
+      <c r="AY172" t="s">
         <v>612</v>
       </c>
     </row>
-    <row r="177" spans="50:50">
-      <c r="AX177" t="s">
+    <row r="173" spans="51:51">
+      <c r="AY173" t="s">
         <v>613</v>
       </c>
     </row>
-    <row r="178" spans="50:50">
-      <c r="AX178" t="s">
+    <row r="174" spans="51:51">
+      <c r="AY174" t="s">
         <v>614</v>
       </c>
     </row>
-    <row r="179" spans="50:50">
-      <c r="AX179" t="s">
+    <row r="175" spans="51:51">
+      <c r="AY175" t="s">
         <v>615</v>
       </c>
     </row>
-    <row r="180" spans="50:50">
-      <c r="AX180" t="s">
+    <row r="176" spans="51:51">
+      <c r="AY176" t="s">
         <v>616</v>
       </c>
     </row>
-    <row r="181" spans="50:50">
-      <c r="AX181" t="s">
+    <row r="177" spans="51:51">
+      <c r="AY177" t="s">
         <v>617</v>
       </c>
     </row>
-    <row r="182" spans="50:50">
-      <c r="AX182" t="s">
+    <row r="178" spans="51:51">
+      <c r="AY178" t="s">
         <v>618</v>
       </c>
     </row>
-    <row r="183" spans="50:50">
-      <c r="AX183" t="s">
+    <row r="179" spans="51:51">
+      <c r="AY179" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="184" spans="50:50">
-      <c r="AX184" t="s">
+    <row r="180" spans="51:51">
+      <c r="AY180" t="s">
         <v>620</v>
       </c>
     </row>
-    <row r="185" spans="50:50">
-      <c r="AX185" t="s">
+    <row r="181" spans="51:51">
+      <c r="AY181" t="s">
         <v>621</v>
       </c>
     </row>
-    <row r="186" spans="50:50">
-      <c r="AX186" t="s">
+    <row r="182" spans="51:51">
+      <c r="AY182" t="s">
         <v>622</v>
       </c>
     </row>
-    <row r="187" spans="50:50">
-      <c r="AX187" t="s">
+    <row r="183" spans="51:51">
+      <c r="AY183" t="s">
         <v>623</v>
       </c>
     </row>
-    <row r="188" spans="50:50">
-      <c r="AX188" t="s">
+    <row r="184" spans="51:51">
+      <c r="AY184" t="s">
         <v>624</v>
       </c>
     </row>
-    <row r="189" spans="50:50">
-      <c r="AX189" t="s">
+    <row r="185" spans="51:51">
+      <c r="AY185" t="s">
         <v>625</v>
       </c>
     </row>
-    <row r="190" spans="50:50">
-      <c r="AX190" t="s">
+    <row r="186" spans="51:51">
+      <c r="AY186" t="s">
         <v>626</v>
       </c>
     </row>
-    <row r="191" spans="50:50">
-      <c r="AX191" t="s">
+    <row r="187" spans="51:51">
+      <c r="AY187" t="s">
         <v>627</v>
       </c>
     </row>
-    <row r="192" spans="50:50">
-      <c r="AX192" t="s">
+    <row r="188" spans="51:51">
+      <c r="AY188" t="s">
         <v>628</v>
       </c>
     </row>
-    <row r="193" spans="50:50">
-      <c r="AX193" t="s">
+    <row r="189" spans="51:51">
+      <c r="AY189" t="s">
         <v>629</v>
       </c>
     </row>
-    <row r="194" spans="50:50">
-      <c r="AX194" t="s">
+    <row r="190" spans="51:51">
+      <c r="AY190" t="s">
         <v>630</v>
       </c>
     </row>
-    <row r="195" spans="50:50">
-      <c r="AX195" t="s">
+    <row r="191" spans="51:51">
+      <c r="AY191" t="s">
         <v>631</v>
       </c>
     </row>
-    <row r="196" spans="50:50">
-      <c r="AX196" t="s">
+    <row r="192" spans="51:51">
+      <c r="AY192" t="s">
         <v>632</v>
       </c>
     </row>
-    <row r="197" spans="50:50">
-      <c r="AX197" t="s">
+    <row r="193" spans="51:51">
+      <c r="AY193" t="s">
         <v>633</v>
       </c>
     </row>
-    <row r="198" spans="50:50">
-      <c r="AX198" t="s">
+    <row r="194" spans="51:51">
+      <c r="AY194" t="s">
         <v>634</v>
       </c>
     </row>
-    <row r="199" spans="50:50">
-      <c r="AX199" t="s">
+    <row r="195" spans="51:51">
+      <c r="AY195" t="s">
         <v>635</v>
       </c>
     </row>
-    <row r="200" spans="50:50">
-      <c r="AX200" t="s">
+    <row r="196" spans="51:51">
+      <c r="AY196" t="s">
         <v>636</v>
       </c>
     </row>
-    <row r="201" spans="50:50">
-      <c r="AX201" t="s">
+    <row r="197" spans="51:51">
+      <c r="AY197" t="s">
         <v>637</v>
       </c>
     </row>
-    <row r="202" spans="50:50">
-      <c r="AX202" t="s">
+    <row r="198" spans="51:51">
+      <c r="AY198" t="s">
         <v>638</v>
       </c>
     </row>
-    <row r="203" spans="50:50">
-      <c r="AX203" t="s">
+    <row r="199" spans="51:51">
+      <c r="AY199" t="s">
         <v>639</v>
       </c>
     </row>
-    <row r="204" spans="50:50">
-      <c r="AX204" t="s">
+    <row r="200" spans="51:51">
+      <c r="AY200" t="s">
         <v>640</v>
       </c>
     </row>
-    <row r="205" spans="50:50">
-      <c r="AX205" t="s">
+    <row r="201" spans="51:51">
+      <c r="AY201" t="s">
         <v>641</v>
       </c>
     </row>
-    <row r="206" spans="50:50">
-      <c r="AX206" t="s">
+    <row r="202" spans="51:51">
+      <c r="AY202" t="s">
         <v>642</v>
       </c>
     </row>
-    <row r="207" spans="50:50">
-      <c r="AX207" t="s">
+    <row r="203" spans="51:51">
+      <c r="AY203" t="s">
         <v>643</v>
       </c>
     </row>
-    <row r="208" spans="50:50">
-      <c r="AX208" t="s">
+    <row r="204" spans="51:51">
+      <c r="AY204" t="s">
         <v>644</v>
       </c>
     </row>
-    <row r="209" spans="50:50">
-      <c r="AX209" t="s">
+    <row r="205" spans="51:51">
+      <c r="AY205" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="210" spans="50:50">
-      <c r="AX210" t="s">
+    <row r="206" spans="51:51">
+      <c r="AY206" t="s">
         <v>646</v>
       </c>
     </row>
-    <row r="211" spans="50:50">
-      <c r="AX211" t="s">
+    <row r="207" spans="51:51">
+      <c r="AY207" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="212" spans="50:50">
-      <c r="AX212" t="s">
+    <row r="208" spans="51:51">
+      <c r="AY208" t="s">
         <v>648</v>
       </c>
     </row>
-    <row r="213" spans="50:50">
-      <c r="AX213" t="s">
+    <row r="209" spans="51:51">
+      <c r="AY209" t="s">
         <v>649</v>
       </c>
     </row>
-    <row r="214" spans="50:50">
-      <c r="AX214" t="s">
+    <row r="210" spans="51:51">
+      <c r="AY210" t="s">
         <v>650</v>
       </c>
     </row>
-    <row r="215" spans="50:50">
-      <c r="AX215" t="s">
+    <row r="211" spans="51:51">
+      <c r="AY211" t="s">
         <v>651</v>
       </c>
     </row>
-    <row r="216" spans="50:50">
-      <c r="AX216" t="s">
+    <row r="212" spans="51:51">
+      <c r="AY212" t="s">
         <v>652</v>
       </c>
     </row>
-    <row r="217" spans="50:50">
-      <c r="AX217" t="s">
+    <row r="213" spans="51:51">
+      <c r="AY213" t="s">
         <v>653</v>
       </c>
     </row>
-    <row r="218" spans="50:50">
-      <c r="AX218" t="s">
+    <row r="214" spans="51:51">
+      <c r="AY214" t="s">
         <v>654</v>
       </c>
     </row>
-    <row r="219" spans="50:50">
-      <c r="AX219" t="s">
+    <row r="215" spans="51:51">
+      <c r="AY215" t="s">
         <v>655</v>
       </c>
     </row>
-    <row r="220" spans="50:50">
-      <c r="AX220" t="s">
+    <row r="216" spans="51:51">
+      <c r="AY216" t="s">
         <v>656</v>
       </c>
     </row>
-    <row r="221" spans="50:50">
-      <c r="AX221" t="s">
+    <row r="217" spans="51:51">
+      <c r="AY217" t="s">
         <v>657</v>
       </c>
     </row>
-    <row r="222" spans="50:50">
-      <c r="AX222" t="s">
+    <row r="218" spans="51:51">
+      <c r="AY218" t="s">
         <v>658</v>
       </c>
     </row>
-    <row r="223" spans="50:50">
-      <c r="AX223" t="s">
+    <row r="219" spans="51:51">
+      <c r="AY219" t="s">
         <v>659</v>
       </c>
     </row>
-    <row r="224" spans="50:50">
-      <c r="AX224" t="s">
+    <row r="220" spans="51:51">
+      <c r="AY220" t="s">
         <v>660</v>
       </c>
     </row>
-    <row r="225" spans="50:50">
-      <c r="AX225" t="s">
+    <row r="221" spans="51:51">
+      <c r="AY221" t="s">
         <v>661</v>
       </c>
     </row>
-    <row r="226" spans="50:50">
-      <c r="AX226" t="s">
+    <row r="222" spans="51:51">
+      <c r="AY222" t="s">
         <v>662</v>
       </c>
     </row>
-    <row r="227" spans="50:50">
-      <c r="AX227" t="s">
+    <row r="223" spans="51:51">
+      <c r="AY223" t="s">
         <v>663</v>
       </c>
     </row>
-    <row r="228" spans="50:50">
-      <c r="AX228" t="s">
+    <row r="224" spans="51:51">
+      <c r="AY224" t="s">
         <v>664</v>
       </c>
     </row>
-    <row r="229" spans="50:50">
-      <c r="AX229" t="s">
+    <row r="225" spans="51:51">
+      <c r="AY225" t="s">
         <v>665</v>
       </c>
     </row>
-    <row r="230" spans="50:50">
-      <c r="AX230" t="s">
+    <row r="226" spans="51:51">
+      <c r="AY226" t="s">
         <v>666</v>
       </c>
     </row>
-    <row r="231" spans="50:50">
-      <c r="AX231" t="s">
+    <row r="227" spans="51:51">
+      <c r="AY227" t="s">
         <v>667</v>
       </c>
     </row>
-    <row r="232" spans="50:50">
-      <c r="AX232" t="s">
+    <row r="228" spans="51:51">
+      <c r="AY228" t="s">
         <v>668</v>
       </c>
     </row>
-    <row r="233" spans="50:50">
-      <c r="AX233" t="s">
+    <row r="229" spans="51:51">
+      <c r="AY229" t="s">
         <v>669</v>
       </c>
     </row>
-    <row r="234" spans="50:50">
-      <c r="AX234" t="s">
+    <row r="230" spans="51:51">
+      <c r="AY230" t="s">
         <v>670</v>
       </c>
     </row>
-    <row r="235" spans="50:50">
-      <c r="AX235" t="s">
+    <row r="231" spans="51:51">
+      <c r="AY231" t="s">
         <v>671</v>
       </c>
     </row>
-    <row r="236" spans="50:50">
-      <c r="AX236" t="s">
+    <row r="232" spans="51:51">
+      <c r="AY232" t="s">
         <v>672</v>
       </c>
     </row>
-    <row r="237" spans="50:50">
-      <c r="AX237" t="s">
+    <row r="233" spans="51:51">
+      <c r="AY233" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="238" spans="50:50">
-      <c r="AX238" t="s">
+    <row r="234" spans="51:51">
+      <c r="AY234" t="s">
         <v>674</v>
       </c>
     </row>
-    <row r="239" spans="50:50">
-      <c r="AX239" t="s">
+    <row r="235" spans="51:51">
+      <c r="AY235" t="s">
         <v>675</v>
       </c>
     </row>
-    <row r="240" spans="50:50">
-      <c r="AX240" t="s">
+    <row r="236" spans="51:51">
+      <c r="AY236" t="s">
         <v>676</v>
       </c>
     </row>
-    <row r="241" spans="50:50">
-      <c r="AX241" t="s">
+    <row r="237" spans="51:51">
+      <c r="AY237" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="242" spans="50:50">
-      <c r="AX242" t="s">
+    <row r="238" spans="51:51">
+      <c r="AY238" t="s">
         <v>678</v>
       </c>
     </row>
-    <row r="243" spans="50:50">
-      <c r="AX243" t="s">
+    <row r="239" spans="51:51">
+      <c r="AY239" t="s">
         <v>679</v>
       </c>
     </row>
-    <row r="244" spans="50:50">
-      <c r="AX244" t="s">
+    <row r="240" spans="51:51">
+      <c r="AY240" t="s">
         <v>680</v>
       </c>
     </row>
-    <row r="245" spans="50:50">
-      <c r="AX245" t="s">
+    <row r="241" spans="51:51">
+      <c r="AY241" t="s">
         <v>681</v>
       </c>
     </row>
-    <row r="246" spans="50:50">
-      <c r="AX246" t="s">
+    <row r="242" spans="51:51">
+      <c r="AY242" t="s">
         <v>682</v>
       </c>
     </row>
-    <row r="247" spans="50:50">
-      <c r="AX247" t="s">
+    <row r="243" spans="51:51">
+      <c r="AY243" t="s">
         <v>683</v>
       </c>
     </row>
-    <row r="248" spans="50:50">
-      <c r="AX248" t="s">
+    <row r="244" spans="51:51">
+      <c r="AY244" t="s">
         <v>684</v>
       </c>
     </row>
-    <row r="249" spans="50:50">
-      <c r="AX249" t="s">
+    <row r="245" spans="51:51">
+      <c r="AY245" t="s">
         <v>685</v>
       </c>
     </row>
-    <row r="250" spans="50:50">
-      <c r="AX250" t="s">
+    <row r="246" spans="51:51">
+      <c r="AY246" t="s">
         <v>686</v>
       </c>
     </row>
-    <row r="251" spans="50:50">
-      <c r="AX251" t="s">
+    <row r="247" spans="51:51">
+      <c r="AY247" t="s">
         <v>687</v>
       </c>
     </row>
-    <row r="252" spans="50:50">
-      <c r="AX252" t="s">
+    <row r="248" spans="51:51">
+      <c r="AY248" t="s">
         <v>688</v>
       </c>
     </row>
-    <row r="253" spans="50:50">
-      <c r="AX253" t="s">
+    <row r="249" spans="51:51">
+      <c r="AY249" t="s">
         <v>689</v>
       </c>
     </row>
-    <row r="254" spans="50:50">
-      <c r="AX254" t="s">
+    <row r="250" spans="51:51">
+      <c r="AY250" t="s">
         <v>690</v>
       </c>
     </row>
-    <row r="255" spans="50:50">
-      <c r="AX255" t="s">
+    <row r="251" spans="51:51">
+      <c r="AY251" t="s">
         <v>691</v>
       </c>
     </row>
-    <row r="256" spans="50:50">
-      <c r="AX256" t="s">
+    <row r="252" spans="51:51">
+      <c r="AY252" t="s">
         <v>692</v>
       </c>
     </row>
-    <row r="257" spans="50:50">
-      <c r="AX257" t="s">
+    <row r="253" spans="51:51">
+      <c r="AY253" t="s">
         <v>693</v>
       </c>
     </row>
-    <row r="258" spans="50:50">
-      <c r="AX258" t="s">
+    <row r="254" spans="51:51">
+      <c r="AY254" t="s">
         <v>694</v>
       </c>
     </row>
-    <row r="259" spans="50:50">
-      <c r="AX259" t="s">
+    <row r="255" spans="51:51">
+      <c r="AY255" t="s">
         <v>695</v>
       </c>
     </row>
-    <row r="260" spans="50:50">
-      <c r="AX260" t="s">
+    <row r="256" spans="51:51">
+      <c r="AY256" t="s">
         <v>696</v>
       </c>
     </row>
-    <row r="261" spans="50:50">
-      <c r="AX261" t="s">
+    <row r="257" spans="51:51">
+      <c r="AY257" t="s">
         <v>697</v>
       </c>
     </row>
-    <row r="262" spans="50:50">
-      <c r="AX262" t="s">
+    <row r="258" spans="51:51">
+      <c r="AY258" t="s">
         <v>698</v>
       </c>
     </row>
-    <row r="263" spans="50:50">
-      <c r="AX263" t="s">
+    <row r="259" spans="51:51">
+      <c r="AY259" t="s">
         <v>699</v>
       </c>
     </row>
-    <row r="264" spans="50:50">
-      <c r="AX264" t="s">
+    <row r="260" spans="51:51">
+      <c r="AY260" t="s">
         <v>700</v>
       </c>
     </row>
-    <row r="265" spans="50:50">
-      <c r="AX265" t="s">
+    <row r="261" spans="51:51">
+      <c r="AY261" t="s">
         <v>701</v>
       </c>
     </row>
-    <row r="266" spans="50:50">
-      <c r="AX266" t="s">
+    <row r="262" spans="51:51">
+      <c r="AY262" t="s">
         <v>702</v>
       </c>
     </row>
-    <row r="267" spans="50:50">
-      <c r="AX267" t="s">
+    <row r="263" spans="51:51">
+      <c r="AY263" t="s">
         <v>703</v>
       </c>
     </row>
-    <row r="268" spans="50:50">
-      <c r="AX268" t="s">
+    <row r="264" spans="51:51">
+      <c r="AY264" t="s">
         <v>704</v>
       </c>
     </row>
-    <row r="269" spans="50:50">
-      <c r="AX269" t="s">
+    <row r="265" spans="51:51">
+      <c r="AY265" t="s">
         <v>705</v>
       </c>
     </row>
-    <row r="270" spans="50:50">
-      <c r="AX270" t="s">
+    <row r="266" spans="51:51">
+      <c r="AY266" t="s">
         <v>706</v>
       </c>
     </row>
-    <row r="271" spans="50:50">
-      <c r="AX271" t="s">
+    <row r="267" spans="51:51">
+      <c r="AY267" t="s">
         <v>707</v>
       </c>
     </row>
-    <row r="272" spans="50:50">
-      <c r="AX272" t="s">
+    <row r="268" spans="51:51">
+      <c r="AY268" t="s">
         <v>708</v>
       </c>
     </row>
-    <row r="273" spans="50:50">
-      <c r="AX273" t="s">
+    <row r="269" spans="51:51">
+      <c r="AY269" t="s">
         <v>709</v>
       </c>
     </row>
-    <row r="274" spans="50:50">
-      <c r="AX274" t="s">
+    <row r="270" spans="51:51">
+      <c r="AY270" t="s">
         <v>710</v>
       </c>
     </row>
-    <row r="275" spans="50:50">
-      <c r="AX275" t="s">
+    <row r="271" spans="51:51">
+      <c r="AY271" t="s">
         <v>711</v>
       </c>
     </row>
-    <row r="276" spans="50:50">
-      <c r="AX276" t="s">
+    <row r="272" spans="51:51">
+      <c r="AY272" t="s">
         <v>712</v>
       </c>
     </row>
-    <row r="277" spans="50:50">
-      <c r="AX277" t="s">
+    <row r="273" spans="51:51">
+      <c r="AY273" t="s">
         <v>713</v>
       </c>
     </row>
-    <row r="278" spans="50:50">
-      <c r="AX278" t="s">
+    <row r="274" spans="51:51">
+      <c r="AY274" t="s">
         <v>714</v>
       </c>
     </row>
-    <row r="279" spans="50:50">
-      <c r="AX279" t="s">
+    <row r="275" spans="51:51">
+      <c r="AY275" t="s">
         <v>715</v>
       </c>
     </row>
-    <row r="280" spans="50:50">
-      <c r="AX280" t="s">
+    <row r="276" spans="51:51">
+      <c r="AY276" t="s">
         <v>716</v>
       </c>
     </row>
-    <row r="281" spans="50:50">
-      <c r="AX281" t="s">
+    <row r="277" spans="51:51">
+      <c r="AY277" t="s">
         <v>717</v>
       </c>
     </row>
-    <row r="282" spans="50:50">
-      <c r="AX282" t="s">
+    <row r="278" spans="51:51">
+      <c r="AY278" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="283" spans="50:50">
-      <c r="AX283" t="s">
+    <row r="279" spans="51:51">
+      <c r="AY279" t="s">
         <v>719</v>
       </c>
     </row>
-    <row r="284" spans="50:50">
-      <c r="AX284" t="s">
+    <row r="280" spans="51:51">
+      <c r="AY280" t="s">
         <v>720</v>
       </c>
     </row>
-    <row r="285" spans="50:50">
-      <c r="AX285" t="s">
+    <row r="281" spans="51:51">
+      <c r="AY281" t="s">
         <v>721</v>
       </c>
     </row>
-    <row r="286" spans="50:50">
-      <c r="AX286" t="s">
+    <row r="282" spans="51:51">
+      <c r="AY282" t="s">
         <v>722</v>
       </c>
     </row>
-    <row r="287" spans="50:50">
-      <c r="AX287" t="s">
+    <row r="283" spans="51:51">
+      <c r="AY283" t="s">
         <v>723</v>
       </c>
     </row>
-    <row r="288" spans="50:50">
-      <c r="AX288" t="s">
+    <row r="284" spans="51:51">
+      <c r="AY284" t="s">
         <v>724</v>
       </c>
     </row>
-    <row r="289" spans="50:50">
-      <c r="AX289" t="s">
+    <row r="285" spans="51:51">
+      <c r="AY285" t="s">
         <v>725</v>
+      </c>
+    </row>
+    <row r="286" spans="51:51">
+      <c r="AY286" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="287" spans="51:51">
+      <c r="AY287" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="288" spans="51:51">
+      <c r="AY288" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="289" spans="51:51">
+      <c r="AY289" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="290" spans="51:51">
+      <c r="AY290" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="291" spans="51:51">
+      <c r="AY291" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="292" spans="51:51">
+      <c r="AY292" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="293" spans="51:51">
+      <c r="AY293" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="294" spans="51:51">
+      <c r="AY294" t="s">
+        <v>734</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000022/metadata_template_ERC000022.xlsx
+++ b/templates/ERC000022/metadata_template_ERC000022.xlsx
@@ -17,30 +17,30 @@
     <sheet name="cv_sample" sheetId="8" state="hidden" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="drainageclassification">'cv_sample'!$BI$1:$BI$6</definedName>
+    <definedName name="drainageclassification">'cv_sample'!$BJ$1:$BJ$6</definedName>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AY$1:$AY$294</definedName>
-    <definedName name="historytillage">'cv_sample'!$CD$1:$CD$9</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AZ$1:$AZ$294</definedName>
+    <definedName name="historytillage">'cv_sample'!$CE$1:$CE$9</definedName>
     <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
-    <definedName name="observedbioticrelationship">'cv_sample'!$G$1:$G$5</definedName>
+    <definedName name="observedbioticrelationship">'cv_sample'!$H$1:$H$5</definedName>
     <definedName name="platform">'cv_experiment'!$M$1:$M$18</definedName>
-    <definedName name="profileposition">'cv_sample'!$BP$1:$BP$5</definedName>
-    <definedName name="relationshiptooxygen">'cv_sample'!$I$1:$I$7</definedName>
-    <definedName name="sequencequalitycheck">'cv_sample'!$AD$1:$AD$3</definedName>
-    <definedName name="soilhorizon">'cv_sample'!$BH$1:$BH$6</definedName>
-    <definedName name="soiltype">'cv_sample'!$Q$1:$Q$32</definedName>
+    <definedName name="profileposition">'cv_sample'!$BQ$1:$BQ$5</definedName>
+    <definedName name="relationshiptooxygen">'cv_sample'!$J$1:$J$7</definedName>
+    <definedName name="sequencequalitycheck">'cv_sample'!$AE$1:$AE$3</definedName>
+    <definedName name="soilhorizon">'cv_sample'!$BI$1:$BI$6</definedName>
+    <definedName name="soiltype">'cv_sample'!$R$1:$R$32</definedName>
     <definedName name="studytype">'cv_study'!$C$1:$C$15</definedName>
-    <definedName name="trophiclevel">'cv_sample'!$F$1:$F$30</definedName>
+    <definedName name="trophiclevel">'cv_sample'!$G$1:$G$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="897" uniqueCount="889">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="899" uniqueCount="891">
   <si>
     <t>alias</t>
   </si>
@@ -856,6 +856,12 @@
   </si>
   <si>
     <t>(Optional) Scientific name of sample that distinguishes its taxonomy.  please use a name or synonym that is tracked in the insdc taxonomy database. also, this field can be used to confirm the taxon_id setting.</t>
+  </si>
+  <si>
+    <t>common_name</t>
+  </si>
+  <si>
+    <t>(Optional) Genbank common name of the organism.  examples: human, mouse.</t>
   </si>
   <si>
     <t>sample_description</t>
@@ -4230,13 +4236,13 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:DJ2"/>
+  <dimension ref="A1:DK2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="301" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:114">
+    <row r="1" spans="1:115">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4253,16 +4259,16 @@
         <v>272</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>304</v>
+        <v>274</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>313</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>324</v>
@@ -4286,7 +4292,7 @@
         <v>336</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>370</v>
+        <v>338</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>372</v>
@@ -4325,7 +4331,7 @@
         <v>394</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="AE1" s="1" t="s">
         <v>401</v>
@@ -4388,7 +4394,7 @@
         <v>439</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>735</v>
+        <v>441</v>
       </c>
       <c r="AZ1" s="1" t="s">
         <v>737</v>
@@ -4415,10 +4421,10 @@
         <v>751</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>759</v>
+        <v>753</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>767</v>
+        <v>761</v>
       </c>
       <c r="BJ1" s="1" t="s">
         <v>769</v>
@@ -4439,7 +4445,7 @@
         <v>779</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>786</v>
+        <v>781</v>
       </c>
       <c r="BQ1" s="1" t="s">
         <v>788</v>
@@ -4481,7 +4487,7 @@
         <v>812</v>
       </c>
       <c r="CD1" s="1" t="s">
-        <v>823</v>
+        <v>814</v>
       </c>
       <c r="CE1" s="1" t="s">
         <v>825</v>
@@ -4579,8 +4585,11 @@
       <c r="DJ1" s="1" t="s">
         <v>887</v>
       </c>
-    </row>
-    <row r="2" spans="1:114" ht="150" customHeight="1">
+      <c r="DK1" s="1" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="2" spans="1:115" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>266</v>
       </c>
@@ -4597,16 +4606,16 @@
         <v>273</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>305</v>
+        <v>275</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>314</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>325</v>
@@ -4630,7 +4639,7 @@
         <v>337</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>371</v>
+        <v>339</v>
       </c>
       <c r="R2" s="2" t="s">
         <v>373</v>
@@ -4669,7 +4678,7 @@
         <v>395</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="AE2" s="2" t="s">
         <v>402</v>
@@ -4732,7 +4741,7 @@
         <v>440</v>
       </c>
       <c r="AY2" s="2" t="s">
-        <v>736</v>
+        <v>442</v>
       </c>
       <c r="AZ2" s="2" t="s">
         <v>738</v>
@@ -4759,10 +4768,10 @@
         <v>752</v>
       </c>
       <c r="BH2" s="2" t="s">
-        <v>760</v>
+        <v>754</v>
       </c>
       <c r="BI2" s="2" t="s">
-        <v>768</v>
+        <v>762</v>
       </c>
       <c r="BJ2" s="2" t="s">
         <v>770</v>
@@ -4783,7 +4792,7 @@
         <v>780</v>
       </c>
       <c r="BP2" s="2" t="s">
-        <v>787</v>
+        <v>782</v>
       </c>
       <c r="BQ2" s="2" t="s">
         <v>789</v>
@@ -4825,7 +4834,7 @@
         <v>813</v>
       </c>
       <c r="CD2" s="2" t="s">
-        <v>824</v>
+        <v>815</v>
       </c>
       <c r="CE2" s="2" t="s">
         <v>826</v>
@@ -4923,37 +4932,40 @@
       <c r="DJ2" s="2" t="s">
         <v>888</v>
       </c>
+      <c r="DK2" s="2" t="s">
+        <v>890</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="10">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G101">
       <formula1>trophiclevel</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H101">
       <formula1>observedbioticrelationship</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I3:I101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J3:J101">
       <formula1>relationshiptooxygen</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q3:Q101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R3:R101">
       <formula1>soiltype</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD3:AD101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE3:AE101">
       <formula1>sequencequalitycheck</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AY3:AY101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AZ3:AZ101">
       <formula1>geographiclocationcountryandorsea</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BH3:BH101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BI3:BI101">
       <formula1>soilhorizon</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BI3:BI101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BJ3:BJ101">
       <formula1>drainageclassification</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BP3:BP101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BQ3:BQ101">
       <formula1>profileposition</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CD3:CD101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CE3:CE101">
       <formula1>historytillage</formula1>
     </dataValidation>
   </dataValidations>
@@ -4963,1786 +4975,1786 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="F1:CD294"/>
+  <dimension ref="G1:CE294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="6:82">
-      <c r="F1" t="s">
-        <v>274</v>
-      </c>
+    <row r="1" spans="7:83">
       <c r="G1" t="s">
-        <v>306</v>
-      </c>
-      <c r="I1" t="s">
-        <v>315</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>338</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>396</v>
-      </c>
-      <c r="AY1" t="s">
-        <v>441</v>
-      </c>
-      <c r="BH1" t="s">
-        <v>753</v>
+        <v>276</v>
+      </c>
+      <c r="H1" t="s">
+        <v>308</v>
+      </c>
+      <c r="J1" t="s">
+        <v>317</v>
+      </c>
+      <c r="R1" t="s">
+        <v>340</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>398</v>
+      </c>
+      <c r="AZ1" t="s">
+        <v>443</v>
       </c>
       <c r="BI1" t="s">
-        <v>761</v>
-      </c>
-      <c r="BP1" t="s">
-        <v>781</v>
-      </c>
-      <c r="CD1" t="s">
-        <v>814</v>
-      </c>
-    </row>
-    <row r="2" spans="6:82">
-      <c r="F2" t="s">
-        <v>275</v>
-      </c>
+        <v>755</v>
+      </c>
+      <c r="BJ1" t="s">
+        <v>763</v>
+      </c>
+      <c r="BQ1" t="s">
+        <v>783</v>
+      </c>
+      <c r="CE1" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="2" spans="7:83">
       <c r="G2" t="s">
-        <v>307</v>
-      </c>
-      <c r="I2" t="s">
-        <v>316</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>339</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>397</v>
-      </c>
-      <c r="AY2" t="s">
-        <v>442</v>
-      </c>
-      <c r="BH2" t="s">
-        <v>754</v>
+        <v>277</v>
+      </c>
+      <c r="H2" t="s">
+        <v>309</v>
+      </c>
+      <c r="J2" t="s">
+        <v>318</v>
+      </c>
+      <c r="R2" t="s">
+        <v>341</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>399</v>
+      </c>
+      <c r="AZ2" t="s">
+        <v>444</v>
       </c>
       <c r="BI2" t="s">
-        <v>762</v>
-      </c>
-      <c r="BP2" t="s">
-        <v>782</v>
-      </c>
-      <c r="CD2" t="s">
-        <v>815</v>
-      </c>
-    </row>
-    <row r="3" spans="6:82">
-      <c r="F3" t="s">
-        <v>276</v>
-      </c>
+        <v>756</v>
+      </c>
+      <c r="BJ2" t="s">
+        <v>764</v>
+      </c>
+      <c r="BQ2" t="s">
+        <v>784</v>
+      </c>
+      <c r="CE2" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="3" spans="7:83">
       <c r="G3" t="s">
-        <v>308</v>
-      </c>
-      <c r="I3" t="s">
-        <v>317</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>340</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>398</v>
-      </c>
-      <c r="AY3" t="s">
-        <v>443</v>
-      </c>
-      <c r="BH3" t="s">
-        <v>755</v>
+        <v>278</v>
+      </c>
+      <c r="H3" t="s">
+        <v>310</v>
+      </c>
+      <c r="J3" t="s">
+        <v>319</v>
+      </c>
+      <c r="R3" t="s">
+        <v>342</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>400</v>
+      </c>
+      <c r="AZ3" t="s">
+        <v>445</v>
       </c>
       <c r="BI3" t="s">
-        <v>763</v>
-      </c>
-      <c r="BP3" t="s">
-        <v>783</v>
-      </c>
-      <c r="CD3" t="s">
-        <v>816</v>
-      </c>
-    </row>
-    <row r="4" spans="6:82">
-      <c r="F4" t="s">
-        <v>277</v>
-      </c>
+        <v>757</v>
+      </c>
+      <c r="BJ3" t="s">
+        <v>765</v>
+      </c>
+      <c r="BQ3" t="s">
+        <v>785</v>
+      </c>
+      <c r="CE3" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="4" spans="7:83">
       <c r="G4" t="s">
-        <v>309</v>
-      </c>
-      <c r="I4" t="s">
-        <v>318</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>341</v>
-      </c>
-      <c r="AY4" t="s">
-        <v>444</v>
-      </c>
-      <c r="BH4" t="s">
-        <v>756</v>
+        <v>279</v>
+      </c>
+      <c r="H4" t="s">
+        <v>311</v>
+      </c>
+      <c r="J4" t="s">
+        <v>320</v>
+      </c>
+      <c r="R4" t="s">
+        <v>343</v>
+      </c>
+      <c r="AZ4" t="s">
+        <v>446</v>
       </c>
       <c r="BI4" t="s">
-        <v>764</v>
-      </c>
-      <c r="BP4" t="s">
-        <v>784</v>
-      </c>
-      <c r="CD4" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="5" spans="6:82">
-      <c r="F5" t="s">
-        <v>278</v>
-      </c>
+        <v>758</v>
+      </c>
+      <c r="BJ4" t="s">
+        <v>766</v>
+      </c>
+      <c r="BQ4" t="s">
+        <v>786</v>
+      </c>
+      <c r="CE4" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="5" spans="7:83">
       <c r="G5" t="s">
-        <v>310</v>
-      </c>
-      <c r="I5" t="s">
-        <v>319</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>342</v>
-      </c>
-      <c r="AY5" t="s">
-        <v>445</v>
-      </c>
-      <c r="BH5" t="s">
-        <v>757</v>
+        <v>280</v>
+      </c>
+      <c r="H5" t="s">
+        <v>312</v>
+      </c>
+      <c r="J5" t="s">
+        <v>321</v>
+      </c>
+      <c r="R5" t="s">
+        <v>344</v>
+      </c>
+      <c r="AZ5" t="s">
+        <v>447</v>
       </c>
       <c r="BI5" t="s">
-        <v>765</v>
-      </c>
-      <c r="BP5" t="s">
-        <v>785</v>
-      </c>
-      <c r="CD5" t="s">
-        <v>818</v>
-      </c>
-    </row>
-    <row r="6" spans="6:82">
-      <c r="F6" t="s">
-        <v>279</v>
-      </c>
-      <c r="I6" t="s">
-        <v>320</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>343</v>
-      </c>
-      <c r="AY6" t="s">
-        <v>446</v>
-      </c>
-      <c r="BH6" t="s">
-        <v>758</v>
+        <v>759</v>
+      </c>
+      <c r="BJ5" t="s">
+        <v>767</v>
+      </c>
+      <c r="BQ5" t="s">
+        <v>787</v>
+      </c>
+      <c r="CE5" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="6" spans="7:83">
+      <c r="G6" t="s">
+        <v>281</v>
+      </c>
+      <c r="J6" t="s">
+        <v>322</v>
+      </c>
+      <c r="R6" t="s">
+        <v>345</v>
+      </c>
+      <c r="AZ6" t="s">
+        <v>448</v>
       </c>
       <c r="BI6" t="s">
-        <v>766</v>
-      </c>
-      <c r="CD6" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="7" spans="6:82">
-      <c r="F7" t="s">
-        <v>280</v>
-      </c>
-      <c r="I7" t="s">
-        <v>321</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>344</v>
-      </c>
-      <c r="AY7" t="s">
-        <v>447</v>
-      </c>
-      <c r="CD7" t="s">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="8" spans="6:82">
-      <c r="F8" t="s">
-        <v>281</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>345</v>
-      </c>
-      <c r="AY8" t="s">
-        <v>448</v>
-      </c>
-      <c r="CD8" t="s">
+        <v>760</v>
+      </c>
+      <c r="BJ6" t="s">
+        <v>768</v>
+      </c>
+      <c r="CE6" t="s">
         <v>821</v>
       </c>
     </row>
-    <row r="9" spans="6:82">
-      <c r="F9" t="s">
+    <row r="7" spans="7:83">
+      <c r="G7" t="s">
         <v>282</v>
       </c>
-      <c r="Q9" t="s">
+      <c r="J7" t="s">
+        <v>323</v>
+      </c>
+      <c r="R7" t="s">
         <v>346</v>
       </c>
-      <c r="AY9" t="s">
+      <c r="AZ7" t="s">
         <v>449</v>
       </c>
-      <c r="CD9" t="s">
+      <c r="CE7" t="s">
         <v>822</v>
       </c>
     </row>
-    <row r="10" spans="6:82">
-      <c r="F10" t="s">
+    <row r="8" spans="7:83">
+      <c r="G8" t="s">
         <v>283</v>
       </c>
-      <c r="Q10" t="s">
+      <c r="R8" t="s">
         <v>347</v>
       </c>
-      <c r="AY10" t="s">
+      <c r="AZ8" t="s">
         <v>450</v>
       </c>
-    </row>
-    <row r="11" spans="6:82">
-      <c r="F11" t="s">
+      <c r="CE8" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="9" spans="7:83">
+      <c r="G9" t="s">
         <v>284</v>
       </c>
-      <c r="Q11" t="s">
+      <c r="R9" t="s">
         <v>348</v>
       </c>
-      <c r="AY11" t="s">
+      <c r="AZ9" t="s">
         <v>451</v>
       </c>
-    </row>
-    <row r="12" spans="6:82">
-      <c r="F12" t="s">
+      <c r="CE9" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="10" spans="7:83">
+      <c r="G10" t="s">
         <v>285</v>
       </c>
-      <c r="Q12" t="s">
+      <c r="R10" t="s">
         <v>349</v>
       </c>
-      <c r="AY12" t="s">
+      <c r="AZ10" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="13" spans="6:82">
-      <c r="F13" t="s">
+    <row r="11" spans="7:83">
+      <c r="G11" t="s">
         <v>286</v>
       </c>
-      <c r="Q13" t="s">
+      <c r="R11" t="s">
         <v>350</v>
       </c>
-      <c r="AY13" t="s">
+      <c r="AZ11" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="14" spans="6:82">
-      <c r="F14" t="s">
+    <row r="12" spans="7:83">
+      <c r="G12" t="s">
         <v>287</v>
       </c>
-      <c r="Q14" t="s">
+      <c r="R12" t="s">
         <v>351</v>
       </c>
-      <c r="AY14" t="s">
+      <c r="AZ12" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="15" spans="6:82">
-      <c r="F15" t="s">
+    <row r="13" spans="7:83">
+      <c r="G13" t="s">
         <v>288</v>
       </c>
-      <c r="Q15" t="s">
+      <c r="R13" t="s">
         <v>352</v>
       </c>
-      <c r="AY15" t="s">
+      <c r="AZ13" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="16" spans="6:82">
-      <c r="F16" t="s">
+    <row r="14" spans="7:83">
+      <c r="G14" t="s">
         <v>289</v>
       </c>
-      <c r="Q16" t="s">
+      <c r="R14" t="s">
         <v>353</v>
       </c>
-      <c r="AY16" t="s">
+      <c r="AZ14" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="17" spans="6:51">
-      <c r="F17" t="s">
+    <row r="15" spans="7:83">
+      <c r="G15" t="s">
         <v>290</v>
       </c>
-      <c r="Q17" t="s">
+      <c r="R15" t="s">
         <v>354</v>
       </c>
-      <c r="AY17" t="s">
+      <c r="AZ15" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="18" spans="6:51">
-      <c r="F18" t="s">
+    <row r="16" spans="7:83">
+      <c r="G16" t="s">
         <v>291</v>
       </c>
-      <c r="Q18" t="s">
+      <c r="R16" t="s">
         <v>355</v>
       </c>
-      <c r="AY18" t="s">
+      <c r="AZ16" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="19" spans="6:51">
-      <c r="F19" t="s">
+    <row r="17" spans="7:52">
+      <c r="G17" t="s">
         <v>292</v>
       </c>
-      <c r="Q19" t="s">
+      <c r="R17" t="s">
         <v>356</v>
       </c>
-      <c r="AY19" t="s">
+      <c r="AZ17" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="20" spans="6:51">
-      <c r="F20" t="s">
+    <row r="18" spans="7:52">
+      <c r="G18" t="s">
         <v>293</v>
       </c>
-      <c r="Q20" t="s">
+      <c r="R18" t="s">
         <v>357</v>
       </c>
-      <c r="AY20" t="s">
+      <c r="AZ18" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="21" spans="6:51">
-      <c r="F21" t="s">
+    <row r="19" spans="7:52">
+      <c r="G19" t="s">
         <v>294</v>
       </c>
-      <c r="Q21" t="s">
+      <c r="R19" t="s">
         <v>358</v>
       </c>
-      <c r="AY21" t="s">
+      <c r="AZ19" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="22" spans="6:51">
-      <c r="F22" t="s">
+    <row r="20" spans="7:52">
+      <c r="G20" t="s">
         <v>295</v>
       </c>
-      <c r="Q22" t="s">
+      <c r="R20" t="s">
         <v>359</v>
       </c>
-      <c r="AY22" t="s">
+      <c r="AZ20" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="23" spans="6:51">
-      <c r="F23" t="s">
+    <row r="21" spans="7:52">
+      <c r="G21" t="s">
         <v>296</v>
       </c>
-      <c r="Q23" t="s">
+      <c r="R21" t="s">
         <v>360</v>
       </c>
-      <c r="AY23" t="s">
+      <c r="AZ21" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="24" spans="6:51">
-      <c r="F24" t="s">
+    <row r="22" spans="7:52">
+      <c r="G22" t="s">
         <v>297</v>
       </c>
-      <c r="Q24" t="s">
+      <c r="R22" t="s">
         <v>361</v>
       </c>
-      <c r="AY24" t="s">
+      <c r="AZ22" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="25" spans="6:51">
-      <c r="F25" t="s">
+    <row r="23" spans="7:52">
+      <c r="G23" t="s">
         <v>298</v>
       </c>
-      <c r="Q25" t="s">
+      <c r="R23" t="s">
         <v>362</v>
       </c>
-      <c r="AY25" t="s">
+      <c r="AZ23" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="26" spans="6:51">
-      <c r="F26" t="s">
+    <row r="24" spans="7:52">
+      <c r="G24" t="s">
         <v>299</v>
       </c>
-      <c r="Q26" t="s">
+      <c r="R24" t="s">
         <v>363</v>
       </c>
-      <c r="AY26" t="s">
+      <c r="AZ24" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="27" spans="6:51">
-      <c r="F27" t="s">
+    <row r="25" spans="7:52">
+      <c r="G25" t="s">
         <v>300</v>
       </c>
-      <c r="Q27" t="s">
+      <c r="R25" t="s">
         <v>364</v>
       </c>
-      <c r="AY27" t="s">
+      <c r="AZ25" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="28" spans="6:51">
-      <c r="F28" t="s">
+    <row r="26" spans="7:52">
+      <c r="G26" t="s">
         <v>301</v>
       </c>
-      <c r="Q28" t="s">
+      <c r="R26" t="s">
         <v>365</v>
       </c>
-      <c r="AY28" t="s">
+      <c r="AZ26" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="29" spans="6:51">
-      <c r="F29" t="s">
+    <row r="27" spans="7:52">
+      <c r="G27" t="s">
         <v>302</v>
       </c>
-      <c r="Q29" t="s">
+      <c r="R27" t="s">
         <v>366</v>
       </c>
-      <c r="AY29" t="s">
+      <c r="AZ27" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="30" spans="6:51">
-      <c r="F30" t="s">
+    <row r="28" spans="7:52">
+      <c r="G28" t="s">
         <v>303</v>
       </c>
-      <c r="Q30" t="s">
+      <c r="R28" t="s">
         <v>367</v>
       </c>
-      <c r="AY30" t="s">
+      <c r="AZ28" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="31" spans="6:51">
-      <c r="Q31" t="s">
+    <row r="29" spans="7:52">
+      <c r="G29" t="s">
+        <v>304</v>
+      </c>
+      <c r="R29" t="s">
         <v>368</v>
       </c>
-      <c r="AY31" t="s">
+      <c r="AZ29" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="32" spans="6:51">
-      <c r="Q32" t="s">
+    <row r="30" spans="7:52">
+      <c r="G30" t="s">
+        <v>305</v>
+      </c>
+      <c r="R30" t="s">
         <v>369</v>
       </c>
-      <c r="AY32" t="s">
+      <c r="AZ30" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="33" spans="51:51">
-      <c r="AY33" t="s">
+    <row r="31" spans="7:52">
+      <c r="R31" t="s">
+        <v>370</v>
+      </c>
+      <c r="AZ31" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="34" spans="51:51">
-      <c r="AY34" t="s">
+    <row r="32" spans="7:52">
+      <c r="R32" t="s">
+        <v>371</v>
+      </c>
+      <c r="AZ32" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="35" spans="51:51">
-      <c r="AY35" t="s">
+    <row r="33" spans="52:52">
+      <c r="AZ33" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="36" spans="51:51">
-      <c r="AY36" t="s">
+    <row r="34" spans="52:52">
+      <c r="AZ34" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="37" spans="51:51">
-      <c r="AY37" t="s">
+    <row r="35" spans="52:52">
+      <c r="AZ35" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="38" spans="51:51">
-      <c r="AY38" t="s">
+    <row r="36" spans="52:52">
+      <c r="AZ36" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="39" spans="51:51">
-      <c r="AY39" t="s">
+    <row r="37" spans="52:52">
+      <c r="AZ37" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="40" spans="51:51">
-      <c r="AY40" t="s">
+    <row r="38" spans="52:52">
+      <c r="AZ38" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="41" spans="51:51">
-      <c r="AY41" t="s">
+    <row r="39" spans="52:52">
+      <c r="AZ39" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="42" spans="51:51">
-      <c r="AY42" t="s">
+    <row r="40" spans="52:52">
+      <c r="AZ40" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="43" spans="51:51">
-      <c r="AY43" t="s">
+    <row r="41" spans="52:52">
+      <c r="AZ41" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="44" spans="51:51">
-      <c r="AY44" t="s">
+    <row r="42" spans="52:52">
+      <c r="AZ42" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="45" spans="51:51">
-      <c r="AY45" t="s">
+    <row r="43" spans="52:52">
+      <c r="AZ43" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="46" spans="51:51">
-      <c r="AY46" t="s">
+    <row r="44" spans="52:52">
+      <c r="AZ44" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="47" spans="51:51">
-      <c r="AY47" t="s">
+    <row r="45" spans="52:52">
+      <c r="AZ45" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="48" spans="51:51">
-      <c r="AY48" t="s">
+    <row r="46" spans="52:52">
+      <c r="AZ46" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="49" spans="51:51">
-      <c r="AY49" t="s">
+    <row r="47" spans="52:52">
+      <c r="AZ47" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="50" spans="51:51">
-      <c r="AY50" t="s">
+    <row r="48" spans="52:52">
+      <c r="AZ48" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="51" spans="51:51">
-      <c r="AY51" t="s">
+    <row r="49" spans="52:52">
+      <c r="AZ49" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="52" spans="51:51">
-      <c r="AY52" t="s">
+    <row r="50" spans="52:52">
+      <c r="AZ50" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="53" spans="51:51">
-      <c r="AY53" t="s">
+    <row r="51" spans="52:52">
+      <c r="AZ51" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="54" spans="51:51">
-      <c r="AY54" t="s">
+    <row r="52" spans="52:52">
+      <c r="AZ52" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="55" spans="51:51">
-      <c r="AY55" t="s">
+    <row r="53" spans="52:52">
+      <c r="AZ53" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="56" spans="51:51">
-      <c r="AY56" t="s">
+    <row r="54" spans="52:52">
+      <c r="AZ54" t="s">
         <v>496</v>
       </c>
     </row>
-    <row r="57" spans="51:51">
-      <c r="AY57" t="s">
+    <row r="55" spans="52:52">
+      <c r="AZ55" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="58" spans="51:51">
-      <c r="AY58" t="s">
+    <row r="56" spans="52:52">
+      <c r="AZ56" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="59" spans="51:51">
-      <c r="AY59" t="s">
+    <row r="57" spans="52:52">
+      <c r="AZ57" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="60" spans="51:51">
-      <c r="AY60" t="s">
+    <row r="58" spans="52:52">
+      <c r="AZ58" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="61" spans="51:51">
-      <c r="AY61" t="s">
+    <row r="59" spans="52:52">
+      <c r="AZ59" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="62" spans="51:51">
-      <c r="AY62" t="s">
+    <row r="60" spans="52:52">
+      <c r="AZ60" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="63" spans="51:51">
-      <c r="AY63" t="s">
+    <row r="61" spans="52:52">
+      <c r="AZ61" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="64" spans="51:51">
-      <c r="AY64" t="s">
+    <row r="62" spans="52:52">
+      <c r="AZ62" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="65" spans="51:51">
-      <c r="AY65" t="s">
+    <row r="63" spans="52:52">
+      <c r="AZ63" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="66" spans="51:51">
-      <c r="AY66" t="s">
+    <row r="64" spans="52:52">
+      <c r="AZ64" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="67" spans="51:51">
-      <c r="AY67" t="s">
+    <row r="65" spans="52:52">
+      <c r="AZ65" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="68" spans="51:51">
-      <c r="AY68" t="s">
+    <row r="66" spans="52:52">
+      <c r="AZ66" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="69" spans="51:51">
-      <c r="AY69" t="s">
+    <row r="67" spans="52:52">
+      <c r="AZ67" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="70" spans="51:51">
-      <c r="AY70" t="s">
+    <row r="68" spans="52:52">
+      <c r="AZ68" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="71" spans="51:51">
-      <c r="AY71" t="s">
+    <row r="69" spans="52:52">
+      <c r="AZ69" t="s">
         <v>511</v>
       </c>
     </row>
-    <row r="72" spans="51:51">
-      <c r="AY72" t="s">
+    <row r="70" spans="52:52">
+      <c r="AZ70" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="73" spans="51:51">
-      <c r="AY73" t="s">
+    <row r="71" spans="52:52">
+      <c r="AZ71" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="74" spans="51:51">
-      <c r="AY74" t="s">
+    <row r="72" spans="52:52">
+      <c r="AZ72" t="s">
         <v>514</v>
       </c>
     </row>
-    <row r="75" spans="51:51">
-      <c r="AY75" t="s">
+    <row r="73" spans="52:52">
+      <c r="AZ73" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="76" spans="51:51">
-      <c r="AY76" t="s">
+    <row r="74" spans="52:52">
+      <c r="AZ74" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="77" spans="51:51">
-      <c r="AY77" t="s">
+    <row r="75" spans="52:52">
+      <c r="AZ75" t="s">
         <v>517</v>
       </c>
     </row>
-    <row r="78" spans="51:51">
-      <c r="AY78" t="s">
+    <row r="76" spans="52:52">
+      <c r="AZ76" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="79" spans="51:51">
-      <c r="AY79" t="s">
+    <row r="77" spans="52:52">
+      <c r="AZ77" t="s">
         <v>519</v>
       </c>
     </row>
-    <row r="80" spans="51:51">
-      <c r="AY80" t="s">
+    <row r="78" spans="52:52">
+      <c r="AZ78" t="s">
         <v>520</v>
       </c>
     </row>
-    <row r="81" spans="51:51">
-      <c r="AY81" t="s">
+    <row r="79" spans="52:52">
+      <c r="AZ79" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="82" spans="51:51">
-      <c r="AY82" t="s">
+    <row r="80" spans="52:52">
+      <c r="AZ80" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="83" spans="51:51">
-      <c r="AY83" t="s">
+    <row r="81" spans="52:52">
+      <c r="AZ81" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="84" spans="51:51">
-      <c r="AY84" t="s">
+    <row r="82" spans="52:52">
+      <c r="AZ82" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="85" spans="51:51">
-      <c r="AY85" t="s">
+    <row r="83" spans="52:52">
+      <c r="AZ83" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="86" spans="51:51">
-      <c r="AY86" t="s">
+    <row r="84" spans="52:52">
+      <c r="AZ84" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="87" spans="51:51">
-      <c r="AY87" t="s">
+    <row r="85" spans="52:52">
+      <c r="AZ85" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="88" spans="51:51">
-      <c r="AY88" t="s">
+    <row r="86" spans="52:52">
+      <c r="AZ86" t="s">
         <v>528</v>
       </c>
     </row>
-    <row r="89" spans="51:51">
-      <c r="AY89" t="s">
+    <row r="87" spans="52:52">
+      <c r="AZ87" t="s">
         <v>529</v>
       </c>
     </row>
-    <row r="90" spans="51:51">
-      <c r="AY90" t="s">
+    <row r="88" spans="52:52">
+      <c r="AZ88" t="s">
         <v>530</v>
       </c>
     </row>
-    <row r="91" spans="51:51">
-      <c r="AY91" t="s">
+    <row r="89" spans="52:52">
+      <c r="AZ89" t="s">
         <v>531</v>
       </c>
     </row>
-    <row r="92" spans="51:51">
-      <c r="AY92" t="s">
+    <row r="90" spans="52:52">
+      <c r="AZ90" t="s">
         <v>532</v>
       </c>
     </row>
-    <row r="93" spans="51:51">
-      <c r="AY93" t="s">
+    <row r="91" spans="52:52">
+      <c r="AZ91" t="s">
         <v>533</v>
       </c>
     </row>
-    <row r="94" spans="51:51">
-      <c r="AY94" t="s">
+    <row r="92" spans="52:52">
+      <c r="AZ92" t="s">
         <v>534</v>
       </c>
     </row>
-    <row r="95" spans="51:51">
-      <c r="AY95" t="s">
+    <row r="93" spans="52:52">
+      <c r="AZ93" t="s">
         <v>535</v>
       </c>
     </row>
-    <row r="96" spans="51:51">
-      <c r="AY96" t="s">
+    <row r="94" spans="52:52">
+      <c r="AZ94" t="s">
         <v>536</v>
       </c>
     </row>
-    <row r="97" spans="51:51">
-      <c r="AY97" t="s">
+    <row r="95" spans="52:52">
+      <c r="AZ95" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="98" spans="51:51">
-      <c r="AY98" t="s">
+    <row r="96" spans="52:52">
+      <c r="AZ96" t="s">
         <v>538</v>
       </c>
     </row>
-    <row r="99" spans="51:51">
-      <c r="AY99" t="s">
+    <row r="97" spans="52:52">
+      <c r="AZ97" t="s">
         <v>539</v>
       </c>
     </row>
-    <row r="100" spans="51:51">
-      <c r="AY100" t="s">
+    <row r="98" spans="52:52">
+      <c r="AZ98" t="s">
         <v>540</v>
       </c>
     </row>
-    <row r="101" spans="51:51">
-      <c r="AY101" t="s">
+    <row r="99" spans="52:52">
+      <c r="AZ99" t="s">
         <v>541</v>
       </c>
     </row>
-    <row r="102" spans="51:51">
-      <c r="AY102" t="s">
+    <row r="100" spans="52:52">
+      <c r="AZ100" t="s">
         <v>542</v>
       </c>
     </row>
-    <row r="103" spans="51:51">
-      <c r="AY103" t="s">
+    <row r="101" spans="52:52">
+      <c r="AZ101" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="104" spans="51:51">
-      <c r="AY104" t="s">
+    <row r="102" spans="52:52">
+      <c r="AZ102" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="105" spans="51:51">
-      <c r="AY105" t="s">
+    <row r="103" spans="52:52">
+      <c r="AZ103" t="s">
         <v>545</v>
       </c>
     </row>
-    <row r="106" spans="51:51">
-      <c r="AY106" t="s">
+    <row r="104" spans="52:52">
+      <c r="AZ104" t="s">
         <v>546</v>
       </c>
     </row>
-    <row r="107" spans="51:51">
-      <c r="AY107" t="s">
+    <row r="105" spans="52:52">
+      <c r="AZ105" t="s">
         <v>547</v>
       </c>
     </row>
-    <row r="108" spans="51:51">
-      <c r="AY108" t="s">
+    <row r="106" spans="52:52">
+      <c r="AZ106" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="109" spans="51:51">
-      <c r="AY109" t="s">
+    <row r="107" spans="52:52">
+      <c r="AZ107" t="s">
         <v>549</v>
       </c>
     </row>
-    <row r="110" spans="51:51">
-      <c r="AY110" t="s">
+    <row r="108" spans="52:52">
+      <c r="AZ108" t="s">
         <v>550</v>
       </c>
     </row>
-    <row r="111" spans="51:51">
-      <c r="AY111" t="s">
+    <row r="109" spans="52:52">
+      <c r="AZ109" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="112" spans="51:51">
-      <c r="AY112" t="s">
+    <row r="110" spans="52:52">
+      <c r="AZ110" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="113" spans="51:51">
-      <c r="AY113" t="s">
+    <row r="111" spans="52:52">
+      <c r="AZ111" t="s">
         <v>553</v>
       </c>
     </row>
-    <row r="114" spans="51:51">
-      <c r="AY114" t="s">
+    <row r="112" spans="52:52">
+      <c r="AZ112" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="115" spans="51:51">
-      <c r="AY115" t="s">
+    <row r="113" spans="52:52">
+      <c r="AZ113" t="s">
         <v>555</v>
       </c>
     </row>
-    <row r="116" spans="51:51">
-      <c r="AY116" t="s">
+    <row r="114" spans="52:52">
+      <c r="AZ114" t="s">
         <v>556</v>
       </c>
     </row>
-    <row r="117" spans="51:51">
-      <c r="AY117" t="s">
+    <row r="115" spans="52:52">
+      <c r="AZ115" t="s">
         <v>557</v>
       </c>
     </row>
-    <row r="118" spans="51:51">
-      <c r="AY118" t="s">
+    <row r="116" spans="52:52">
+      <c r="AZ116" t="s">
         <v>558</v>
       </c>
     </row>
-    <row r="119" spans="51:51">
-      <c r="AY119" t="s">
+    <row r="117" spans="52:52">
+      <c r="AZ117" t="s">
         <v>559</v>
       </c>
     </row>
-    <row r="120" spans="51:51">
-      <c r="AY120" t="s">
+    <row r="118" spans="52:52">
+      <c r="AZ118" t="s">
         <v>560</v>
       </c>
     </row>
-    <row r="121" spans="51:51">
-      <c r="AY121" t="s">
+    <row r="119" spans="52:52">
+      <c r="AZ119" t="s">
         <v>561</v>
       </c>
     </row>
-    <row r="122" spans="51:51">
-      <c r="AY122" t="s">
+    <row r="120" spans="52:52">
+      <c r="AZ120" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="123" spans="51:51">
-      <c r="AY123" t="s">
+    <row r="121" spans="52:52">
+      <c r="AZ121" t="s">
         <v>563</v>
       </c>
     </row>
-    <row r="124" spans="51:51">
-      <c r="AY124" t="s">
+    <row r="122" spans="52:52">
+      <c r="AZ122" t="s">
         <v>564</v>
       </c>
     </row>
-    <row r="125" spans="51:51">
-      <c r="AY125" t="s">
+    <row r="123" spans="52:52">
+      <c r="AZ123" t="s">
         <v>565</v>
       </c>
     </row>
-    <row r="126" spans="51:51">
-      <c r="AY126" t="s">
+    <row r="124" spans="52:52">
+      <c r="AZ124" t="s">
         <v>566</v>
       </c>
     </row>
-    <row r="127" spans="51:51">
-      <c r="AY127" t="s">
+    <row r="125" spans="52:52">
+      <c r="AZ125" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="128" spans="51:51">
-      <c r="AY128" t="s">
+    <row r="126" spans="52:52">
+      <c r="AZ126" t="s">
         <v>568</v>
       </c>
     </row>
-    <row r="129" spans="51:51">
-      <c r="AY129" t="s">
+    <row r="127" spans="52:52">
+      <c r="AZ127" t="s">
         <v>569</v>
       </c>
     </row>
-    <row r="130" spans="51:51">
-      <c r="AY130" t="s">
+    <row r="128" spans="52:52">
+      <c r="AZ128" t="s">
         <v>570</v>
       </c>
     </row>
-    <row r="131" spans="51:51">
-      <c r="AY131" t="s">
+    <row r="129" spans="52:52">
+      <c r="AZ129" t="s">
         <v>571</v>
       </c>
     </row>
-    <row r="132" spans="51:51">
-      <c r="AY132" t="s">
+    <row r="130" spans="52:52">
+      <c r="AZ130" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="133" spans="51:51">
-      <c r="AY133" t="s">
+    <row r="131" spans="52:52">
+      <c r="AZ131" t="s">
         <v>573</v>
       </c>
     </row>
-    <row r="134" spans="51:51">
-      <c r="AY134" t="s">
+    <row r="132" spans="52:52">
+      <c r="AZ132" t="s">
         <v>574</v>
       </c>
     </row>
-    <row r="135" spans="51:51">
-      <c r="AY135" t="s">
+    <row r="133" spans="52:52">
+      <c r="AZ133" t="s">
         <v>575</v>
       </c>
     </row>
-    <row r="136" spans="51:51">
-      <c r="AY136" t="s">
+    <row r="134" spans="52:52">
+      <c r="AZ134" t="s">
         <v>576</v>
       </c>
     </row>
-    <row r="137" spans="51:51">
-      <c r="AY137" t="s">
+    <row r="135" spans="52:52">
+      <c r="AZ135" t="s">
         <v>577</v>
       </c>
     </row>
-    <row r="138" spans="51:51">
-      <c r="AY138" t="s">
+    <row r="136" spans="52:52">
+      <c r="AZ136" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="139" spans="51:51">
-      <c r="AY139" t="s">
+    <row r="137" spans="52:52">
+      <c r="AZ137" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="140" spans="51:51">
-      <c r="AY140" t="s">
+    <row r="138" spans="52:52">
+      <c r="AZ138" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="141" spans="51:51">
-      <c r="AY141" t="s">
+    <row r="139" spans="52:52">
+      <c r="AZ139" t="s">
         <v>581</v>
       </c>
     </row>
-    <row r="142" spans="51:51">
-      <c r="AY142" t="s">
+    <row r="140" spans="52:52">
+      <c r="AZ140" t="s">
         <v>582</v>
       </c>
     </row>
-    <row r="143" spans="51:51">
-      <c r="AY143" t="s">
+    <row r="141" spans="52:52">
+      <c r="AZ141" t="s">
         <v>583</v>
       </c>
     </row>
-    <row r="144" spans="51:51">
-      <c r="AY144" t="s">
+    <row r="142" spans="52:52">
+      <c r="AZ142" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="145" spans="51:51">
-      <c r="AY145" t="s">
+    <row r="143" spans="52:52">
+      <c r="AZ143" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="146" spans="51:51">
-      <c r="AY146" t="s">
+    <row r="144" spans="52:52">
+      <c r="AZ144" t="s">
         <v>586</v>
       </c>
     </row>
-    <row r="147" spans="51:51">
-      <c r="AY147" t="s">
+    <row r="145" spans="52:52">
+      <c r="AZ145" t="s">
         <v>587</v>
       </c>
     </row>
-    <row r="148" spans="51:51">
-      <c r="AY148" t="s">
+    <row r="146" spans="52:52">
+      <c r="AZ146" t="s">
         <v>588</v>
       </c>
     </row>
-    <row r="149" spans="51:51">
-      <c r="AY149" t="s">
+    <row r="147" spans="52:52">
+      <c r="AZ147" t="s">
         <v>589</v>
       </c>
     </row>
-    <row r="150" spans="51:51">
-      <c r="AY150" t="s">
+    <row r="148" spans="52:52">
+      <c r="AZ148" t="s">
         <v>590</v>
       </c>
     </row>
-    <row r="151" spans="51:51">
-      <c r="AY151" t="s">
+    <row r="149" spans="52:52">
+      <c r="AZ149" t="s">
         <v>591</v>
       </c>
     </row>
-    <row r="152" spans="51:51">
-      <c r="AY152" t="s">
+    <row r="150" spans="52:52">
+      <c r="AZ150" t="s">
         <v>592</v>
       </c>
     </row>
-    <row r="153" spans="51:51">
-      <c r="AY153" t="s">
+    <row r="151" spans="52:52">
+      <c r="AZ151" t="s">
         <v>593</v>
       </c>
     </row>
-    <row r="154" spans="51:51">
-      <c r="AY154" t="s">
+    <row r="152" spans="52:52">
+      <c r="AZ152" t="s">
         <v>594</v>
       </c>
     </row>
-    <row r="155" spans="51:51">
-      <c r="AY155" t="s">
+    <row r="153" spans="52:52">
+      <c r="AZ153" t="s">
         <v>595</v>
       </c>
     </row>
-    <row r="156" spans="51:51">
-      <c r="AY156" t="s">
+    <row r="154" spans="52:52">
+      <c r="AZ154" t="s">
         <v>596</v>
       </c>
     </row>
-    <row r="157" spans="51:51">
-      <c r="AY157" t="s">
+    <row r="155" spans="52:52">
+      <c r="AZ155" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="158" spans="51:51">
-      <c r="AY158" t="s">
+    <row r="156" spans="52:52">
+      <c r="AZ156" t="s">
         <v>598</v>
       </c>
     </row>
-    <row r="159" spans="51:51">
-      <c r="AY159" t="s">
+    <row r="157" spans="52:52">
+      <c r="AZ157" t="s">
         <v>599</v>
       </c>
     </row>
-    <row r="160" spans="51:51">
-      <c r="AY160" t="s">
+    <row r="158" spans="52:52">
+      <c r="AZ158" t="s">
         <v>600</v>
       </c>
     </row>
-    <row r="161" spans="51:51">
-      <c r="AY161" t="s">
+    <row r="159" spans="52:52">
+      <c r="AZ159" t="s">
         <v>601</v>
       </c>
     </row>
-    <row r="162" spans="51:51">
-      <c r="AY162" t="s">
+    <row r="160" spans="52:52">
+      <c r="AZ160" t="s">
         <v>602</v>
       </c>
     </row>
-    <row r="163" spans="51:51">
-      <c r="AY163" t="s">
+    <row r="161" spans="52:52">
+      <c r="AZ161" t="s">
         <v>603</v>
       </c>
     </row>
-    <row r="164" spans="51:51">
-      <c r="AY164" t="s">
+    <row r="162" spans="52:52">
+      <c r="AZ162" t="s">
         <v>604</v>
       </c>
     </row>
-    <row r="165" spans="51:51">
-      <c r="AY165" t="s">
+    <row r="163" spans="52:52">
+      <c r="AZ163" t="s">
         <v>605</v>
       </c>
     </row>
-    <row r="166" spans="51:51">
-      <c r="AY166" t="s">
+    <row r="164" spans="52:52">
+      <c r="AZ164" t="s">
         <v>606</v>
       </c>
     </row>
-    <row r="167" spans="51:51">
-      <c r="AY167" t="s">
+    <row r="165" spans="52:52">
+      <c r="AZ165" t="s">
         <v>607</v>
       </c>
     </row>
-    <row r="168" spans="51:51">
-      <c r="AY168" t="s">
+    <row r="166" spans="52:52">
+      <c r="AZ166" t="s">
         <v>608</v>
       </c>
     </row>
-    <row r="169" spans="51:51">
-      <c r="AY169" t="s">
+    <row r="167" spans="52:52">
+      <c r="AZ167" t="s">
         <v>609</v>
       </c>
     </row>
-    <row r="170" spans="51:51">
-      <c r="AY170" t="s">
+    <row r="168" spans="52:52">
+      <c r="AZ168" t="s">
         <v>610</v>
       </c>
     </row>
-    <row r="171" spans="51:51">
-      <c r="AY171" t="s">
+    <row r="169" spans="52:52">
+      <c r="AZ169" t="s">
         <v>611</v>
       </c>
     </row>
-    <row r="172" spans="51:51">
-      <c r="AY172" t="s">
+    <row r="170" spans="52:52">
+      <c r="AZ170" t="s">
         <v>612</v>
       </c>
     </row>
-    <row r="173" spans="51:51">
-      <c r="AY173" t="s">
+    <row r="171" spans="52:52">
+      <c r="AZ171" t="s">
         <v>613</v>
       </c>
     </row>
-    <row r="174" spans="51:51">
-      <c r="AY174" t="s">
+    <row r="172" spans="52:52">
+      <c r="AZ172" t="s">
         <v>614</v>
       </c>
     </row>
-    <row r="175" spans="51:51">
-      <c r="AY175" t="s">
+    <row r="173" spans="52:52">
+      <c r="AZ173" t="s">
         <v>615</v>
       </c>
     </row>
-    <row r="176" spans="51:51">
-      <c r="AY176" t="s">
+    <row r="174" spans="52:52">
+      <c r="AZ174" t="s">
         <v>616</v>
       </c>
     </row>
-    <row r="177" spans="51:51">
-      <c r="AY177" t="s">
+    <row r="175" spans="52:52">
+      <c r="AZ175" t="s">
         <v>617</v>
       </c>
     </row>
-    <row r="178" spans="51:51">
-      <c r="AY178" t="s">
+    <row r="176" spans="52:52">
+      <c r="AZ176" t="s">
         <v>618</v>
       </c>
     </row>
-    <row r="179" spans="51:51">
-      <c r="AY179" t="s">
+    <row r="177" spans="52:52">
+      <c r="AZ177" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="180" spans="51:51">
-      <c r="AY180" t="s">
+    <row r="178" spans="52:52">
+      <c r="AZ178" t="s">
         <v>620</v>
       </c>
     </row>
-    <row r="181" spans="51:51">
-      <c r="AY181" t="s">
+    <row r="179" spans="52:52">
+      <c r="AZ179" t="s">
         <v>621</v>
       </c>
     </row>
-    <row r="182" spans="51:51">
-      <c r="AY182" t="s">
+    <row r="180" spans="52:52">
+      <c r="AZ180" t="s">
         <v>622</v>
       </c>
     </row>
-    <row r="183" spans="51:51">
-      <c r="AY183" t="s">
+    <row r="181" spans="52:52">
+      <c r="AZ181" t="s">
         <v>623</v>
       </c>
     </row>
-    <row r="184" spans="51:51">
-      <c r="AY184" t="s">
+    <row r="182" spans="52:52">
+      <c r="AZ182" t="s">
         <v>624</v>
       </c>
     </row>
-    <row r="185" spans="51:51">
-      <c r="AY185" t="s">
+    <row r="183" spans="52:52">
+      <c r="AZ183" t="s">
         <v>625</v>
       </c>
     </row>
-    <row r="186" spans="51:51">
-      <c r="AY186" t="s">
+    <row r="184" spans="52:52">
+      <c r="AZ184" t="s">
         <v>626</v>
       </c>
     </row>
-    <row r="187" spans="51:51">
-      <c r="AY187" t="s">
+    <row r="185" spans="52:52">
+      <c r="AZ185" t="s">
         <v>627</v>
       </c>
     </row>
-    <row r="188" spans="51:51">
-      <c r="AY188" t="s">
+    <row r="186" spans="52:52">
+      <c r="AZ186" t="s">
         <v>628</v>
       </c>
     </row>
-    <row r="189" spans="51:51">
-      <c r="AY189" t="s">
+    <row r="187" spans="52:52">
+      <c r="AZ187" t="s">
         <v>629</v>
       </c>
     </row>
-    <row r="190" spans="51:51">
-      <c r="AY190" t="s">
+    <row r="188" spans="52:52">
+      <c r="AZ188" t="s">
         <v>630</v>
       </c>
     </row>
-    <row r="191" spans="51:51">
-      <c r="AY191" t="s">
+    <row r="189" spans="52:52">
+      <c r="AZ189" t="s">
         <v>631</v>
       </c>
     </row>
-    <row r="192" spans="51:51">
-      <c r="AY192" t="s">
+    <row r="190" spans="52:52">
+      <c r="AZ190" t="s">
         <v>632</v>
       </c>
     </row>
-    <row r="193" spans="51:51">
-      <c r="AY193" t="s">
+    <row r="191" spans="52:52">
+      <c r="AZ191" t="s">
         <v>633</v>
       </c>
     </row>
-    <row r="194" spans="51:51">
-      <c r="AY194" t="s">
+    <row r="192" spans="52:52">
+      <c r="AZ192" t="s">
         <v>634</v>
       </c>
     </row>
-    <row r="195" spans="51:51">
-      <c r="AY195" t="s">
+    <row r="193" spans="52:52">
+      <c r="AZ193" t="s">
         <v>635</v>
       </c>
     </row>
-    <row r="196" spans="51:51">
-      <c r="AY196" t="s">
+    <row r="194" spans="52:52">
+      <c r="AZ194" t="s">
         <v>636</v>
       </c>
     </row>
-    <row r="197" spans="51:51">
-      <c r="AY197" t="s">
+    <row r="195" spans="52:52">
+      <c r="AZ195" t="s">
         <v>637</v>
       </c>
     </row>
-    <row r="198" spans="51:51">
-      <c r="AY198" t="s">
+    <row r="196" spans="52:52">
+      <c r="AZ196" t="s">
         <v>638</v>
       </c>
     </row>
-    <row r="199" spans="51:51">
-      <c r="AY199" t="s">
+    <row r="197" spans="52:52">
+      <c r="AZ197" t="s">
         <v>639</v>
       </c>
     </row>
-    <row r="200" spans="51:51">
-      <c r="AY200" t="s">
+    <row r="198" spans="52:52">
+      <c r="AZ198" t="s">
         <v>640</v>
       </c>
     </row>
-    <row r="201" spans="51:51">
-      <c r="AY201" t="s">
+    <row r="199" spans="52:52">
+      <c r="AZ199" t="s">
         <v>641</v>
       </c>
     </row>
-    <row r="202" spans="51:51">
-      <c r="AY202" t="s">
+    <row r="200" spans="52:52">
+      <c r="AZ200" t="s">
         <v>642</v>
       </c>
     </row>
-    <row r="203" spans="51:51">
-      <c r="AY203" t="s">
+    <row r="201" spans="52:52">
+      <c r="AZ201" t="s">
         <v>643</v>
       </c>
     </row>
-    <row r="204" spans="51:51">
-      <c r="AY204" t="s">
+    <row r="202" spans="52:52">
+      <c r="AZ202" t="s">
         <v>644</v>
       </c>
     </row>
-    <row r="205" spans="51:51">
-      <c r="AY205" t="s">
+    <row r="203" spans="52:52">
+      <c r="AZ203" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="206" spans="51:51">
-      <c r="AY206" t="s">
+    <row r="204" spans="52:52">
+      <c r="AZ204" t="s">
         <v>646</v>
       </c>
     </row>
-    <row r="207" spans="51:51">
-      <c r="AY207" t="s">
+    <row r="205" spans="52:52">
+      <c r="AZ205" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="208" spans="51:51">
-      <c r="AY208" t="s">
+    <row r="206" spans="52:52">
+      <c r="AZ206" t="s">
         <v>648</v>
       </c>
     </row>
-    <row r="209" spans="51:51">
-      <c r="AY209" t="s">
+    <row r="207" spans="52:52">
+      <c r="AZ207" t="s">
         <v>649</v>
       </c>
     </row>
-    <row r="210" spans="51:51">
-      <c r="AY210" t="s">
+    <row r="208" spans="52:52">
+      <c r="AZ208" t="s">
         <v>650</v>
       </c>
     </row>
-    <row r="211" spans="51:51">
-      <c r="AY211" t="s">
+    <row r="209" spans="52:52">
+      <c r="AZ209" t="s">
         <v>651</v>
       </c>
     </row>
-    <row r="212" spans="51:51">
-      <c r="AY212" t="s">
+    <row r="210" spans="52:52">
+      <c r="AZ210" t="s">
         <v>652</v>
       </c>
     </row>
-    <row r="213" spans="51:51">
-      <c r="AY213" t="s">
+    <row r="211" spans="52:52">
+      <c r="AZ211" t="s">
         <v>653</v>
       </c>
     </row>
-    <row r="214" spans="51:51">
-      <c r="AY214" t="s">
+    <row r="212" spans="52:52">
+      <c r="AZ212" t="s">
         <v>654</v>
       </c>
     </row>
-    <row r="215" spans="51:51">
-      <c r="AY215" t="s">
+    <row r="213" spans="52:52">
+      <c r="AZ213" t="s">
         <v>655</v>
       </c>
     </row>
-    <row r="216" spans="51:51">
-      <c r="AY216" t="s">
+    <row r="214" spans="52:52">
+      <c r="AZ214" t="s">
         <v>656</v>
       </c>
     </row>
-    <row r="217" spans="51:51">
-      <c r="AY217" t="s">
+    <row r="215" spans="52:52">
+      <c r="AZ215" t="s">
         <v>657</v>
       </c>
     </row>
-    <row r="218" spans="51:51">
-      <c r="AY218" t="s">
+    <row r="216" spans="52:52">
+      <c r="AZ216" t="s">
         <v>658</v>
       </c>
     </row>
-    <row r="219" spans="51:51">
-      <c r="AY219" t="s">
+    <row r="217" spans="52:52">
+      <c r="AZ217" t="s">
         <v>659</v>
       </c>
     </row>
-    <row r="220" spans="51:51">
-      <c r="AY220" t="s">
+    <row r="218" spans="52:52">
+      <c r="AZ218" t="s">
         <v>660</v>
       </c>
     </row>
-    <row r="221" spans="51:51">
-      <c r="AY221" t="s">
+    <row r="219" spans="52:52">
+      <c r="AZ219" t="s">
         <v>661</v>
       </c>
     </row>
-    <row r="222" spans="51:51">
-      <c r="AY222" t="s">
+    <row r="220" spans="52:52">
+      <c r="AZ220" t="s">
         <v>662</v>
       </c>
     </row>
-    <row r="223" spans="51:51">
-      <c r="AY223" t="s">
+    <row r="221" spans="52:52">
+      <c r="AZ221" t="s">
         <v>663</v>
       </c>
     </row>
-    <row r="224" spans="51:51">
-      <c r="AY224" t="s">
+    <row r="222" spans="52:52">
+      <c r="AZ222" t="s">
         <v>664</v>
       </c>
     </row>
-    <row r="225" spans="51:51">
-      <c r="AY225" t="s">
+    <row r="223" spans="52:52">
+      <c r="AZ223" t="s">
         <v>665</v>
       </c>
     </row>
-    <row r="226" spans="51:51">
-      <c r="AY226" t="s">
+    <row r="224" spans="52:52">
+      <c r="AZ224" t="s">
         <v>666</v>
       </c>
     </row>
-    <row r="227" spans="51:51">
-      <c r="AY227" t="s">
+    <row r="225" spans="52:52">
+      <c r="AZ225" t="s">
         <v>667</v>
       </c>
     </row>
-    <row r="228" spans="51:51">
-      <c r="AY228" t="s">
+    <row r="226" spans="52:52">
+      <c r="AZ226" t="s">
         <v>668</v>
       </c>
     </row>
-    <row r="229" spans="51:51">
-      <c r="AY229" t="s">
+    <row r="227" spans="52:52">
+      <c r="AZ227" t="s">
         <v>669</v>
       </c>
     </row>
-    <row r="230" spans="51:51">
-      <c r="AY230" t="s">
+    <row r="228" spans="52:52">
+      <c r="AZ228" t="s">
         <v>670</v>
       </c>
     </row>
-    <row r="231" spans="51:51">
-      <c r="AY231" t="s">
+    <row r="229" spans="52:52">
+      <c r="AZ229" t="s">
         <v>671</v>
       </c>
     </row>
-    <row r="232" spans="51:51">
-      <c r="AY232" t="s">
+    <row r="230" spans="52:52">
+      <c r="AZ230" t="s">
         <v>672</v>
       </c>
     </row>
-    <row r="233" spans="51:51">
-      <c r="AY233" t="s">
+    <row r="231" spans="52:52">
+      <c r="AZ231" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="234" spans="51:51">
-      <c r="AY234" t="s">
+    <row r="232" spans="52:52">
+      <c r="AZ232" t="s">
         <v>674</v>
       </c>
     </row>
-    <row r="235" spans="51:51">
-      <c r="AY235" t="s">
+    <row r="233" spans="52:52">
+      <c r="AZ233" t="s">
         <v>675</v>
       </c>
     </row>
-    <row r="236" spans="51:51">
-      <c r="AY236" t="s">
+    <row r="234" spans="52:52">
+      <c r="AZ234" t="s">
         <v>676</v>
       </c>
     </row>
-    <row r="237" spans="51:51">
-      <c r="AY237" t="s">
+    <row r="235" spans="52:52">
+      <c r="AZ235" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="238" spans="51:51">
-      <c r="AY238" t="s">
+    <row r="236" spans="52:52">
+      <c r="AZ236" t="s">
         <v>678</v>
       </c>
     </row>
-    <row r="239" spans="51:51">
-      <c r="AY239" t="s">
+    <row r="237" spans="52:52">
+      <c r="AZ237" t="s">
         <v>679</v>
       </c>
     </row>
-    <row r="240" spans="51:51">
-      <c r="AY240" t="s">
+    <row r="238" spans="52:52">
+      <c r="AZ238" t="s">
         <v>680</v>
       </c>
     </row>
-    <row r="241" spans="51:51">
-      <c r="AY241" t="s">
+    <row r="239" spans="52:52">
+      <c r="AZ239" t="s">
         <v>681</v>
       </c>
     </row>
-    <row r="242" spans="51:51">
-      <c r="AY242" t="s">
+    <row r="240" spans="52:52">
+      <c r="AZ240" t="s">
         <v>682</v>
       </c>
     </row>
-    <row r="243" spans="51:51">
-      <c r="AY243" t="s">
+    <row r="241" spans="52:52">
+      <c r="AZ241" t="s">
         <v>683</v>
       </c>
     </row>
-    <row r="244" spans="51:51">
-      <c r="AY244" t="s">
+    <row r="242" spans="52:52">
+      <c r="AZ242" t="s">
         <v>684</v>
       </c>
     </row>
-    <row r="245" spans="51:51">
-      <c r="AY245" t="s">
+    <row r="243" spans="52:52">
+      <c r="AZ243" t="s">
         <v>685</v>
       </c>
     </row>
-    <row r="246" spans="51:51">
-      <c r="AY246" t="s">
+    <row r="244" spans="52:52">
+      <c r="AZ244" t="s">
         <v>686</v>
       </c>
     </row>
-    <row r="247" spans="51:51">
-      <c r="AY247" t="s">
+    <row r="245" spans="52:52">
+      <c r="AZ245" t="s">
         <v>687</v>
       </c>
     </row>
-    <row r="248" spans="51:51">
-      <c r="AY248" t="s">
+    <row r="246" spans="52:52">
+      <c r="AZ246" t="s">
         <v>688</v>
       </c>
     </row>
-    <row r="249" spans="51:51">
-      <c r="AY249" t="s">
+    <row r="247" spans="52:52">
+      <c r="AZ247" t="s">
         <v>689</v>
       </c>
     </row>
-    <row r="250" spans="51:51">
-      <c r="AY250" t="s">
+    <row r="248" spans="52:52">
+      <c r="AZ248" t="s">
         <v>690</v>
       </c>
     </row>
-    <row r="251" spans="51:51">
-      <c r="AY251" t="s">
+    <row r="249" spans="52:52">
+      <c r="AZ249" t="s">
         <v>691</v>
       </c>
     </row>
-    <row r="252" spans="51:51">
-      <c r="AY252" t="s">
+    <row r="250" spans="52:52">
+      <c r="AZ250" t="s">
         <v>692</v>
       </c>
     </row>
-    <row r="253" spans="51:51">
-      <c r="AY253" t="s">
+    <row r="251" spans="52:52">
+      <c r="AZ251" t="s">
         <v>693</v>
       </c>
     </row>
-    <row r="254" spans="51:51">
-      <c r="AY254" t="s">
+    <row r="252" spans="52:52">
+      <c r="AZ252" t="s">
         <v>694</v>
       </c>
     </row>
-    <row r="255" spans="51:51">
-      <c r="AY255" t="s">
+    <row r="253" spans="52:52">
+      <c r="AZ253" t="s">
         <v>695</v>
       </c>
     </row>
-    <row r="256" spans="51:51">
-      <c r="AY256" t="s">
+    <row r="254" spans="52:52">
+      <c r="AZ254" t="s">
         <v>696</v>
       </c>
     </row>
-    <row r="257" spans="51:51">
-      <c r="AY257" t="s">
+    <row r="255" spans="52:52">
+      <c r="AZ255" t="s">
         <v>697</v>
       </c>
     </row>
-    <row r="258" spans="51:51">
-      <c r="AY258" t="s">
+    <row r="256" spans="52:52">
+      <c r="AZ256" t="s">
         <v>698</v>
       </c>
     </row>
-    <row r="259" spans="51:51">
-      <c r="AY259" t="s">
+    <row r="257" spans="52:52">
+      <c r="AZ257" t="s">
         <v>699</v>
       </c>
     </row>
-    <row r="260" spans="51:51">
-      <c r="AY260" t="s">
+    <row r="258" spans="52:52">
+      <c r="AZ258" t="s">
         <v>700</v>
       </c>
     </row>
-    <row r="261" spans="51:51">
-      <c r="AY261" t="s">
+    <row r="259" spans="52:52">
+      <c r="AZ259" t="s">
         <v>701</v>
       </c>
     </row>
-    <row r="262" spans="51:51">
-      <c r="AY262" t="s">
+    <row r="260" spans="52:52">
+      <c r="AZ260" t="s">
         <v>702</v>
       </c>
     </row>
-    <row r="263" spans="51:51">
-      <c r="AY263" t="s">
+    <row r="261" spans="52:52">
+      <c r="AZ261" t="s">
         <v>703</v>
       </c>
     </row>
-    <row r="264" spans="51:51">
-      <c r="AY264" t="s">
+    <row r="262" spans="52:52">
+      <c r="AZ262" t="s">
         <v>704</v>
       </c>
     </row>
-    <row r="265" spans="51:51">
-      <c r="AY265" t="s">
+    <row r="263" spans="52:52">
+      <c r="AZ263" t="s">
         <v>705</v>
       </c>
     </row>
-    <row r="266" spans="51:51">
-      <c r="AY266" t="s">
+    <row r="264" spans="52:52">
+      <c r="AZ264" t="s">
         <v>706</v>
       </c>
     </row>
-    <row r="267" spans="51:51">
-      <c r="AY267" t="s">
+    <row r="265" spans="52:52">
+      <c r="AZ265" t="s">
         <v>707</v>
       </c>
     </row>
-    <row r="268" spans="51:51">
-      <c r="AY268" t="s">
+    <row r="266" spans="52:52">
+      <c r="AZ266" t="s">
         <v>708</v>
       </c>
     </row>
-    <row r="269" spans="51:51">
-      <c r="AY269" t="s">
+    <row r="267" spans="52:52">
+      <c r="AZ267" t="s">
         <v>709</v>
       </c>
     </row>
-    <row r="270" spans="51:51">
-      <c r="AY270" t="s">
+    <row r="268" spans="52:52">
+      <c r="AZ268" t="s">
         <v>710</v>
       </c>
     </row>
-    <row r="271" spans="51:51">
-      <c r="AY271" t="s">
+    <row r="269" spans="52:52">
+      <c r="AZ269" t="s">
         <v>711</v>
       </c>
     </row>
-    <row r="272" spans="51:51">
-      <c r="AY272" t="s">
+    <row r="270" spans="52:52">
+      <c r="AZ270" t="s">
         <v>712</v>
       </c>
     </row>
-    <row r="273" spans="51:51">
-      <c r="AY273" t="s">
+    <row r="271" spans="52:52">
+      <c r="AZ271" t="s">
         <v>713</v>
       </c>
     </row>
-    <row r="274" spans="51:51">
-      <c r="AY274" t="s">
+    <row r="272" spans="52:52">
+      <c r="AZ272" t="s">
         <v>714</v>
       </c>
     </row>
-    <row r="275" spans="51:51">
-      <c r="AY275" t="s">
+    <row r="273" spans="52:52">
+      <c r="AZ273" t="s">
         <v>715</v>
       </c>
     </row>
-    <row r="276" spans="51:51">
-      <c r="AY276" t="s">
+    <row r="274" spans="52:52">
+      <c r="AZ274" t="s">
         <v>716</v>
       </c>
     </row>
-    <row r="277" spans="51:51">
-      <c r="AY277" t="s">
+    <row r="275" spans="52:52">
+      <c r="AZ275" t="s">
         <v>717</v>
       </c>
     </row>
-    <row r="278" spans="51:51">
-      <c r="AY278" t="s">
+    <row r="276" spans="52:52">
+      <c r="AZ276" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="279" spans="51:51">
-      <c r="AY279" t="s">
+    <row r="277" spans="52:52">
+      <c r="AZ277" t="s">
         <v>719</v>
       </c>
     </row>
-    <row r="280" spans="51:51">
-      <c r="AY280" t="s">
+    <row r="278" spans="52:52">
+      <c r="AZ278" t="s">
         <v>720</v>
       </c>
     </row>
-    <row r="281" spans="51:51">
-      <c r="AY281" t="s">
+    <row r="279" spans="52:52">
+      <c r="AZ279" t="s">
         <v>721</v>
       </c>
     </row>
-    <row r="282" spans="51:51">
-      <c r="AY282" t="s">
+    <row r="280" spans="52:52">
+      <c r="AZ280" t="s">
         <v>722</v>
       </c>
     </row>
-    <row r="283" spans="51:51">
-      <c r="AY283" t="s">
+    <row r="281" spans="52:52">
+      <c r="AZ281" t="s">
         <v>723</v>
       </c>
     </row>
-    <row r="284" spans="51:51">
-      <c r="AY284" t="s">
+    <row r="282" spans="52:52">
+      <c r="AZ282" t="s">
         <v>724</v>
       </c>
     </row>
-    <row r="285" spans="51:51">
-      <c r="AY285" t="s">
+    <row r="283" spans="52:52">
+      <c r="AZ283" t="s">
         <v>725</v>
       </c>
     </row>
-    <row r="286" spans="51:51">
-      <c r="AY286" t="s">
+    <row r="284" spans="52:52">
+      <c r="AZ284" t="s">
         <v>726</v>
       </c>
     </row>
-    <row r="287" spans="51:51">
-      <c r="AY287" t="s">
+    <row r="285" spans="52:52">
+      <c r="AZ285" t="s">
         <v>727</v>
       </c>
     </row>
-    <row r="288" spans="51:51">
-      <c r="AY288" t="s">
+    <row r="286" spans="52:52">
+      <c r="AZ286" t="s">
         <v>728</v>
       </c>
     </row>
-    <row r="289" spans="51:51">
-      <c r="AY289" t="s">
+    <row r="287" spans="52:52">
+      <c r="AZ287" t="s">
         <v>729</v>
       </c>
     </row>
-    <row r="290" spans="51:51">
-      <c r="AY290" t="s">
+    <row r="288" spans="52:52">
+      <c r="AZ288" t="s">
         <v>730</v>
       </c>
     </row>
-    <row r="291" spans="51:51">
-      <c r="AY291" t="s">
+    <row r="289" spans="52:52">
+      <c r="AZ289" t="s">
         <v>731</v>
       </c>
     </row>
-    <row r="292" spans="51:51">
-      <c r="AY292" t="s">
+    <row r="290" spans="52:52">
+      <c r="AZ290" t="s">
         <v>732</v>
       </c>
     </row>
-    <row r="293" spans="51:51">
-      <c r="AY293" t="s">
+    <row r="291" spans="52:52">
+      <c r="AZ291" t="s">
         <v>733</v>
       </c>
     </row>
-    <row r="294" spans="51:51">
-      <c r="AY294" t="s">
+    <row r="292" spans="52:52">
+      <c r="AZ292" t="s">
         <v>734</v>
+      </c>
+    </row>
+    <row r="293" spans="52:52">
+      <c r="AZ293" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="294" spans="52:52">
+      <c r="AZ294" t="s">
+        <v>736</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000022/metadata_template_ERC000022.xlsx
+++ b/templates/ERC000022/metadata_template_ERC000022.xlsx
@@ -19,14 +19,14 @@
   <definedNames>
     <definedName name="drainageclassification">'cv_sample'!$BJ$1:$BJ$6</definedName>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AZ$1:$AZ$289</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AZ$1:$AZ$294</definedName>
     <definedName name="historytillage">'cv_sample'!$CE$1:$CE$9</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
     <definedName name="observedbioticrelationship">'cv_sample'!$H$1:$H$5</definedName>
-    <definedName name="platform">'cv_experiment'!$M$1:$M$17</definedName>
+    <definedName name="platform">'cv_experiment'!$M$1:$M$18</definedName>
     <definedName name="profileposition">'cv_sample'!$BQ$1:$BQ$5</definedName>
     <definedName name="relationshiptooxygen">'cv_sample'!$J$1:$J$7</definedName>
     <definedName name="sequencequalitycheck">'cv_sample'!$AE$1:$AE$3</definedName>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="884">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="899" uniqueCount="891">
   <si>
     <t>alias</t>
   </si>
@@ -456,6 +456,9 @@
     <t>ELEMENT</t>
   </si>
   <si>
+    <t>AVITI</t>
+  </si>
+  <si>
     <t>ULTIMA</t>
   </si>
   <si>
@@ -546,6 +549,9 @@
     <t>AB SOLiD System 3.0</t>
   </si>
   <si>
+    <t>AVITI 24</t>
+  </si>
+  <si>
     <t>BGISEQ-50</t>
   </si>
   <si>
@@ -1578,9 +1584,6 @@
     <t>Dominican Republic</t>
   </si>
   <si>
-    <t>East Timor</t>
-  </si>
-  <si>
     <t>Ecuador</t>
   </si>
   <si>
@@ -1599,6 +1602,9 @@
     <t>Estonia</t>
   </si>
   <si>
+    <t>Eswatini</t>
+  </si>
+  <si>
     <t>Ethiopia</t>
   </si>
   <si>
@@ -1800,6 +1806,9 @@
     <t>Liechtenstein</t>
   </si>
   <si>
+    <t>Line Islands</t>
+  </si>
+  <si>
     <t>Lithuania</t>
   </si>
   <si>
@@ -1809,9 +1818,6 @@
     <t>Macau</t>
   </si>
   <si>
-    <t>Macedonia</t>
-  </si>
-  <si>
     <t>Madagascar</t>
   </si>
   <si>
@@ -1851,7 +1857,7 @@
     <t>Mexico</t>
   </si>
   <si>
-    <t>Micronesia</t>
+    <t>Micronesia, Federated States of</t>
   </si>
   <si>
     <t>Midway Islands</t>
@@ -1920,6 +1926,9 @@
     <t>North Korea</t>
   </si>
   <si>
+    <t>North Macedonia</t>
+  </si>
+  <si>
     <t>North Sea</t>
   </si>
   <si>
@@ -1995,6 +2004,9 @@
     <t>Rwanda</t>
   </si>
   <si>
+    <t>Saint Barthelemy</t>
+  </si>
+  <si>
     <t>Saint Helena</t>
   </si>
   <si>
@@ -2016,6 +2028,9 @@
     <t>San Marino</t>
   </si>
   <si>
+    <t>Saint Martin</t>
+  </si>
+  <si>
     <t>Sao Tome and Principe</t>
   </si>
   <si>
@@ -2061,6 +2076,9 @@
     <t>South Korea</t>
   </si>
   <si>
+    <t>South Sudan</t>
+  </si>
+  <si>
     <t>Southern Ocean</t>
   </si>
   <si>
@@ -2073,6 +2091,9 @@
     <t>Sri Lanka</t>
   </si>
   <si>
+    <t>State of Palestine</t>
+  </si>
+  <si>
     <t>Sudan</t>
   </si>
   <si>
@@ -2082,9 +2103,6 @@
     <t>Svalbard</t>
   </si>
   <si>
-    <t>Swaziland</t>
-  </si>
-  <si>
     <t>Sweden</t>
   </si>
   <si>
@@ -2109,6 +2127,9 @@
     <t>Thailand</t>
   </si>
   <si>
+    <t>Timor-Leste</t>
+  </si>
+  <si>
     <t>Togo</t>
   </si>
   <si>
@@ -2169,10 +2190,10 @@
     <t>Viet Nam</t>
   </si>
   <si>
+    <t>Wake Island</t>
+  </si>
+  <si>
     <t>Virgin Islands</t>
-  </si>
-  <si>
-    <t>Wake Island</t>
   </si>
   <si>
     <t>Wallis and Futuna</t>
@@ -3218,10 +3239,10 @@
         <v>124</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -3262,10 +3283,10 @@
         <v>125</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -3292,7 +3313,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N87"/>
+  <dimension ref="G1:N88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -3309,7 +3330,7 @@
         <v>126</v>
       </c>
       <c r="N1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="7:14">
@@ -3326,7 +3347,7 @@
         <v>127</v>
       </c>
       <c r="N2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="7:14">
@@ -3343,7 +3364,7 @@
         <v>128</v>
       </c>
       <c r="N3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="7:14">
@@ -3360,7 +3381,7 @@
         <v>129</v>
       </c>
       <c r="N4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="7:14">
@@ -3377,7 +3398,7 @@
         <v>130</v>
       </c>
       <c r="N5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="7:14">
@@ -3394,7 +3415,7 @@
         <v>131</v>
       </c>
       <c r="N6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="7:14">
@@ -3411,7 +3432,7 @@
         <v>132</v>
       </c>
       <c r="N7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="7:14">
@@ -3428,7 +3449,7 @@
         <v>133</v>
       </c>
       <c r="N8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="7:14">
@@ -3445,7 +3466,7 @@
         <v>134</v>
       </c>
       <c r="N9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="7:14">
@@ -3459,7 +3480,7 @@
         <v>135</v>
       </c>
       <c r="N10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="7:14">
@@ -3473,7 +3494,7 @@
         <v>136</v>
       </c>
       <c r="N11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="7:14">
@@ -3487,7 +3508,7 @@
         <v>137</v>
       </c>
       <c r="N12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="7:14">
@@ -3501,7 +3522,7 @@
         <v>138</v>
       </c>
       <c r="N13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="7:14">
@@ -3515,7 +3536,7 @@
         <v>139</v>
       </c>
       <c r="N14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="7:14">
@@ -3529,7 +3550,7 @@
         <v>140</v>
       </c>
       <c r="N15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="7:14">
@@ -3543,7 +3564,7 @@
         <v>141</v>
       </c>
       <c r="N16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="7:14">
@@ -3557,7 +3578,7 @@
         <v>142</v>
       </c>
       <c r="N17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="7:14">
@@ -3567,8 +3588,11 @@
       <c r="I18" t="s">
         <v>54</v>
       </c>
+      <c r="M18" t="s">
+        <v>143</v>
+      </c>
       <c r="N18" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="7:14">
@@ -3579,7 +3603,7 @@
         <v>105</v>
       </c>
       <c r="N19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="7:14">
@@ -3590,7 +3614,7 @@
         <v>106</v>
       </c>
       <c r="N20" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="7:14">
@@ -3601,7 +3625,7 @@
         <v>107</v>
       </c>
       <c r="N21" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="7:14">
@@ -3612,7 +3636,7 @@
         <v>108</v>
       </c>
       <c r="N22" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="7:14">
@@ -3623,7 +3647,7 @@
         <v>109</v>
       </c>
       <c r="N23" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24" spans="7:14">
@@ -3634,7 +3658,7 @@
         <v>110</v>
       </c>
       <c r="N24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="7:14">
@@ -3645,7 +3669,7 @@
         <v>111</v>
       </c>
       <c r="N25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" spans="7:14">
@@ -3656,7 +3680,7 @@
         <v>112</v>
       </c>
       <c r="N26" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="7:14">
@@ -3667,7 +3691,7 @@
         <v>113</v>
       </c>
       <c r="N27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="7:14">
@@ -3678,7 +3702,7 @@
         <v>114</v>
       </c>
       <c r="N28" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="7:14">
@@ -3689,7 +3713,7 @@
         <v>115</v>
       </c>
       <c r="N29" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="7:14">
@@ -3700,7 +3724,7 @@
         <v>116</v>
       </c>
       <c r="N30" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="7:14">
@@ -3711,7 +3735,7 @@
         <v>117</v>
       </c>
       <c r="N31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="7:14">
@@ -3719,7 +3743,7 @@
         <v>66</v>
       </c>
       <c r="N32" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="7:14">
@@ -3727,7 +3751,7 @@
         <v>67</v>
       </c>
       <c r="N33" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="7:14">
@@ -3735,7 +3759,7 @@
         <v>68</v>
       </c>
       <c r="N34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="7:14">
@@ -3743,7 +3767,7 @@
         <v>69</v>
       </c>
       <c r="N35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="7:14">
@@ -3751,7 +3775,7 @@
         <v>70</v>
       </c>
       <c r="N36" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" spans="7:14">
@@ -3759,7 +3783,7 @@
         <v>71</v>
       </c>
       <c r="N37" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="38" spans="7:14">
@@ -3767,7 +3791,7 @@
         <v>72</v>
       </c>
       <c r="N38" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39" spans="7:14">
@@ -3775,7 +3799,7 @@
         <v>73</v>
       </c>
       <c r="N39" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40" spans="7:14">
@@ -3783,7 +3807,7 @@
         <v>74</v>
       </c>
       <c r="N40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="41" spans="7:14">
@@ -3791,236 +3815,241 @@
         <v>75</v>
       </c>
       <c r="N41" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="7:14">
       <c r="N42" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="43" spans="7:14">
       <c r="N43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="7:14">
       <c r="N44" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="7:14">
       <c r="N45" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="46" spans="7:14">
       <c r="N46" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="47" spans="7:14">
       <c r="N47" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="48" spans="7:14">
       <c r="N48" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="49" spans="14:14">
       <c r="N49" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="50" spans="14:14">
       <c r="N50" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="14:14">
       <c r="N51" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="52" spans="14:14">
       <c r="N52" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="53" spans="14:14">
       <c r="N53" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="54" spans="14:14">
       <c r="N54" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="55" spans="14:14">
       <c r="N55" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="56" spans="14:14">
       <c r="N56" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57" spans="14:14">
       <c r="N57" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="58" spans="14:14">
       <c r="N58" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="59" spans="14:14">
       <c r="N59" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="60" spans="14:14">
       <c r="N60" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" spans="14:14">
       <c r="N61" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="62" spans="14:14">
       <c r="N62" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="63" spans="14:14">
       <c r="N63" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="64" spans="14:14">
       <c r="N64" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="65" spans="14:14">
       <c r="N65" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="66" spans="14:14">
       <c r="N66" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="67" spans="14:14">
       <c r="N67" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="68" spans="14:14">
       <c r="N68" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="69" spans="14:14">
       <c r="N69" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="70" spans="14:14">
       <c r="N70" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="71" spans="14:14">
       <c r="N71" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="72" spans="14:14">
       <c r="N72" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="73" spans="14:14">
       <c r="N73" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="74" spans="14:14">
       <c r="N74" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="75" spans="14:14">
       <c r="N75" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="76" spans="14:14">
       <c r="N76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="77" spans="14:14">
       <c r="N77" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="78" spans="14:14">
       <c r="N78" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="79" spans="14:14">
       <c r="N79" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="80" spans="14:14">
       <c r="N80" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="81" spans="14:14">
       <c r="N81" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="82" spans="14:14">
       <c r="N82" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="83" spans="14:14">
       <c r="N83" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="84" spans="14:14">
       <c r="N84" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="85" spans="14:14">
       <c r="N85" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="86" spans="14:14">
       <c r="N86" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="87" spans="14:14">
       <c r="N87" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="88" spans="14:14">
+      <c r="N88" t="s">
         <v>117</v>
       </c>
     </row>
@@ -4042,27 +4071,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -4082,122 +4111,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -4221,690 +4250,690 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>730</v>
+        <v>737</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>732</v>
+        <v>739</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>734</v>
+        <v>741</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>736</v>
+        <v>743</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>738</v>
+        <v>745</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>740</v>
+        <v>747</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>742</v>
+        <v>749</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>744</v>
+        <v>751</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>746</v>
+        <v>753</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>754</v>
+        <v>761</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>762</v>
+        <v>769</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>764</v>
+        <v>771</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>766</v>
+        <v>773</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>768</v>
+        <v>775</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>770</v>
+        <v>777</v>
       </c>
       <c r="BO1" s="1" t="s">
-        <v>772</v>
+        <v>779</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>774</v>
+        <v>781</v>
       </c>
       <c r="BQ1" s="1" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="BS1" s="1" t="s">
-        <v>785</v>
+        <v>792</v>
       </c>
       <c r="BT1" s="1" t="s">
-        <v>787</v>
+        <v>794</v>
       </c>
       <c r="BU1" s="1" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="BV1" s="1" t="s">
-        <v>791</v>
+        <v>798</v>
       </c>
       <c r="BW1" s="1" t="s">
-        <v>793</v>
+        <v>800</v>
       </c>
       <c r="BX1" s="1" t="s">
-        <v>795</v>
+        <v>802</v>
       </c>
       <c r="BY1" s="1" t="s">
-        <v>797</v>
+        <v>804</v>
       </c>
       <c r="BZ1" s="1" t="s">
-        <v>799</v>
+        <v>806</v>
       </c>
       <c r="CA1" s="1" t="s">
-        <v>801</v>
+        <v>808</v>
       </c>
       <c r="CB1" s="1" t="s">
-        <v>803</v>
+        <v>810</v>
       </c>
       <c r="CC1" s="1" t="s">
-        <v>805</v>
+        <v>812</v>
       </c>
       <c r="CD1" s="1" t="s">
-        <v>807</v>
+        <v>814</v>
       </c>
       <c r="CE1" s="1" t="s">
-        <v>818</v>
+        <v>825</v>
       </c>
       <c r="CF1" s="1" t="s">
-        <v>820</v>
+        <v>827</v>
       </c>
       <c r="CG1" s="1" t="s">
-        <v>822</v>
+        <v>829</v>
       </c>
       <c r="CH1" s="1" t="s">
-        <v>824</v>
+        <v>831</v>
       </c>
       <c r="CI1" s="1" t="s">
-        <v>826</v>
+        <v>833</v>
       </c>
       <c r="CJ1" s="1" t="s">
-        <v>828</v>
+        <v>835</v>
       </c>
       <c r="CK1" s="1" t="s">
-        <v>830</v>
+        <v>837</v>
       </c>
       <c r="CL1" s="1" t="s">
-        <v>832</v>
+        <v>839</v>
       </c>
       <c r="CM1" s="1" t="s">
-        <v>834</v>
+        <v>841</v>
       </c>
       <c r="CN1" s="1" t="s">
-        <v>836</v>
+        <v>843</v>
       </c>
       <c r="CO1" s="1" t="s">
-        <v>838</v>
+        <v>845</v>
       </c>
       <c r="CP1" s="1" t="s">
-        <v>840</v>
+        <v>847</v>
       </c>
       <c r="CQ1" s="1" t="s">
-        <v>842</v>
+        <v>849</v>
       </c>
       <c r="CR1" s="1" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
       <c r="CS1" s="1" t="s">
-        <v>846</v>
+        <v>853</v>
       </c>
       <c r="CT1" s="1" t="s">
-        <v>848</v>
+        <v>855</v>
       </c>
       <c r="CU1" s="1" t="s">
-        <v>850</v>
+        <v>857</v>
       </c>
       <c r="CV1" s="1" t="s">
-        <v>852</v>
+        <v>859</v>
       </c>
       <c r="CW1" s="1" t="s">
-        <v>854</v>
+        <v>861</v>
       </c>
       <c r="CX1" s="1" t="s">
-        <v>856</v>
+        <v>863</v>
       </c>
       <c r="CY1" s="1" t="s">
-        <v>858</v>
+        <v>865</v>
       </c>
       <c r="CZ1" s="1" t="s">
-        <v>860</v>
+        <v>867</v>
       </c>
       <c r="DA1" s="1" t="s">
-        <v>862</v>
+        <v>869</v>
       </c>
       <c r="DB1" s="1" t="s">
-        <v>864</v>
+        <v>871</v>
       </c>
       <c r="DC1" s="1" t="s">
-        <v>866</v>
+        <v>873</v>
       </c>
       <c r="DD1" s="1" t="s">
-        <v>868</v>
+        <v>875</v>
       </c>
       <c r="DE1" s="1" t="s">
-        <v>870</v>
+        <v>877</v>
       </c>
       <c r="DF1" s="1" t="s">
-        <v>872</v>
+        <v>879</v>
       </c>
       <c r="DG1" s="1" t="s">
-        <v>874</v>
+        <v>881</v>
       </c>
       <c r="DH1" s="1" t="s">
-        <v>876</v>
+        <v>883</v>
       </c>
       <c r="DI1" s="1" t="s">
-        <v>878</v>
+        <v>885</v>
       </c>
       <c r="DJ1" s="1" t="s">
-        <v>880</v>
+        <v>887</v>
       </c>
       <c r="DK1" s="1" t="s">
-        <v>882</v>
+        <v>889</v>
       </c>
     </row>
     <row r="2" spans="1:115" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AS2" s="2" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AU2" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="AW2" s="2" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AX2" s="2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AY2" s="2" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AZ2" s="2" t="s">
-        <v>731</v>
+        <v>738</v>
       </c>
       <c r="BA2" s="2" t="s">
-        <v>733</v>
+        <v>740</v>
       </c>
       <c r="BB2" s="2" t="s">
-        <v>735</v>
+        <v>742</v>
       </c>
       <c r="BC2" s="2" t="s">
-        <v>737</v>
+        <v>744</v>
       </c>
       <c r="BD2" s="2" t="s">
-        <v>739</v>
+        <v>746</v>
       </c>
       <c r="BE2" s="2" t="s">
-        <v>741</v>
+        <v>748</v>
       </c>
       <c r="BF2" s="2" t="s">
-        <v>743</v>
+        <v>750</v>
       </c>
       <c r="BG2" s="2" t="s">
-        <v>745</v>
+        <v>752</v>
       </c>
       <c r="BH2" s="2" t="s">
-        <v>747</v>
+        <v>754</v>
       </c>
       <c r="BI2" s="2" t="s">
-        <v>755</v>
+        <v>762</v>
       </c>
       <c r="BJ2" s="2" t="s">
-        <v>763</v>
+        <v>770</v>
       </c>
       <c r="BK2" s="2" t="s">
-        <v>765</v>
+        <v>772</v>
       </c>
       <c r="BL2" s="2" t="s">
-        <v>767</v>
+        <v>774</v>
       </c>
       <c r="BM2" s="2" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="BN2" s="2" t="s">
-        <v>771</v>
+        <v>778</v>
       </c>
       <c r="BO2" s="2" t="s">
-        <v>773</v>
+        <v>780</v>
       </c>
       <c r="BP2" s="2" t="s">
-        <v>775</v>
+        <v>782</v>
       </c>
       <c r="BQ2" s="2" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="BR2" s="2" t="s">
-        <v>784</v>
+        <v>791</v>
       </c>
       <c r="BS2" s="2" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="BT2" s="2" t="s">
-        <v>788</v>
+        <v>795</v>
       </c>
       <c r="BU2" s="2" t="s">
-        <v>790</v>
+        <v>797</v>
       </c>
       <c r="BV2" s="2" t="s">
-        <v>792</v>
+        <v>799</v>
       </c>
       <c r="BW2" s="2" t="s">
-        <v>794</v>
+        <v>801</v>
       </c>
       <c r="BX2" s="2" t="s">
-        <v>796</v>
+        <v>803</v>
       </c>
       <c r="BY2" s="2" t="s">
-        <v>798</v>
+        <v>805</v>
       </c>
       <c r="BZ2" s="2" t="s">
-        <v>800</v>
+        <v>807</v>
       </c>
       <c r="CA2" s="2" t="s">
-        <v>802</v>
+        <v>809</v>
       </c>
       <c r="CB2" s="2" t="s">
-        <v>804</v>
+        <v>811</v>
       </c>
       <c r="CC2" s="2" t="s">
-        <v>806</v>
+        <v>813</v>
       </c>
       <c r="CD2" s="2" t="s">
-        <v>808</v>
+        <v>815</v>
       </c>
       <c r="CE2" s="2" t="s">
-        <v>819</v>
+        <v>826</v>
       </c>
       <c r="CF2" s="2" t="s">
-        <v>821</v>
+        <v>828</v>
       </c>
       <c r="CG2" s="2" t="s">
-        <v>823</v>
+        <v>830</v>
       </c>
       <c r="CH2" s="2" t="s">
-        <v>825</v>
+        <v>832</v>
       </c>
       <c r="CI2" s="2" t="s">
-        <v>827</v>
+        <v>834</v>
       </c>
       <c r="CJ2" s="2" t="s">
-        <v>829</v>
+        <v>836</v>
       </c>
       <c r="CK2" s="2" t="s">
-        <v>831</v>
+        <v>838</v>
       </c>
       <c r="CL2" s="2" t="s">
-        <v>833</v>
+        <v>840</v>
       </c>
       <c r="CM2" s="2" t="s">
-        <v>835</v>
+        <v>842</v>
       </c>
       <c r="CN2" s="2" t="s">
-        <v>837</v>
+        <v>844</v>
       </c>
       <c r="CO2" s="2" t="s">
-        <v>839</v>
+        <v>846</v>
       </c>
       <c r="CP2" s="2" t="s">
-        <v>841</v>
+        <v>848</v>
       </c>
       <c r="CQ2" s="2" t="s">
-        <v>843</v>
+        <v>850</v>
       </c>
       <c r="CR2" s="2" t="s">
-        <v>845</v>
+        <v>852</v>
       </c>
       <c r="CS2" s="2" t="s">
-        <v>847</v>
+        <v>854</v>
       </c>
       <c r="CT2" s="2" t="s">
-        <v>849</v>
+        <v>856</v>
       </c>
       <c r="CU2" s="2" t="s">
-        <v>851</v>
+        <v>858</v>
       </c>
       <c r="CV2" s="2" t="s">
-        <v>853</v>
+        <v>860</v>
       </c>
       <c r="CW2" s="2" t="s">
-        <v>855</v>
+        <v>862</v>
       </c>
       <c r="CX2" s="2" t="s">
-        <v>857</v>
+        <v>864</v>
       </c>
       <c r="CY2" s="2" t="s">
-        <v>859</v>
+        <v>866</v>
       </c>
       <c r="CZ2" s="2" t="s">
-        <v>861</v>
+        <v>868</v>
       </c>
       <c r="DA2" s="2" t="s">
-        <v>863</v>
+        <v>870</v>
       </c>
       <c r="DB2" s="2" t="s">
-        <v>865</v>
+        <v>872</v>
       </c>
       <c r="DC2" s="2" t="s">
-        <v>867</v>
+        <v>874</v>
       </c>
       <c r="DD2" s="2" t="s">
-        <v>869</v>
+        <v>876</v>
       </c>
       <c r="DE2" s="2" t="s">
-        <v>871</v>
+        <v>878</v>
       </c>
       <c r="DF2" s="2" t="s">
-        <v>873</v>
+        <v>880</v>
       </c>
       <c r="DG2" s="2" t="s">
-        <v>875</v>
+        <v>882</v>
       </c>
       <c r="DH2" s="2" t="s">
-        <v>877</v>
+        <v>884</v>
       </c>
       <c r="DI2" s="2" t="s">
-        <v>879</v>
+        <v>886</v>
       </c>
       <c r="DJ2" s="2" t="s">
-        <v>881</v>
+        <v>888</v>
       </c>
       <c r="DK2" s="2" t="s">
-        <v>883</v>
+        <v>890</v>
       </c>
     </row>
   </sheetData>
@@ -4946,1761 +4975,1786 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:CE289"/>
+  <dimension ref="G1:CE294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:83">
       <c r="G1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="J1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="R1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AE1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AZ1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="BI1" t="s">
-        <v>748</v>
+        <v>755</v>
       </c>
       <c r="BJ1" t="s">
-        <v>756</v>
+        <v>763</v>
       </c>
       <c r="BQ1" t="s">
-        <v>776</v>
+        <v>783</v>
       </c>
       <c r="CE1" t="s">
-        <v>809</v>
+        <v>816</v>
       </c>
     </row>
     <row r="2" spans="7:83">
       <c r="G2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="H2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="J2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="R2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AE2" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AZ2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="BI2" t="s">
-        <v>749</v>
+        <v>756</v>
       </c>
       <c r="BJ2" t="s">
-        <v>757</v>
+        <v>764</v>
       </c>
       <c r="BQ2" t="s">
-        <v>777</v>
+        <v>784</v>
       </c>
       <c r="CE2" t="s">
-        <v>810</v>
+        <v>817</v>
       </c>
     </row>
     <row r="3" spans="7:83">
       <c r="G3" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="H3" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="J3" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="R3" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AE3" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AZ3" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="BI3" t="s">
-        <v>750</v>
+        <v>757</v>
       </c>
       <c r="BJ3" t="s">
-        <v>758</v>
+        <v>765</v>
       </c>
       <c r="BQ3" t="s">
-        <v>778</v>
+        <v>785</v>
       </c>
       <c r="CE3" t="s">
-        <v>811</v>
+        <v>818</v>
       </c>
     </row>
     <row r="4" spans="7:83">
       <c r="G4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="H4" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="J4" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="R4" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AZ4" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="BI4" t="s">
-        <v>751</v>
+        <v>758</v>
       </c>
       <c r="BJ4" t="s">
-        <v>759</v>
+        <v>766</v>
       </c>
       <c r="BQ4" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="CE4" t="s">
-        <v>812</v>
+        <v>819</v>
       </c>
     </row>
     <row r="5" spans="7:83">
       <c r="G5" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H5" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="J5" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="R5" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AZ5" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="BI5" t="s">
-        <v>752</v>
+        <v>759</v>
       </c>
       <c r="BJ5" t="s">
-        <v>760</v>
+        <v>767</v>
       </c>
       <c r="BQ5" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="CE5" t="s">
-        <v>813</v>
+        <v>820</v>
       </c>
     </row>
     <row r="6" spans="7:83">
       <c r="G6" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="J6" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="R6" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AZ6" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="BI6" t="s">
-        <v>753</v>
+        <v>760</v>
       </c>
       <c r="BJ6" t="s">
-        <v>761</v>
+        <v>768</v>
       </c>
       <c r="CE6" t="s">
-        <v>814</v>
+        <v>821</v>
       </c>
     </row>
     <row r="7" spans="7:83">
       <c r="G7" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J7" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="R7" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AZ7" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="CE7" t="s">
-        <v>815</v>
+        <v>822</v>
       </c>
     </row>
     <row r="8" spans="7:83">
       <c r="G8" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="R8" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AZ8" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="CE8" t="s">
-        <v>816</v>
+        <v>823</v>
       </c>
     </row>
     <row r="9" spans="7:83">
       <c r="G9" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="R9" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AZ9" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="CE9" t="s">
-        <v>817</v>
+        <v>824</v>
       </c>
     </row>
     <row r="10" spans="7:83">
       <c r="G10" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="R10" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AZ10" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="11" spans="7:83">
       <c r="G11" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="R11" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AZ11" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="12" spans="7:83">
       <c r="G12" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="R12" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AZ12" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="13" spans="7:83">
       <c r="G13" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="R13" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AZ13" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="14" spans="7:83">
       <c r="G14" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="R14" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AZ14" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="15" spans="7:83">
       <c r="G15" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="R15" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AZ15" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="16" spans="7:83">
       <c r="G16" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="R16" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AZ16" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="17" spans="7:52">
       <c r="G17" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="R17" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AZ17" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="18" spans="7:52">
       <c r="G18" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="R18" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AZ18" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="19" spans="7:52">
       <c r="G19" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="R19" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AZ19" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="20" spans="7:52">
       <c r="G20" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="R20" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AZ20" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="21" spans="7:52">
       <c r="G21" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="R21" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AZ21" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="22" spans="7:52">
       <c r="G22" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="R22" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AZ22" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="23" spans="7:52">
       <c r="G23" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="R23" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AZ23" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="24" spans="7:52">
       <c r="G24" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="R24" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AZ24" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="25" spans="7:52">
       <c r="G25" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="R25" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AZ25" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="26" spans="7:52">
       <c r="G26" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="R26" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AZ26" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="27" spans="7:52">
       <c r="G27" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="R27" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AZ27" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="28" spans="7:52">
       <c r="G28" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="R28" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AZ28" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="29" spans="7:52">
       <c r="G29" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="R29" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AZ29" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="30" spans="7:52">
       <c r="G30" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="R30" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AZ30" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="31" spans="7:52">
       <c r="R31" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AZ31" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="32" spans="7:52">
       <c r="R32" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AZ32" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="33" spans="52:52">
       <c r="AZ33" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="34" spans="52:52">
       <c r="AZ34" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="35" spans="52:52">
       <c r="AZ35" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="36" spans="52:52">
       <c r="AZ36" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="37" spans="52:52">
       <c r="AZ37" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="38" spans="52:52">
       <c r="AZ38" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="39" spans="52:52">
       <c r="AZ39" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="40" spans="52:52">
       <c r="AZ40" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="41" spans="52:52">
       <c r="AZ41" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="42" spans="52:52">
       <c r="AZ42" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="43" spans="52:52">
       <c r="AZ43" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="44" spans="52:52">
       <c r="AZ44" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="45" spans="52:52">
       <c r="AZ45" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="46" spans="52:52">
       <c r="AZ46" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="47" spans="52:52">
       <c r="AZ47" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="48" spans="52:52">
       <c r="AZ48" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="49" spans="52:52">
       <c r="AZ49" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="50" spans="52:52">
       <c r="AZ50" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="51" spans="52:52">
       <c r="AZ51" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="52" spans="52:52">
       <c r="AZ52" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="53" spans="52:52">
       <c r="AZ53" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="54" spans="52:52">
       <c r="AZ54" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="55" spans="52:52">
       <c r="AZ55" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="56" spans="52:52">
       <c r="AZ56" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="57" spans="52:52">
       <c r="AZ57" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="58" spans="52:52">
       <c r="AZ58" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="59" spans="52:52">
       <c r="AZ59" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="60" spans="52:52">
       <c r="AZ60" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="61" spans="52:52">
       <c r="AZ61" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="62" spans="52:52">
       <c r="AZ62" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="63" spans="52:52">
       <c r="AZ63" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="64" spans="52:52">
       <c r="AZ64" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="65" spans="52:52">
       <c r="AZ65" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="66" spans="52:52">
       <c r="AZ66" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="67" spans="52:52">
       <c r="AZ67" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="68" spans="52:52">
       <c r="AZ68" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="69" spans="52:52">
       <c r="AZ69" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="70" spans="52:52">
       <c r="AZ70" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="71" spans="52:52">
       <c r="AZ71" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="72" spans="52:52">
       <c r="AZ72" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="73" spans="52:52">
       <c r="AZ73" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="74" spans="52:52">
       <c r="AZ74" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="75" spans="52:52">
       <c r="AZ75" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="76" spans="52:52">
       <c r="AZ76" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="77" spans="52:52">
       <c r="AZ77" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="78" spans="52:52">
       <c r="AZ78" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="79" spans="52:52">
       <c r="AZ79" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="80" spans="52:52">
       <c r="AZ80" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="81" spans="52:52">
       <c r="AZ81" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="82" spans="52:52">
       <c r="AZ82" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="83" spans="52:52">
       <c r="AZ83" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="84" spans="52:52">
       <c r="AZ84" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="85" spans="52:52">
       <c r="AZ85" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="86" spans="52:52">
       <c r="AZ86" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="87" spans="52:52">
       <c r="AZ87" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="88" spans="52:52">
       <c r="AZ88" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="89" spans="52:52">
       <c r="AZ89" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="90" spans="52:52">
       <c r="AZ90" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="91" spans="52:52">
       <c r="AZ91" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="92" spans="52:52">
       <c r="AZ92" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="93" spans="52:52">
       <c r="AZ93" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="94" spans="52:52">
       <c r="AZ94" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="95" spans="52:52">
       <c r="AZ95" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="96" spans="52:52">
       <c r="AZ96" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="97" spans="52:52">
       <c r="AZ97" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="98" spans="52:52">
       <c r="AZ98" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="99" spans="52:52">
       <c r="AZ99" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="100" spans="52:52">
       <c r="AZ100" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="101" spans="52:52">
       <c r="AZ101" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="102" spans="52:52">
       <c r="AZ102" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="103" spans="52:52">
       <c r="AZ103" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="104" spans="52:52">
       <c r="AZ104" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="105" spans="52:52">
       <c r="AZ105" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="106" spans="52:52">
       <c r="AZ106" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="107" spans="52:52">
       <c r="AZ107" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="108" spans="52:52">
       <c r="AZ108" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="109" spans="52:52">
       <c r="AZ109" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="110" spans="52:52">
       <c r="AZ110" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="111" spans="52:52">
       <c r="AZ111" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="112" spans="52:52">
       <c r="AZ112" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="113" spans="52:52">
       <c r="AZ113" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="114" spans="52:52">
       <c r="AZ114" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="115" spans="52:52">
       <c r="AZ115" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="116" spans="52:52">
       <c r="AZ116" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="117" spans="52:52">
       <c r="AZ117" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="118" spans="52:52">
       <c r="AZ118" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="119" spans="52:52">
       <c r="AZ119" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="120" spans="52:52">
       <c r="AZ120" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="121" spans="52:52">
       <c r="AZ121" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="122" spans="52:52">
       <c r="AZ122" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="123" spans="52:52">
       <c r="AZ123" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="124" spans="52:52">
       <c r="AZ124" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="125" spans="52:52">
       <c r="AZ125" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="126" spans="52:52">
       <c r="AZ126" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="127" spans="52:52">
       <c r="AZ127" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="128" spans="52:52">
       <c r="AZ128" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="129" spans="52:52">
       <c r="AZ129" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="130" spans="52:52">
       <c r="AZ130" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="131" spans="52:52">
       <c r="AZ131" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="132" spans="52:52">
       <c r="AZ132" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="133" spans="52:52">
       <c r="AZ133" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="134" spans="52:52">
       <c r="AZ134" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="135" spans="52:52">
       <c r="AZ135" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="136" spans="52:52">
       <c r="AZ136" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="137" spans="52:52">
       <c r="AZ137" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="138" spans="52:52">
       <c r="AZ138" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="139" spans="52:52">
       <c r="AZ139" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="140" spans="52:52">
       <c r="AZ140" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="141" spans="52:52">
       <c r="AZ141" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="142" spans="52:52">
       <c r="AZ142" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="143" spans="52:52">
       <c r="AZ143" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="144" spans="52:52">
       <c r="AZ144" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="145" spans="52:52">
       <c r="AZ145" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="146" spans="52:52">
       <c r="AZ146" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="147" spans="52:52">
       <c r="AZ147" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="148" spans="52:52">
       <c r="AZ148" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="149" spans="52:52">
       <c r="AZ149" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="150" spans="52:52">
       <c r="AZ150" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="151" spans="52:52">
       <c r="AZ151" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="152" spans="52:52">
       <c r="AZ152" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="153" spans="52:52">
       <c r="AZ153" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="154" spans="52:52">
       <c r="AZ154" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="155" spans="52:52">
       <c r="AZ155" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="156" spans="52:52">
       <c r="AZ156" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="157" spans="52:52">
       <c r="AZ157" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="158" spans="52:52">
       <c r="AZ158" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="159" spans="52:52">
       <c r="AZ159" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="160" spans="52:52">
       <c r="AZ160" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="161" spans="52:52">
       <c r="AZ161" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="162" spans="52:52">
       <c r="AZ162" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="163" spans="52:52">
       <c r="AZ163" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="164" spans="52:52">
       <c r="AZ164" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="165" spans="52:52">
       <c r="AZ165" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="166" spans="52:52">
       <c r="AZ166" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="167" spans="52:52">
       <c r="AZ167" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="168" spans="52:52">
       <c r="AZ168" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="169" spans="52:52">
       <c r="AZ169" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="170" spans="52:52">
       <c r="AZ170" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="171" spans="52:52">
       <c r="AZ171" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="172" spans="52:52">
       <c r="AZ172" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="173" spans="52:52">
       <c r="AZ173" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="174" spans="52:52">
       <c r="AZ174" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="175" spans="52:52">
       <c r="AZ175" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="176" spans="52:52">
       <c r="AZ176" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="177" spans="52:52">
       <c r="AZ177" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="178" spans="52:52">
       <c r="AZ178" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="179" spans="52:52">
       <c r="AZ179" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="180" spans="52:52">
       <c r="AZ180" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="181" spans="52:52">
       <c r="AZ181" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
     </row>
     <row r="182" spans="52:52">
       <c r="AZ182" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="183" spans="52:52">
       <c r="AZ183" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="184" spans="52:52">
       <c r="AZ184" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="185" spans="52:52">
       <c r="AZ185" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="186" spans="52:52">
       <c r="AZ186" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="187" spans="52:52">
       <c r="AZ187" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="188" spans="52:52">
       <c r="AZ188" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="189" spans="52:52">
       <c r="AZ189" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="190" spans="52:52">
       <c r="AZ190" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="191" spans="52:52">
       <c r="AZ191" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
     </row>
     <row r="192" spans="52:52">
       <c r="AZ192" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="193" spans="52:52">
       <c r="AZ193" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
     </row>
     <row r="194" spans="52:52">
       <c r="AZ194" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
     </row>
     <row r="195" spans="52:52">
       <c r="AZ195" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="196" spans="52:52">
       <c r="AZ196" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
     </row>
     <row r="197" spans="52:52">
       <c r="AZ197" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
     </row>
     <row r="198" spans="52:52">
       <c r="AZ198" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="199" spans="52:52">
       <c r="AZ199" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="200" spans="52:52">
       <c r="AZ200" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="201" spans="52:52">
       <c r="AZ201" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
     <row r="202" spans="52:52">
       <c r="AZ202" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="203" spans="52:52">
       <c r="AZ203" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
     </row>
     <row r="204" spans="52:52">
       <c r="AZ204" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="205" spans="52:52">
       <c r="AZ205" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
     </row>
     <row r="206" spans="52:52">
       <c r="AZ206" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="207" spans="52:52">
       <c r="AZ207" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
     </row>
     <row r="208" spans="52:52">
       <c r="AZ208" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="209" spans="52:52">
       <c r="AZ209" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="210" spans="52:52">
       <c r="AZ210" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="211" spans="52:52">
       <c r="AZ211" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="212" spans="52:52">
       <c r="AZ212" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="213" spans="52:52">
       <c r="AZ213" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="214" spans="52:52">
       <c r="AZ214" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="215" spans="52:52">
       <c r="AZ215" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
     </row>
     <row r="216" spans="52:52">
       <c r="AZ216" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="217" spans="52:52">
       <c r="AZ217" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
     </row>
     <row r="218" spans="52:52">
       <c r="AZ218" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="219" spans="52:52">
       <c r="AZ219" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="220" spans="52:52">
       <c r="AZ220" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="221" spans="52:52">
       <c r="AZ221" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="222" spans="52:52">
       <c r="AZ222" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="223" spans="52:52">
       <c r="AZ223" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="224" spans="52:52">
       <c r="AZ224" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="225" spans="52:52">
       <c r="AZ225" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="226" spans="52:52">
       <c r="AZ226" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="227" spans="52:52">
       <c r="AZ227" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="228" spans="52:52">
       <c r="AZ228" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="229" spans="52:52">
       <c r="AZ229" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="230" spans="52:52">
       <c r="AZ230" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
     </row>
     <row r="231" spans="52:52">
       <c r="AZ231" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="232" spans="52:52">
       <c r="AZ232" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="233" spans="52:52">
       <c r="AZ233" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="234" spans="52:52">
       <c r="AZ234" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="235" spans="52:52">
       <c r="AZ235" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
     </row>
     <row r="236" spans="52:52">
       <c r="AZ236" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="237" spans="52:52">
       <c r="AZ237" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
     <row r="238" spans="52:52">
       <c r="AZ238" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="239" spans="52:52">
       <c r="AZ239" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
     </row>
     <row r="240" spans="52:52">
       <c r="AZ240" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
     </row>
     <row r="241" spans="52:52">
       <c r="AZ241" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
     </row>
     <row r="242" spans="52:52">
       <c r="AZ242" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
     </row>
     <row r="243" spans="52:52">
       <c r="AZ243" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="244" spans="52:52">
       <c r="AZ244" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
     </row>
     <row r="245" spans="52:52">
       <c r="AZ245" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
     </row>
     <row r="246" spans="52:52">
       <c r="AZ246" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
     </row>
     <row r="247" spans="52:52">
       <c r="AZ247" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
     </row>
     <row r="248" spans="52:52">
       <c r="AZ248" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
     </row>
     <row r="249" spans="52:52">
       <c r="AZ249" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
     </row>
     <row r="250" spans="52:52">
       <c r="AZ250" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
     </row>
     <row r="251" spans="52:52">
       <c r="AZ251" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
     </row>
     <row r="252" spans="52:52">
       <c r="AZ252" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
     </row>
     <row r="253" spans="52:52">
       <c r="AZ253" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
     </row>
     <row r="254" spans="52:52">
       <c r="AZ254" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
     </row>
     <row r="255" spans="52:52">
       <c r="AZ255" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
     </row>
     <row r="256" spans="52:52">
       <c r="AZ256" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
     </row>
     <row r="257" spans="52:52">
       <c r="AZ257" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
     </row>
     <row r="258" spans="52:52">
       <c r="AZ258" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
     </row>
     <row r="259" spans="52:52">
       <c r="AZ259" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
     </row>
     <row r="260" spans="52:52">
       <c r="AZ260" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
     </row>
     <row r="261" spans="52:52">
       <c r="AZ261" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
     </row>
     <row r="262" spans="52:52">
       <c r="AZ262" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
     </row>
     <row r="263" spans="52:52">
       <c r="AZ263" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
     </row>
     <row r="264" spans="52:52">
       <c r="AZ264" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
     </row>
     <row r="265" spans="52:52">
       <c r="AZ265" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
     </row>
     <row r="266" spans="52:52">
       <c r="AZ266" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
     </row>
     <row r="267" spans="52:52">
       <c r="AZ267" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
     </row>
     <row r="268" spans="52:52">
       <c r="AZ268" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
     </row>
     <row r="269" spans="52:52">
       <c r="AZ269" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
     </row>
     <row r="270" spans="52:52">
       <c r="AZ270" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
     </row>
     <row r="271" spans="52:52">
       <c r="AZ271" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
     </row>
     <row r="272" spans="52:52">
       <c r="AZ272" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
     </row>
     <row r="273" spans="52:52">
       <c r="AZ273" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
     </row>
     <row r="274" spans="52:52">
       <c r="AZ274" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
     </row>
     <row r="275" spans="52:52">
       <c r="AZ275" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
     </row>
     <row r="276" spans="52:52">
       <c r="AZ276" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
     </row>
     <row r="277" spans="52:52">
       <c r="AZ277" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
     </row>
     <row r="278" spans="52:52">
       <c r="AZ278" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
     </row>
     <row r="279" spans="52:52">
       <c r="AZ279" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
     </row>
     <row r="280" spans="52:52">
       <c r="AZ280" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
     </row>
     <row r="281" spans="52:52">
       <c r="AZ281" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
     </row>
     <row r="282" spans="52:52">
       <c r="AZ282" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
     </row>
     <row r="283" spans="52:52">
       <c r="AZ283" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
     </row>
     <row r="284" spans="52:52">
       <c r="AZ284" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
     </row>
     <row r="285" spans="52:52">
       <c r="AZ285" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
     </row>
     <row r="286" spans="52:52">
       <c r="AZ286" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
     </row>
     <row r="287" spans="52:52">
       <c r="AZ287" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
     </row>
     <row r="288" spans="52:52">
       <c r="AZ288" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
     </row>
     <row r="289" spans="52:52">
       <c r="AZ289" t="s">
-        <v>729</v>
+        <v>731</v>
+      </c>
+    </row>
+    <row r="290" spans="52:52">
+      <c r="AZ290" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="291" spans="52:52">
+      <c r="AZ291" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="292" spans="52:52">
+      <c r="AZ292" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="293" spans="52:52">
+      <c r="AZ293" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="294" spans="52:52">
+      <c r="AZ294" t="s">
+        <v>736</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000022/metadata_template_ERC000022.xlsx
+++ b/templates/ERC000022/metadata_template_ERC000022.xlsx
@@ -21,7 +21,7 @@
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
     <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AZ$1:$AZ$294</definedName>
     <definedName name="historytillage">'cv_sample'!$CE$1:$CE$9</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$89</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="899" uniqueCount="891">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="892">
   <si>
     <t>alias</t>
   </si>
@@ -736,6 +736,9 @@
   </si>
   <si>
     <t>UG 100</t>
+  </si>
+  <si>
+    <t>UG 200</t>
   </si>
   <si>
     <t>Vega</t>
@@ -3242,7 +3245,7 @@
         <v>144</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -3286,7 +3289,7 @@
         <v>145</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -3313,7 +3316,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N88"/>
+  <dimension ref="G1:N89"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -4050,6 +4053,11 @@
     </row>
     <row r="88" spans="14:14">
       <c r="N88" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="89" spans="14:14">
+      <c r="N89" t="s">
         <v>117</v>
       </c>
     </row>
@@ -4071,27 +4079,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
   </sheetData>
@@ -4111,122 +4119,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
   </sheetData>
@@ -4250,690 +4258,690 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="BO1" s="1" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="BQ1" s="1" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="BS1" s="1" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="BT1" s="1" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="BU1" s="1" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="BV1" s="1" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="BW1" s="1" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="BX1" s="1" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="BY1" s="1" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="BZ1" s="1" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="CA1" s="1" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="CB1" s="1" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="CC1" s="1" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="CD1" s="1" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="CE1" s="1" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="CF1" s="1" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="CG1" s="1" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="CH1" s="1" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="CI1" s="1" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="CJ1" s="1" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="CK1" s="1" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="CL1" s="1" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="CM1" s="1" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="CN1" s="1" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="CO1" s="1" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="CP1" s="1" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="CQ1" s="1" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="CR1" s="1" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="CS1" s="1" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="CT1" s="1" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="CU1" s="1" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="CV1" s="1" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="CW1" s="1" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="CX1" s="1" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="CY1" s="1" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="CZ1" s="1" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="DA1" s="1" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="DB1" s="1" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="DC1" s="1" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="DD1" s="1" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="DE1" s="1" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="DF1" s="1" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="DG1" s="1" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="DH1" s="1" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="DI1" s="1" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="DJ1" s="1" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="DK1" s="1" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
     </row>
     <row r="2" spans="1:115" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AS2" s="2" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AU2" s="2" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AW2" s="2" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AX2" s="2" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AY2" s="2" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AZ2" s="2" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="BA2" s="2" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="BB2" s="2" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="BC2" s="2" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="BD2" s="2" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="BE2" s="2" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="BF2" s="2" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="BG2" s="2" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="BH2" s="2" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="BI2" s="2" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="BJ2" s="2" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="BK2" s="2" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="BL2" s="2" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="BM2" s="2" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="BN2" s="2" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="BO2" s="2" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="BP2" s="2" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="BQ2" s="2" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="BR2" s="2" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="BS2" s="2" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="BT2" s="2" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="BU2" s="2" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="BV2" s="2" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="BW2" s="2" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="BX2" s="2" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BY2" s="2" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="BZ2" s="2" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="CA2" s="2" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="CB2" s="2" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="CC2" s="2" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="CD2" s="2" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="CE2" s="2" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="CF2" s="2" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="CG2" s="2" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="CH2" s="2" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="CI2" s="2" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="CJ2" s="2" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="CK2" s="2" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="CL2" s="2" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="CM2" s="2" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="CN2" s="2" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="CO2" s="2" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="CP2" s="2" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="CQ2" s="2" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="CR2" s="2" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="CS2" s="2" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="CT2" s="2" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="CU2" s="2" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="CV2" s="2" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="CW2" s="2" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="CX2" s="2" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="CY2" s="2" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="CZ2" s="2" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="DA2" s="2" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="DB2" s="2" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="DC2" s="2" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="DD2" s="2" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="DE2" s="2" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="DF2" s="2" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="DG2" s="2" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="DH2" s="2" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="DI2" s="2" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="DJ2" s="2" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="DK2" s="2" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
     </row>
   </sheetData>
@@ -4980,1781 +4988,1781 @@
   <sheetData>
     <row r="1" spans="7:83">
       <c r="G1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="J1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="R1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AE1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AZ1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="BI1" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="BJ1" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="BQ1" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="CE1" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
     </row>
     <row r="2" spans="7:83">
       <c r="G2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="J2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="R2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AE2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AZ2" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="BI2" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="BJ2" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="BQ2" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="CE2" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
     </row>
     <row r="3" spans="7:83">
       <c r="G3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H3" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="R3" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AE3" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AZ3" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="BI3" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="BJ3" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="BQ3" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="CE3" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
     </row>
     <row r="4" spans="7:83">
       <c r="G4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="J4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="R4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AZ4" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="BI4" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="BJ4" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="BQ4" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="CE4" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
     </row>
     <row r="5" spans="7:83">
       <c r="G5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H5" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="J5" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="R5" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AZ5" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="BI5" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="BJ5" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="BQ5" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="CE5" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
     </row>
     <row r="6" spans="7:83">
       <c r="G6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="J6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="R6" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AZ6" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="BI6" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="BJ6" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="CE6" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
     </row>
     <row r="7" spans="7:83">
       <c r="G7" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="J7" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="R7" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AZ7" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="CE7" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
     </row>
     <row r="8" spans="7:83">
       <c r="G8" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="R8" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AZ8" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="CE8" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
     </row>
     <row r="9" spans="7:83">
       <c r="G9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="R9" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AZ9" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="CE9" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
     </row>
     <row r="10" spans="7:83">
       <c r="G10" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="R10" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AZ10" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="11" spans="7:83">
       <c r="G11" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="R11" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AZ11" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="12" spans="7:83">
       <c r="G12" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="R12" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AZ12" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="13" spans="7:83">
       <c r="G13" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="R13" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AZ13" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="14" spans="7:83">
       <c r="G14" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="R14" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AZ14" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="15" spans="7:83">
       <c r="G15" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="R15" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AZ15" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="16" spans="7:83">
       <c r="G16" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="R16" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AZ16" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="17" spans="7:52">
       <c r="G17" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="R17" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AZ17" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="18" spans="7:52">
       <c r="G18" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="R18" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AZ18" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="19" spans="7:52">
       <c r="G19" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="R19" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AZ19" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="20" spans="7:52">
       <c r="G20" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="R20" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AZ20" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="21" spans="7:52">
       <c r="G21" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="R21" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AZ21" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="22" spans="7:52">
       <c r="G22" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="R22" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AZ22" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="23" spans="7:52">
       <c r="G23" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="R23" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AZ23" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="24" spans="7:52">
       <c r="G24" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="R24" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AZ24" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="25" spans="7:52">
       <c r="G25" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="R25" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AZ25" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="26" spans="7:52">
       <c r="G26" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="R26" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AZ26" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="27" spans="7:52">
       <c r="G27" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="R27" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AZ27" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="28" spans="7:52">
       <c r="G28" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="R28" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AZ28" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="29" spans="7:52">
       <c r="G29" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="R29" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AZ29" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="30" spans="7:52">
       <c r="G30" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="R30" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AZ30" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="31" spans="7:52">
       <c r="R31" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AZ31" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="32" spans="7:52">
       <c r="R32" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AZ32" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="33" spans="52:52">
       <c r="AZ33" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="34" spans="52:52">
       <c r="AZ34" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="35" spans="52:52">
       <c r="AZ35" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="36" spans="52:52">
       <c r="AZ36" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="37" spans="52:52">
       <c r="AZ37" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="38" spans="52:52">
       <c r="AZ38" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="39" spans="52:52">
       <c r="AZ39" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="40" spans="52:52">
       <c r="AZ40" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="41" spans="52:52">
       <c r="AZ41" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="42" spans="52:52">
       <c r="AZ42" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="43" spans="52:52">
       <c r="AZ43" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="44" spans="52:52">
       <c r="AZ44" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="45" spans="52:52">
       <c r="AZ45" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="46" spans="52:52">
       <c r="AZ46" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="47" spans="52:52">
       <c r="AZ47" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="48" spans="52:52">
       <c r="AZ48" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="49" spans="52:52">
       <c r="AZ49" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="50" spans="52:52">
       <c r="AZ50" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="51" spans="52:52">
       <c r="AZ51" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="52" spans="52:52">
       <c r="AZ52" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="53" spans="52:52">
       <c r="AZ53" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="54" spans="52:52">
       <c r="AZ54" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="55" spans="52:52">
       <c r="AZ55" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="56" spans="52:52">
       <c r="AZ56" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="57" spans="52:52">
       <c r="AZ57" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="58" spans="52:52">
       <c r="AZ58" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="59" spans="52:52">
       <c r="AZ59" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="60" spans="52:52">
       <c r="AZ60" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="61" spans="52:52">
       <c r="AZ61" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="62" spans="52:52">
       <c r="AZ62" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="63" spans="52:52">
       <c r="AZ63" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="64" spans="52:52">
       <c r="AZ64" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="65" spans="52:52">
       <c r="AZ65" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="66" spans="52:52">
       <c r="AZ66" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="67" spans="52:52">
       <c r="AZ67" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="68" spans="52:52">
       <c r="AZ68" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="69" spans="52:52">
       <c r="AZ69" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="70" spans="52:52">
       <c r="AZ70" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="71" spans="52:52">
       <c r="AZ71" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="72" spans="52:52">
       <c r="AZ72" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="73" spans="52:52">
       <c r="AZ73" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="74" spans="52:52">
       <c r="AZ74" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="75" spans="52:52">
       <c r="AZ75" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="76" spans="52:52">
       <c r="AZ76" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="77" spans="52:52">
       <c r="AZ77" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="78" spans="52:52">
       <c r="AZ78" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="79" spans="52:52">
       <c r="AZ79" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="80" spans="52:52">
       <c r="AZ80" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="81" spans="52:52">
       <c r="AZ81" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="82" spans="52:52">
       <c r="AZ82" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="83" spans="52:52">
       <c r="AZ83" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="84" spans="52:52">
       <c r="AZ84" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="85" spans="52:52">
       <c r="AZ85" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="86" spans="52:52">
       <c r="AZ86" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="87" spans="52:52">
       <c r="AZ87" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="88" spans="52:52">
       <c r="AZ88" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="89" spans="52:52">
       <c r="AZ89" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="90" spans="52:52">
       <c r="AZ90" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="91" spans="52:52">
       <c r="AZ91" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="92" spans="52:52">
       <c r="AZ92" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="93" spans="52:52">
       <c r="AZ93" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="94" spans="52:52">
       <c r="AZ94" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="95" spans="52:52">
       <c r="AZ95" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="96" spans="52:52">
       <c r="AZ96" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="97" spans="52:52">
       <c r="AZ97" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="98" spans="52:52">
       <c r="AZ98" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="99" spans="52:52">
       <c r="AZ99" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="100" spans="52:52">
       <c r="AZ100" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="101" spans="52:52">
       <c r="AZ101" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="102" spans="52:52">
       <c r="AZ102" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="103" spans="52:52">
       <c r="AZ103" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="104" spans="52:52">
       <c r="AZ104" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="105" spans="52:52">
       <c r="AZ105" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="106" spans="52:52">
       <c r="AZ106" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="107" spans="52:52">
       <c r="AZ107" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="108" spans="52:52">
       <c r="AZ108" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="109" spans="52:52">
       <c r="AZ109" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="110" spans="52:52">
       <c r="AZ110" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="111" spans="52:52">
       <c r="AZ111" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="112" spans="52:52">
       <c r="AZ112" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="113" spans="52:52">
       <c r="AZ113" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="114" spans="52:52">
       <c r="AZ114" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="115" spans="52:52">
       <c r="AZ115" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="116" spans="52:52">
       <c r="AZ116" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="117" spans="52:52">
       <c r="AZ117" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="118" spans="52:52">
       <c r="AZ118" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="119" spans="52:52">
       <c r="AZ119" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="120" spans="52:52">
       <c r="AZ120" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="121" spans="52:52">
       <c r="AZ121" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="122" spans="52:52">
       <c r="AZ122" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="123" spans="52:52">
       <c r="AZ123" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="124" spans="52:52">
       <c r="AZ124" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="125" spans="52:52">
       <c r="AZ125" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="126" spans="52:52">
       <c r="AZ126" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="127" spans="52:52">
       <c r="AZ127" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="128" spans="52:52">
       <c r="AZ128" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="129" spans="52:52">
       <c r="AZ129" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="130" spans="52:52">
       <c r="AZ130" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="131" spans="52:52">
       <c r="AZ131" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="132" spans="52:52">
       <c r="AZ132" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="133" spans="52:52">
       <c r="AZ133" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="134" spans="52:52">
       <c r="AZ134" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="135" spans="52:52">
       <c r="AZ135" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="136" spans="52:52">
       <c r="AZ136" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="137" spans="52:52">
       <c r="AZ137" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="138" spans="52:52">
       <c r="AZ138" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="139" spans="52:52">
       <c r="AZ139" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="140" spans="52:52">
       <c r="AZ140" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="141" spans="52:52">
       <c r="AZ141" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="142" spans="52:52">
       <c r="AZ142" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="143" spans="52:52">
       <c r="AZ143" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="144" spans="52:52">
       <c r="AZ144" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="145" spans="52:52">
       <c r="AZ145" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="146" spans="52:52">
       <c r="AZ146" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="147" spans="52:52">
       <c r="AZ147" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="148" spans="52:52">
       <c r="AZ148" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="149" spans="52:52">
       <c r="AZ149" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="150" spans="52:52">
       <c r="AZ150" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="151" spans="52:52">
       <c r="AZ151" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="152" spans="52:52">
       <c r="AZ152" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="153" spans="52:52">
       <c r="AZ153" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="154" spans="52:52">
       <c r="AZ154" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="155" spans="52:52">
       <c r="AZ155" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="156" spans="52:52">
       <c r="AZ156" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="157" spans="52:52">
       <c r="AZ157" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="158" spans="52:52">
       <c r="AZ158" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="159" spans="52:52">
       <c r="AZ159" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="160" spans="52:52">
       <c r="AZ160" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="161" spans="52:52">
       <c r="AZ161" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="162" spans="52:52">
       <c r="AZ162" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="163" spans="52:52">
       <c r="AZ163" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="164" spans="52:52">
       <c r="AZ164" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="165" spans="52:52">
       <c r="AZ165" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="166" spans="52:52">
       <c r="AZ166" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="167" spans="52:52">
       <c r="AZ167" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="168" spans="52:52">
       <c r="AZ168" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="169" spans="52:52">
       <c r="AZ169" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="170" spans="52:52">
       <c r="AZ170" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="171" spans="52:52">
       <c r="AZ171" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="172" spans="52:52">
       <c r="AZ172" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="173" spans="52:52">
       <c r="AZ173" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="174" spans="52:52">
       <c r="AZ174" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="175" spans="52:52">
       <c r="AZ175" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="176" spans="52:52">
       <c r="AZ176" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="177" spans="52:52">
       <c r="AZ177" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="178" spans="52:52">
       <c r="AZ178" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="179" spans="52:52">
       <c r="AZ179" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="180" spans="52:52">
       <c r="AZ180" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="181" spans="52:52">
       <c r="AZ181" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="182" spans="52:52">
       <c r="AZ182" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="183" spans="52:52">
       <c r="AZ183" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="184" spans="52:52">
       <c r="AZ184" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="185" spans="52:52">
       <c r="AZ185" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="186" spans="52:52">
       <c r="AZ186" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="187" spans="52:52">
       <c r="AZ187" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="188" spans="52:52">
       <c r="AZ188" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="189" spans="52:52">
       <c r="AZ189" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="190" spans="52:52">
       <c r="AZ190" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="191" spans="52:52">
       <c r="AZ191" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="192" spans="52:52">
       <c r="AZ192" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="193" spans="52:52">
       <c r="AZ193" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="194" spans="52:52">
       <c r="AZ194" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="195" spans="52:52">
       <c r="AZ195" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="196" spans="52:52">
       <c r="AZ196" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
     </row>
     <row r="197" spans="52:52">
       <c r="AZ197" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="198" spans="52:52">
       <c r="AZ198" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="199" spans="52:52">
       <c r="AZ199" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="200" spans="52:52">
       <c r="AZ200" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="201" spans="52:52">
       <c r="AZ201" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="202" spans="52:52">
       <c r="AZ202" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="203" spans="52:52">
       <c r="AZ203" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="204" spans="52:52">
       <c r="AZ204" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="205" spans="52:52">
       <c r="AZ205" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="206" spans="52:52">
       <c r="AZ206" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="207" spans="52:52">
       <c r="AZ207" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="208" spans="52:52">
       <c r="AZ208" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="209" spans="52:52">
       <c r="AZ209" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="210" spans="52:52">
       <c r="AZ210" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="211" spans="52:52">
       <c r="AZ211" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="212" spans="52:52">
       <c r="AZ212" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="213" spans="52:52">
       <c r="AZ213" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="214" spans="52:52">
       <c r="AZ214" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="215" spans="52:52">
       <c r="AZ215" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="216" spans="52:52">
       <c r="AZ216" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="217" spans="52:52">
       <c r="AZ217" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="218" spans="52:52">
       <c r="AZ218" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="219" spans="52:52">
       <c r="AZ219" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="220" spans="52:52">
       <c r="AZ220" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="221" spans="52:52">
       <c r="AZ221" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="222" spans="52:52">
       <c r="AZ222" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="223" spans="52:52">
       <c r="AZ223" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="224" spans="52:52">
       <c r="AZ224" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="225" spans="52:52">
       <c r="AZ225" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="226" spans="52:52">
       <c r="AZ226" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="227" spans="52:52">
       <c r="AZ227" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="228" spans="52:52">
       <c r="AZ228" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="229" spans="52:52">
       <c r="AZ229" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="230" spans="52:52">
       <c r="AZ230" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="231" spans="52:52">
       <c r="AZ231" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="232" spans="52:52">
       <c r="AZ232" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="233" spans="52:52">
       <c r="AZ233" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="234" spans="52:52">
       <c r="AZ234" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="235" spans="52:52">
       <c r="AZ235" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="236" spans="52:52">
       <c r="AZ236" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="237" spans="52:52">
       <c r="AZ237" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="238" spans="52:52">
       <c r="AZ238" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="239" spans="52:52">
       <c r="AZ239" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="240" spans="52:52">
       <c r="AZ240" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="241" spans="52:52">
       <c r="AZ241" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="242" spans="52:52">
       <c r="AZ242" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="243" spans="52:52">
       <c r="AZ243" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="244" spans="52:52">
       <c r="AZ244" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="245" spans="52:52">
       <c r="AZ245" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="246" spans="52:52">
       <c r="AZ246" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
     </row>
     <row r="247" spans="52:52">
       <c r="AZ247" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="248" spans="52:52">
       <c r="AZ248" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
     </row>
     <row r="249" spans="52:52">
       <c r="AZ249" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="250" spans="52:52">
       <c r="AZ250" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
     </row>
     <row r="251" spans="52:52">
       <c r="AZ251" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="252" spans="52:52">
       <c r="AZ252" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="253" spans="52:52">
       <c r="AZ253" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="254" spans="52:52">
       <c r="AZ254" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
     </row>
     <row r="255" spans="52:52">
       <c r="AZ255" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="256" spans="52:52">
       <c r="AZ256" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
     </row>
     <row r="257" spans="52:52">
       <c r="AZ257" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="258" spans="52:52">
       <c r="AZ258" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
     </row>
     <row r="259" spans="52:52">
       <c r="AZ259" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="260" spans="52:52">
       <c r="AZ260" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="261" spans="52:52">
       <c r="AZ261" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="262" spans="52:52">
       <c r="AZ262" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="263" spans="52:52">
       <c r="AZ263" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
     </row>
     <row r="264" spans="52:52">
       <c r="AZ264" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
     </row>
     <row r="265" spans="52:52">
       <c r="AZ265" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
     </row>
     <row r="266" spans="52:52">
       <c r="AZ266" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
     </row>
     <row r="267" spans="52:52">
       <c r="AZ267" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
     </row>
     <row r="268" spans="52:52">
       <c r="AZ268" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
     </row>
     <row r="269" spans="52:52">
       <c r="AZ269" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="270" spans="52:52">
       <c r="AZ270" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
     </row>
     <row r="271" spans="52:52">
       <c r="AZ271" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
     </row>
     <row r="272" spans="52:52">
       <c r="AZ272" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
     </row>
     <row r="273" spans="52:52">
       <c r="AZ273" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
     </row>
     <row r="274" spans="52:52">
       <c r="AZ274" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
     </row>
     <row r="275" spans="52:52">
       <c r="AZ275" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="276" spans="52:52">
       <c r="AZ276" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
     </row>
     <row r="277" spans="52:52">
       <c r="AZ277" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="278" spans="52:52">
       <c r="AZ278" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
     </row>
     <row r="279" spans="52:52">
       <c r="AZ279" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="280" spans="52:52">
       <c r="AZ280" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
     </row>
     <row r="281" spans="52:52">
       <c r="AZ281" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
     </row>
     <row r="282" spans="52:52">
       <c r="AZ282" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
     </row>
     <row r="283" spans="52:52">
       <c r="AZ283" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
     </row>
     <row r="284" spans="52:52">
       <c r="AZ284" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
     </row>
     <row r="285" spans="52:52">
       <c r="AZ285" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
     </row>
     <row r="286" spans="52:52">
       <c r="AZ286" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
     </row>
     <row r="287" spans="52:52">
       <c r="AZ287" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="288" spans="52:52">
       <c r="AZ288" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
     </row>
     <row r="289" spans="52:52">
       <c r="AZ289" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
     </row>
     <row r="290" spans="52:52">
       <c r="AZ290" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
     </row>
     <row r="291" spans="52:52">
       <c r="AZ291" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
     </row>
     <row r="292" spans="52:52">
       <c r="AZ292" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
     </row>
     <row r="293" spans="52:52">
       <c r="AZ293" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
     </row>
     <row r="294" spans="52:52">
       <c r="AZ294" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
     </row>
   </sheetData>
